--- a/_OUTPUT--Recruiting_Coord.xlsx
+++ b/_OUTPUT--Recruiting_Coord.xlsx
@@ -845,7 +845,11 @@
           <t>Auto-disqualifier: no explicit Gujarat/Gujarati connection on profile</t>
         </is>
       </c>
-      <c r="AM2" s="4" t="n"/>
+      <c r="AM2" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN2" s="3" t="n"/>
     </row>
     <row r="3">
@@ -1013,7 +1017,11 @@
           <t>Limited SaaS company exposure; no Sales recruiting specifically; no Greenhouse/ATS experience</t>
         </is>
       </c>
-      <c r="AM3" s="4" t="n"/>
+      <c r="AM3" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN3" s="3" t="n"/>
     </row>
     <row r="4">
@@ -1177,7 +1185,11 @@
           <t>No Sales recruiting; limited SaaS exposure; no Greenhouse ATS; lacks startup experience; senior-level background may overshooting role requirements</t>
         </is>
       </c>
-      <c r="AM4" s="4" t="n"/>
+      <c r="AM4" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN4" s="3" t="n"/>
     </row>
     <row r="5">
@@ -1344,7 +1356,11 @@
           <t>No Sales hiring experience; zero SaaS exposure; no high-volume metrics; no Greenhouse ATS experience</t>
         </is>
       </c>
-      <c r="AM5" s="4" t="n"/>
+      <c r="AM5" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN5" s="3" t="n"/>
     </row>
     <row r="6">
@@ -1510,7 +1526,11 @@
           <t>Auto-disqualifier: zero SaaS exposure across career</t>
         </is>
       </c>
-      <c r="AM6" s="4" t="n"/>
+      <c r="AM6" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN6" s="3" t="n"/>
     </row>
     <row r="7">
@@ -1677,7 +1697,11 @@
           <t>No Sales recruiting experience; zero validated SaaS exposure; no high-volume metrics; no ATS tool experience; limited tenure stability</t>
         </is>
       </c>
-      <c r="AM7" s="4" t="n"/>
+      <c r="AM7" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN7" s="3" t="n"/>
     </row>
     <row r="8">
@@ -1843,7 +1867,11 @@
           <t>Auto-disqualifier: zero SaaS exposure across career</t>
         </is>
       </c>
-      <c r="AM8" s="4" t="n"/>
+      <c r="AM8" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN8" s="3" t="n"/>
     </row>
     <row r="9">
@@ -2011,7 +2039,11 @@
           <t>No explicit Sales hiring experience; limited high-volume metrics; title mismatch (Recruiter vs Coordinator); limited SaaS validation beyond Greenhouse</t>
         </is>
       </c>
-      <c r="AM9" s="4" t="n"/>
+      <c r="AM9" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN9" s="3" t="n"/>
     </row>
     <row r="10">
@@ -2168,7 +2200,7 @@
       </c>
       <c r="AJ10" s="4" t="inlineStr">
         <is>
-          <t>Auto-DQ</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AK10" s="4" t="inlineStr">
@@ -2183,7 +2215,11 @@
           <t>No Sales hiring experience; no validated SaaS company; limited high-volume metrics; no Greenhouse ATS</t>
         </is>
       </c>
-      <c r="AM10" s="4" t="n"/>
+      <c r="AM10" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN10" s="3" t="n"/>
     </row>
     <row r="11">
@@ -2349,7 +2385,11 @@
           <t>Auto-disqualifier: zero SaaS exposure across career</t>
         </is>
       </c>
-      <c r="AM11" s="4" t="n"/>
+      <c r="AM11" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN11" s="3" t="n"/>
     </row>
     <row r="12">
@@ -2515,7 +2555,11 @@
           <t>Auto-disqualifier: zero SaaS exposure across career; BPO/call center operations background</t>
         </is>
       </c>
-      <c r="AM12" s="4" t="n"/>
+      <c r="AM12" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN12" s="3" t="n"/>
     </row>
     <row r="13">
@@ -2683,7 +2727,11 @@
           <t>No Sales hiring experience; limited SaaS validation; no Greenhouse ATS; lacks high-volume metrics; pattern of job-hopping</t>
         </is>
       </c>
-      <c r="AM13" s="4" t="n"/>
+      <c r="AM13" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN13" s="3" t="n"/>
     </row>
     <row r="14">
@@ -2851,7 +2899,11 @@
           <t>Zero Sales hiring experience; no validated SaaS exposure; no high-volume metrics; no Greenhouse ATS; IT-only recruiting background</t>
         </is>
       </c>
-      <c r="AM14" s="4" t="n"/>
+      <c r="AM14" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN14" s="3" t="n"/>
     </row>
     <row r="15">
@@ -3017,7 +3069,11 @@
           <t>Auto-disqualifier: zero SaaS exposure across career</t>
         </is>
       </c>
-      <c r="AM15" s="4" t="n"/>
+      <c r="AM15" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN15" s="3" t="n"/>
     </row>
     <row r="16">
@@ -3173,7 +3229,11 @@
           <t>Profile URL mismatch — couldn't verify full work history. No SaaS specifically. No sales hiring or high-volume evidence.</t>
         </is>
       </c>
-      <c r="AM16" s="4" t="n"/>
+      <c r="AM16" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN16" s="3" t="n"/>
     </row>
     <row r="17">
@@ -3339,7 +3399,11 @@
           <t>Auto-disqualifier: zero SaaS exposure; BPO/call center operations background</t>
         </is>
       </c>
-      <c r="AM17" s="4" t="n"/>
+      <c r="AM17" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN17" s="3" t="n"/>
     </row>
     <row r="18">
@@ -3505,7 +3569,11 @@
           <t>Auto-disqualifier: zero SaaS exposure across career</t>
         </is>
       </c>
-      <c r="AM18" s="4" t="n"/>
+      <c r="AM18" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN18" s="3" t="n"/>
     </row>
     <row r="19">
@@ -3671,7 +3739,11 @@
           <t>Auto-disqualifier: zero SaaS exposure across career</t>
         </is>
       </c>
-      <c r="AM19" s="4" t="n"/>
+      <c r="AM19" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN19" s="3" t="n"/>
     </row>
     <row r="20">
@@ -3837,7 +3909,11 @@
           <t>Auto-disqualifier: zero SaaS exposure across entire career</t>
         </is>
       </c>
-      <c r="AM20" s="4" t="n"/>
+      <c r="AM20" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN20" s="3" t="n"/>
     </row>
     <row r="21">
@@ -4003,7 +4079,11 @@
           <t>Auto-disqualifier: zero SaaS exposure across career</t>
         </is>
       </c>
-      <c r="AM21" s="4" t="n"/>
+      <c r="AM21" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN21" s="3" t="n"/>
     </row>
     <row r="22">
@@ -4169,7 +4249,11 @@
           <t>Auto-disqualifier: zero SaaS exposure; pure staffing agency recruiter background</t>
         </is>
       </c>
-      <c r="AM22" s="4" t="n"/>
+      <c r="AM22" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN22" s="3" t="n"/>
     </row>
     <row r="23">
@@ -4339,7 +4423,11 @@
           <t>No explicit Sales hiring focus (SDR/AE recruiting); no Greenhouse/ATS system experience; no quantified high-volume sourcing metrics (calls/screens)</t>
         </is>
       </c>
-      <c r="AM23" s="4" t="n"/>
+      <c r="AM23" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN23" s="3" t="n"/>
     </row>
     <row r="24">
@@ -4505,7 +4593,11 @@
           <t>Auto-disqualifier: zero SaaS exposure; staffing/recruiting services company background only</t>
         </is>
       </c>
-      <c r="AM24" s="4" t="n"/>
+      <c r="AM24" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN24" s="3" t="n"/>
     </row>
     <row r="25">
@@ -4671,7 +4763,11 @@
           <t>Auto-disqualifier: zero SaaS exposure across entire career</t>
         </is>
       </c>
-      <c r="AM25" s="4" t="n"/>
+      <c r="AM25" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN25" s="3" t="n"/>
     </row>
     <row r="26">
@@ -4827,7 +4923,11 @@
           <t>No SaaS specifically. No sales hiring experience. No high-volume metrics quantified. Company (Moksh Tech) is small/unclear scale.</t>
         </is>
       </c>
-      <c r="AM26" s="4" t="n"/>
+      <c r="AM26" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN26" s="3" t="n"/>
     </row>
     <row r="27">
@@ -4993,7 +5093,11 @@
           <t>Auto-disqualifier: zero SaaS exposure across career</t>
         </is>
       </c>
-      <c r="AM27" s="4" t="n"/>
+      <c r="AM27" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN27" s="3" t="n"/>
     </row>
     <row r="28">
@@ -5149,7 +5253,11 @@
           <t>Just started at ProductSquads 1 month ago. Prior career entirely US staffing agencies. No SaaS specifically. No sales hiring. Short tenures.</t>
         </is>
       </c>
-      <c r="AM28" s="4" t="n"/>
+      <c r="AM28" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN28" s="3" t="n"/>
     </row>
     <row r="29">
@@ -5315,7 +5423,11 @@
           <t>Auto-disqualifier: iGeeksBlog is a tech media platform (Apple product coverage), not a validated SaaS/Software product company</t>
         </is>
       </c>
-      <c r="AM29" s="4" t="n"/>
+      <c r="AM29" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN29" s="3" t="n"/>
     </row>
     <row r="30">
@@ -5481,7 +5593,11 @@
           <t>Auto-disqualifier: zero SaaS/tech product exposure; pure staffing agency recruiter background</t>
         </is>
       </c>
-      <c r="AM30" s="4" t="n"/>
+      <c r="AM30" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN30" s="3" t="n"/>
     </row>
     <row r="31">
@@ -5491,7 +5607,11 @@
         </is>
       </c>
       <c r="B31" s="5" t="n"/>
-      <c r="C31" s="6" t="n"/>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nishi-acharya-a0536231a</t>
+        </is>
+      </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/talent/profile/AEMAAFDavSUBtSaqubyCfA_tmkCDmbzZeykrUfY</t>
@@ -5647,7 +5767,11 @@
           <t>Auto-disqualifier: zero SaaS exposure across entire career</t>
         </is>
       </c>
-      <c r="AM31" s="4" t="n"/>
+      <c r="AM31" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN31" s="3" t="n"/>
     </row>
     <row r="32">
@@ -5657,7 +5781,11 @@
         </is>
       </c>
       <c r="B32" s="5" t="n"/>
-      <c r="C32" s="6" t="n"/>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/yash-basrani</t>
+        </is>
+      </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/talent/profile/AEMAACgF49EB8XLqrUdQ59SDFUXu5H9ijLU2Q10</t>
@@ -5813,7 +5941,11 @@
           <t>Auto-disqualifier: zero SaaS/tech exposure</t>
         </is>
       </c>
-      <c r="AM32" s="4" t="n"/>
+      <c r="AM32" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN32" s="3" t="n"/>
     </row>
     <row r="33">
@@ -5979,7 +6111,11 @@
           <t>Auto-disqualifier: zero SaaS/tech product company exposure</t>
         </is>
       </c>
-      <c r="AM33" s="4" t="n"/>
+      <c r="AM33" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN33" s="3" t="n"/>
     </row>
     <row r="34">
@@ -6145,7 +6281,11 @@
           <t>Auto-disqualifier: zero SaaS or software product company exposure across entire career; staffing/recruiting services background only (IMS Group)</t>
         </is>
       </c>
-      <c r="AM34" s="4" t="n"/>
+      <c r="AM34" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN34" s="3" t="n"/>
     </row>
     <row r="35">
@@ -6311,7 +6451,11 @@
           <t>Auto-disqualifier: zero SaaS exposure across entire career</t>
         </is>
       </c>
-      <c r="AM35" s="4" t="n"/>
+      <c r="AM35" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN35" s="3" t="n"/>
     </row>
     <row r="36">
@@ -6479,7 +6623,11 @@
           <t>Zero Sales hiring experience; limited high-volume metrics; no Greenhouse ATS; minimal SaaS exposure</t>
         </is>
       </c>
-      <c r="AM36" s="4" t="n"/>
+      <c r="AM36" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN36" s="3" t="n"/>
     </row>
     <row r="37">
@@ -6645,7 +6793,11 @@
           <t>Auto-disqualifier: zero SaaS/tech product company exposure across entire career; all career roles at non-SaaS companies (engineering consulting, energy/solar)</t>
         </is>
       </c>
-      <c r="AM37" s="4" t="n"/>
+      <c r="AM37" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN37" s="3" t="n"/>
     </row>
     <row r="38">
@@ -6811,7 +6963,11 @@
           <t>Auto-disqualifier: zero SaaS exposure; pure staffing/recruiting agency recruiter; accounting/finance focus incompatible with SaaS recruiting coordinator role</t>
         </is>
       </c>
-      <c r="AM38" s="4" t="n"/>
+      <c r="AM38" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN38" s="3" t="n"/>
     </row>
     <row r="39">
@@ -6977,7 +7133,11 @@
           <t>Auto-disqualifier: zero SaaS exposure across entire career</t>
         </is>
       </c>
-      <c r="AM39" s="4" t="n"/>
+      <c r="AM39" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN39" s="3" t="n"/>
     </row>
     <row r="40">
@@ -7143,7 +7303,11 @@
           <t>Auto-disqualifier: zero SaaS exposure across entire career; pure staffing/recruiting services background (IMS Group) with no in-house product/SaaS company experience</t>
         </is>
       </c>
-      <c r="AM40" s="4" t="n"/>
+      <c r="AM40" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN40" s="3" t="n"/>
     </row>
     <row r="41">
@@ -7311,7 +7475,11 @@
           <t>No Sales recruiting experience; no high-volume sourcing metrics; no Greenhouse ATS; limited startup exposure; senior-level background may exceed coordinator role scope</t>
         </is>
       </c>
-      <c r="AM41" s="4" t="n"/>
+      <c r="AM41" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN41" s="3" t="n"/>
     </row>
     <row r="42">
@@ -7477,7 +7645,11 @@
           <t>Auto-disqualifier: zero SaaS/software product company exposure across entire career; all roles at staffing/recruiting services, HR services, or non-tech companies</t>
         </is>
       </c>
-      <c r="AM42" s="4" t="n"/>
+      <c r="AM42" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN42" s="3" t="n"/>
     </row>
     <row r="43">
@@ -7603,7 +7775,11 @@
       </c>
       <c r="AK43" s="4" t="n"/>
       <c r="AL43" s="4" t="n"/>
-      <c r="AM43" s="4" t="n"/>
+      <c r="AM43" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN43" s="3" t="n"/>
     </row>
     <row r="44">
@@ -7765,7 +7941,11 @@
           <t>No Sales hiring exp; weak title match; no high-volume metrics; minimal SaaS product exposure; no ATS/ops experience</t>
         </is>
       </c>
-      <c r="AM44" s="4" t="n"/>
+      <c r="AM44" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN44" s="3" t="n"/>
     </row>
     <row r="45">
@@ -7931,7 +8111,11 @@
           <t>Zero SaaS exposure disqualifies</t>
         </is>
       </c>
-      <c r="AM45" s="4" t="n"/>
+      <c r="AM45" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN45" s="3" t="n"/>
     </row>
     <row r="46">
@@ -8093,7 +8277,11 @@
       </c>
       <c r="AK46" s="4" t="n"/>
       <c r="AL46" s="4" t="n"/>
-      <c r="AM46" s="4" t="n"/>
+      <c r="AM46" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN46" s="3" t="n"/>
     </row>
     <row r="47">
@@ -8259,7 +8447,11 @@
           <t>No venture-backed SaaS/tech product company experience</t>
         </is>
       </c>
-      <c r="AM47" s="4" t="n"/>
+      <c r="AM47" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN47" s="3" t="n"/>
     </row>
     <row r="48">
@@ -8425,7 +8617,11 @@
           <t>Auto-disqualifier: zero SaaS exposure; staffing/recruiting services company background only</t>
         </is>
       </c>
-      <c r="AM48" s="4" t="n"/>
+      <c r="AM48" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN48" s="3" t="n"/>
     </row>
     <row r="49">
@@ -8591,7 +8787,11 @@
           <t>Linkruit is recruitment agency, not SaaS/tech company</t>
         </is>
       </c>
-      <c r="AM49" s="4" t="n"/>
+      <c r="AM49" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN49" s="3" t="n"/>
     </row>
     <row r="50">
@@ -8717,7 +8917,11 @@
       </c>
       <c r="AK50" s="4" t="n"/>
       <c r="AL50" s="4" t="n"/>
-      <c r="AM50" s="4" t="n"/>
+      <c r="AM50" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN50" s="3" t="n"/>
     </row>
     <row r="51">
@@ -8887,7 +9091,11 @@
           <t>No Sales hiring experience is the primary gap for this role; would need training on Sales candidate profiles</t>
         </is>
       </c>
-      <c r="AM51" s="4" t="n"/>
+      <c r="AM51" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN51" s="3" t="n"/>
     </row>
     <row r="52">
@@ -9017,7 +9225,11 @@
           <t>Auto-disqualified: No SaaS/tech product experience</t>
         </is>
       </c>
-      <c r="AM52" s="4" t="n"/>
+      <c r="AM52" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN52" s="3" t="n"/>
     </row>
     <row r="53">
@@ -9143,7 +9355,11 @@
       </c>
       <c r="AK53" s="4" t="n"/>
       <c r="AL53" s="4" t="n"/>
-      <c r="AM53" s="4" t="n"/>
+      <c r="AM53" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN53" s="3" t="n"/>
     </row>
     <row r="54">
@@ -9305,7 +9521,11 @@
           <t>No Sales hiring experience, no quantified high-volume metrics, unclear SaaS background, non-recruiting-focused titles</t>
         </is>
       </c>
-      <c r="AM54" s="4" t="n"/>
+      <c r="AM54" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN54" s="3" t="n"/>
     </row>
     <row r="55">
@@ -9471,7 +9691,11 @@
           <t>Auto-disqualifier: zero SaaS exposure across entire career; pure staffing/recruiting services background</t>
         </is>
       </c>
-      <c r="AM55" s="4" t="n"/>
+      <c r="AM55" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN55" s="3" t="n"/>
     </row>
     <row r="56">
@@ -9633,7 +9857,11 @@
           <t>Fundamental mismatch: candidate is business development/partnership specialist, not recruiting coordinator; zero recruiting, zero ATS, zero Sales hiring experience; no title match or role alignment with recruiting coordinator position</t>
         </is>
       </c>
-      <c r="AM56" s="4" t="n"/>
+      <c r="AM56" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN56" s="3" t="n"/>
     </row>
     <row r="57">
@@ -9799,7 +10027,11 @@
           <t>No validated SaaS company or venture-backed tech company experience</t>
         </is>
       </c>
-      <c r="AM57" s="4" t="n"/>
+      <c r="AM57" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN57" s="3" t="n"/>
     </row>
     <row r="58">
@@ -9965,7 +10197,11 @@
           <t>Auto-disqualifier: zero SaaS/tech exposure. All experience in traditional industries (food, healthcare, fashion, HR services).</t>
         </is>
       </c>
-      <c r="AM58" s="4" t="n"/>
+      <c r="AM58" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN58" s="3" t="n"/>
     </row>
     <row r="59">
@@ -10127,7 +10363,11 @@
           <t>No Sales hiring (critical 5×); no high-volume metrics; limited SaaS; no ATS/ops experience; no US/startup background</t>
         </is>
       </c>
-      <c r="AM59" s="4" t="n"/>
+      <c r="AM59" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN59" s="3" t="n"/>
     </row>
     <row r="60">
@@ -10296,7 +10536,11 @@
           <t>Limited SaaS exposure; primarily traditional industry (Adani); no US company experience; title not exact match</t>
         </is>
       </c>
-      <c r="AM60" s="4" t="n"/>
+      <c r="AM60" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN60" s="3" t="n"/>
     </row>
     <row r="61">
@@ -10462,7 +10706,11 @@
           <t>Auto-disqualifier: No explicit SaaS or venture-backed tech company experience</t>
         </is>
       </c>
-      <c r="AM61" s="4" t="n"/>
+      <c r="AM61" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN61" s="3" t="n"/>
     </row>
     <row r="62">
@@ -10588,7 +10836,11 @@
       </c>
       <c r="AK62" s="4" t="n"/>
       <c r="AL62" s="4" t="n"/>
-      <c r="AM62" s="4" t="n"/>
+      <c r="AM62" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN62" s="3" t="n"/>
     </row>
     <row r="63">
@@ -10766,7 +11018,11 @@
           <t>No recruiting coordination background, zero high-volume sourcing experience, no Sales hiring exposure</t>
         </is>
       </c>
-      <c r="AM63" s="7" t="n"/>
+      <c r="AM63" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN63" s="3" t="n"/>
     </row>
     <row r="64">
@@ -10948,7 +11204,11 @@
           <t>Auto-disqualifier: zero SaaS/tech company exposure</t>
         </is>
       </c>
-      <c r="AM64" s="7" t="n"/>
+      <c r="AM64" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN64" s="3" t="n"/>
     </row>
     <row r="65">
@@ -11111,7 +11371,7 @@
       </c>
       <c r="AM65" s="7" t="inlineStr">
         <is>
-          <t>Zero Sales hiring experience (critical gap); no true SaaS exposure; no specific ATS named; no startup experience</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="AN65" s="7" t="n"/>
@@ -11299,7 +11559,11 @@
           <t>No SaaS product company experience; no Sales hiring background; no ATS tools mentioned; job hopping pattern; very short current tenure (3 months); limited to IT services/recruitment consulting only</t>
         </is>
       </c>
-      <c r="AM66" s="7" t="n"/>
+      <c r="AM66" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN66" s="3" t="n"/>
     </row>
     <row r="67">
@@ -11463,7 +11727,11 @@
           <t>No recruiting-specific ATS (Greenhouse) mentioned; no quantified sourcing volume; recent role changes frequent (6-12 mos); BabyOrgano is FMCG not SaaS; limited SaaS tenure (1 yr at Paramount only)</t>
         </is>
       </c>
-      <c r="AM67" s="7" t="n"/>
+      <c r="AM67" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN67" s="3" t="n"/>
     </row>
     <row r="68">
@@ -11653,7 +11921,11 @@
           <t>Title mismatch (HR Recruiter vs. Recruiting Coordinator); no quantified sourcing metrics; no Sales hiring background</t>
         </is>
       </c>
-      <c r="AM68" s="7" t="n"/>
+      <c r="AM68" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN68" s="3" t="n"/>
     </row>
     <row r="69">
@@ -11803,7 +12075,11 @@
           <t>Pure staffing agency career with no in-house recruiting coordination experience at product company</t>
         </is>
       </c>
-      <c r="AM69" s="7" t="n"/>
+      <c r="AM69" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN69" s="3" t="n"/>
     </row>
     <row r="70">
@@ -11961,7 +12237,11 @@
           <t>Title is HR Lead (not Recruiting Coordinator); no explicit Sales hiring experience; no mention of Greenhouse or recruiting-specific ATS; no startup/VC experience</t>
         </is>
       </c>
-      <c r="AM70" s="7" t="n"/>
+      <c r="AM70" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN70" s="3" t="n"/>
     </row>
     <row r="71">
@@ -12099,7 +12379,11 @@
       </c>
       <c r="AK71" s="7" t="n"/>
       <c r="AL71" s="7" t="n"/>
-      <c r="AM71" s="7" t="n"/>
+      <c r="AM71" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN71" s="3" t="n"/>
     </row>
     <row r="72">
@@ -12286,7 +12570,11 @@
           <t>Not Recruiting Coordinator title match. Zero Sales hiring experience. Weak SaaS background (primarily enterprise/tech non-SaaS). No specific ATS tool experience mentioned.</t>
         </is>
       </c>
-      <c r="AM72" s="7" t="n"/>
+      <c r="AM72" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN72" s="3" t="n"/>
     </row>
     <row r="73">
@@ -12468,7 +12756,11 @@
           <t>Zero SaaS product experience - entire career in traditional staffing/automotive recruiting</t>
         </is>
       </c>
-      <c r="AM73" s="7" t="n"/>
+      <c r="AM73" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN73" s="3" t="n"/>
     </row>
     <row r="74">
@@ -12610,7 +12902,11 @@
       </c>
       <c r="AK74" s="7" t="n"/>
       <c r="AL74" s="7" t="n"/>
-      <c r="AM74" s="7" t="n"/>
+      <c r="AM74" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN74" s="3" t="n"/>
     </row>
     <row r="75">
@@ -12792,7 +13088,11 @@
           <t>Title mismatch (HR Generalist vs Recruiting Coordinator); no Sales hiring; no high-volume metrics; zero ATS experience; no Greenhouse</t>
         </is>
       </c>
-      <c r="AM75" s="7" t="n"/>
+      <c r="AM75" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN75" s="3" t="n"/>
     </row>
     <row r="76">
@@ -12934,7 +13234,11 @@
       </c>
       <c r="AK76" s="7" t="n"/>
       <c r="AL76" s="7" t="n"/>
-      <c r="AM76" s="7" t="n"/>
+      <c r="AM76" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN76" s="3" t="n"/>
     </row>
     <row r="77">
@@ -13120,7 +13424,11 @@
           <t>No explicit ATS (Greenhouse) experience; recent roles shorter tenure; Sales hiring secondary not primary focus</t>
         </is>
       </c>
-      <c r="AM77" s="7" t="n"/>
+      <c r="AM77" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN77" s="3" t="n"/>
     </row>
     <row r="78">
@@ -13306,7 +13614,11 @@
           <t>No Sales hiring experience - exclusively technical recruiting; No Greenhouse experience (SwiftSku uses Greenhouse); Limited high-volume metrics quantification; No US company exposure; Relatively short tenures across roles</t>
         </is>
       </c>
-      <c r="AM78" s="7" t="n"/>
+      <c r="AM78" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN78" s="3" t="n"/>
     </row>
     <row r="79">
@@ -13473,7 +13785,11 @@
           <t>Limited SaaS exposure; TA Specialist title vs Recruiting Coordinator; no Sales hiring background</t>
         </is>
       </c>
-      <c r="AM79" s="7" t="n"/>
+      <c r="AM79" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN79" s="3" t="n"/>
     </row>
     <row r="80">
@@ -13655,7 +13971,11 @@
           <t>Career heavily weighted toward Adani (cement/ports/logistics) - non-tech traditional industry</t>
         </is>
       </c>
-      <c r="AM80" s="7" t="n"/>
+      <c r="AM80" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN80" s="3" t="n"/>
     </row>
     <row r="81">
@@ -13801,7 +14121,11 @@
           <t>Zero SaaS/tech background</t>
         </is>
       </c>
-      <c r="AM81" s="7" t="n"/>
+      <c r="AM81" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN81" s="3" t="n"/>
     </row>
     <row r="82">
@@ -13947,7 +14271,11 @@
           <t>No SaaS or venture-backed tech company experience</t>
         </is>
       </c>
-      <c r="AM82" s="7" t="n"/>
+      <c r="AM82" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN82" s="3" t="n"/>
     </row>
     <row r="83">
@@ -14089,7 +14417,11 @@
       </c>
       <c r="AK83" s="7" t="n"/>
       <c r="AL83" s="7" t="n"/>
-      <c r="AM83" s="7" t="n"/>
+      <c r="AM83" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN83" s="3" t="n"/>
     </row>
     <row r="84">
@@ -14231,7 +14563,11 @@
       </c>
       <c r="AK84" s="7" t="n"/>
       <c r="AL84" s="7" t="n"/>
-      <c r="AM84" s="7" t="n"/>
+      <c r="AM84" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN84" s="3" t="n"/>
     </row>
     <row r="85">
@@ -14415,7 +14751,11 @@
           <t>Zero Sales hiring experience - critical gap for role; No Greenhouse ATS knowledge; Limited SaaS exposure</t>
         </is>
       </c>
-      <c r="AM85" s="7" t="n"/>
+      <c r="AM85" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN85" s="3" t="n"/>
     </row>
     <row r="86">
@@ -14565,7 +14905,11 @@
           <t>Career entirely in traditional banking (Bank of America). Zero exposure to SaaS, software products, or tech companies. Does not meet fundamental requirement for SwiftSku recruiting coordinator role.</t>
         </is>
       </c>
-      <c r="AM86" s="7" t="n"/>
+      <c r="AM86" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN86" s="3" t="n"/>
     </row>
     <row r="87">
@@ -14719,7 +15063,11 @@
           <t>Career entirely in traditional industries (banking, manufacturing, HR consulting) - no SaaS exposure</t>
         </is>
       </c>
-      <c r="AM87" s="7" t="n"/>
+      <c r="AM87" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN87" s="3" t="n"/>
     </row>
     <row r="88">
@@ -14897,7 +15245,11 @@
           <t>Title too senior (executive vs coordinator), no sales hiring, unclear SaaS background, job hopping</t>
         </is>
       </c>
-      <c r="AM88" s="7" t="n"/>
+      <c r="AM88" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN88" s="3" t="n"/>
     </row>
     <row r="89">
@@ -15083,7 +15435,11 @@
           <t>No Sales hiring experience; Title is TA Specialist not Recruiting Coordinator; No Greenhouse ATS experience; Job hopping pattern; No explicit US company exposure; Education in progress</t>
         </is>
       </c>
-      <c r="AM89" s="7" t="n"/>
+      <c r="AM89" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN89" s="3" t="n"/>
     </row>
     <row r="90">
@@ -15270,7 +15626,11 @@
           <t>Limited high-volume sourcing background; no Sales hiring focus; lacks ATS experience; no startup/US exposure</t>
         </is>
       </c>
-      <c r="AM90" s="7" t="n"/>
+      <c r="AM90" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN90" s="3" t="n"/>
     </row>
     <row r="91">
@@ -15452,7 +15812,11 @@
           <t>All recruiting roles at staffing/recruiting agencies (Surekha Technologies, Tridhya Tech, HireWay Consulting). No in-house recruiting coordinator experience at product company.</t>
         </is>
       </c>
-      <c r="AM91" s="3" t="n"/>
+      <c r="AM91" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN91" s="3" t="n"/>
     </row>
     <row r="92">
@@ -15580,7 +15944,11 @@
       </c>
       <c r="AK92" s="7" t="n"/>
       <c r="AL92" s="7" t="n"/>
-      <c r="AM92" s="7" t="n"/>
+      <c r="AM92" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN92" s="3" t="n"/>
     </row>
     <row r="93">
@@ -15741,7 +16109,11 @@
           <t>Associate TA title (not coordinator); no high-volume metrics; zero Sales hiring experience; recent Adani role (traditional conglomerate) concerning; no ATS/Greenhouse experience; no US exposure</t>
         </is>
       </c>
-      <c r="AM93" s="3" t="n"/>
+      <c r="AM93" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN93" s="3" t="n"/>
     </row>
     <row r="94">
@@ -15969,7 +16341,11 @@
           <t>No clear SaaS company background; all roles at staffing/recruitment agencies or unknown companies</t>
         </is>
       </c>
-      <c r="AM95" s="3" t="n"/>
+      <c r="AM95" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN95" s="3" t="n"/>
     </row>
     <row r="96">
@@ -16160,7 +16536,11 @@
           <t>No Sales hiring experience; no recruiting-specific ATS (Greenhouse/Lever) mentioned; startup status unclear</t>
         </is>
       </c>
-      <c r="AM96" s="7" t="n"/>
+      <c r="AM96" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN96" s="3" t="n"/>
     </row>
     <row r="97">
@@ -16345,7 +16725,11 @@
           <t>No Sales hiring experience (role needs Sales recruiter); No validated SaaS company background; No HR credentials; Recruiting firm background, not SaaS product company</t>
         </is>
       </c>
-      <c r="AM97" s="7" t="n"/>
+      <c r="AM97" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN97" s="7" t="n"/>
     </row>
     <row r="98">
@@ -16527,7 +16911,11 @@
           <t>Entire career at staffing agencies (IMS People Possible, Shivansh Outsourcing). Pharma/life science recruiting is non-SaaS. No in-house recruiting coordination experience.</t>
         </is>
       </c>
-      <c r="AM98" s="3" t="n"/>
+      <c r="AM98" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN98" s="3" t="n"/>
     </row>
     <row r="99">
@@ -16709,7 +17097,11 @@
           <t>Career limited to staffing/recruiting agencies and in-house HR ops. No SaaS product company experience.</t>
         </is>
       </c>
-      <c r="AM99" s="3" t="n"/>
+      <c r="AM99" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN99" s="3" t="n"/>
     </row>
     <row r="100">
@@ -16851,7 +17243,11 @@
       </c>
       <c r="AK100" s="7" t="n"/>
       <c r="AL100" s="7" t="n"/>
-      <c r="AM100" s="3" t="n"/>
+      <c r="AM100" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN100" s="3" t="n"/>
     </row>
     <row r="101">
@@ -16993,7 +17389,11 @@
       </c>
       <c r="AK101" s="7" t="n"/>
       <c r="AL101" s="7" t="n"/>
-      <c r="AM101" s="3" t="n"/>
+      <c r="AM101" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN101" s="3" t="n"/>
     </row>
     <row r="102">
@@ -17178,7 +17578,11 @@
           <t>No SaaS product company experience; no ATS tooling mentioned; title is Sr. Executive level (overqualified/wrong level for Coordinator role); no US company background</t>
         </is>
       </c>
-      <c r="AM102" s="7" t="n"/>
+      <c r="AM102" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN102" s="3" t="n"/>
     </row>
   </sheetData>

--- a/_OUTPUT--Recruiting_Coord.xlsx
+++ b/_OUTPUT--Recruiting_Coord.xlsx
@@ -71,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -93,6 +93,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -459,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN102"/>
+  <dimension ref="A1:AN109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20.29" customWidth="1" min="1" max="1"/>
@@ -5955,7 +5958,11 @@
         </is>
       </c>
       <c r="B33" s="5" t="n"/>
-      <c r="C33" s="6" t="n"/>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shubham-patel-sap356427</t>
+        </is>
+      </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/talent/profile/AEMAADV7-rMBq5lTm7XaNLk68qrDTxeA7PVficc</t>
@@ -6977,7 +6984,11 @@
         </is>
       </c>
       <c r="B39" s="5" t="n"/>
-      <c r="C39" s="6" t="n"/>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/piyush-malviya-7a6382375</t>
+        </is>
+      </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/talent/profile/AEMAAFzIDe4BPucGq8TqheaFYhgboGOh8AJNlUw</t>
@@ -7147,7 +7158,11 @@
         </is>
       </c>
       <c r="B40" s="5" t="n"/>
-      <c r="C40" s="6" t="n"/>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/simran-kumari-a29075200</t>
+        </is>
+      </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/talent/profile/AEMAADNEXoEBP8EfpTStSd8WZo0-a0Nc9XGC8wk</t>
@@ -16177,29 +16192,43 @@
       <c r="Z94" s="7" t="n"/>
       <c r="AA94" s="7" t="n"/>
       <c r="AB94" s="7" t="n"/>
-      <c r="AC94" s="7" t="n"/>
-      <c r="AD94" s="7" t="n"/>
-      <c r="AE94" s="7" t="n"/>
-      <c r="AF94" s="7" t="inlineStr">
-        <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="AG94" s="7" t="n"/>
+      <c r="AC94" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="7" t="n">
+        <v>52.8</v>
+      </c>
       <c r="AH94" s="7" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AI94" s="7" t="inlineStr">
+        <is>
           <t>F</t>
         </is>
       </c>
-      <c r="AI94" s="7" t="inlineStr">
+      <c r="AJ94" s="7" t="inlineStr">
         <is>
           <t>Hard No</t>
         </is>
       </c>
-      <c r="AJ94" s="7" t="n"/>
       <c r="AK94" s="7" t="n"/>
       <c r="AL94" s="3" t="n"/>
-      <c r="AM94" s="3" t="n"/>
+      <c r="AM94" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="AN94" s="3" t="n"/>
     </row>
     <row r="95">
@@ -17585,6 +17614,907 @@
       </c>
       <c r="AN102" s="3" t="n"/>
     </row>
+    <row r="103">
+      <c r="A103" s="8" t="inlineStr">
+        <is>
+          <t>Paras Shah</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="inlineStr"/>
+      <c r="C103" s="8" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/parashah</t>
+        </is>
+      </c>
+      <c r="D103" s="8" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/talent/profile/AEMAAB_w53kBJjUA4mGrVR4OZYVK_EGxxZehRIA</t>
+        </is>
+      </c>
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t>Talent Scout Specialist</t>
+        </is>
+      </c>
+      <c r="F103" s="8" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="G103" s="8" t="inlineStr">
+        <is>
+          <t>Ahmedabad, Gujarat, India</t>
+        </is>
+      </c>
+      <c r="H103" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I103" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J103" s="8" t="inlineStr"/>
+      <c r="K103" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L103" s="8" t="inlineStr">
+        <is>
+          <t>HR generalist/Talent Scout role; recruiting duties but not titled 'Coordinator'</t>
+        </is>
+      </c>
+      <c r="M103" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N103" s="8" t="inlineStr">
+        <is>
+          <t>Mentions full-cycle recruiting and proactive sourcing; lacks quantified daily call/screen metrics</t>
+        </is>
+      </c>
+      <c r="O103" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" s="8" t="inlineStr">
+        <is>
+          <t>Recruited for Analytics/Data Science, Account Managers, Marketing Ops; no SDRs, AEs, or BDRs</t>
+        </is>
+      </c>
+      <c r="Q103" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R103" s="8" t="inlineStr">
+        <is>
+          <t>Accenture consulting with projects for Data &amp; AI, tech initiatives; SaaS-adjacent but not core product company</t>
+        </is>
+      </c>
+      <c r="S103" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T103" s="8" t="inlineStr">
+        <is>
+          <t>B.E. Computer Engineering from GTU (2016); engineering background but no HR certifications</t>
+        </is>
+      </c>
+      <c r="U103" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V103" s="8" t="inlineStr">
+        <is>
+          <t>Workforce Analytics and HR Consulting skills mentioned; no specific ATS tools (no Greenhouse) mentioned</t>
+        </is>
+      </c>
+      <c r="W103" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="X103" s="8" t="inlineStr">
+        <is>
+          <t>Mixed tenure: current 7 months, prior role 1.5 yrs, various 1-2 year stints; moderate stability</t>
+        </is>
+      </c>
+      <c r="Y103" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z103" s="8" t="inlineStr">
+        <is>
+          <t>Accenture US HQ but India-based role; some US stakeholder collaboration mentioned</t>
+        </is>
+      </c>
+      <c r="AA103" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB103" s="8" t="inlineStr">
+        <is>
+          <t>Career at large consulting/services firms (Accenture, dentsu, ALOIS); no VC-backed or startup experience</t>
+        </is>
+      </c>
+      <c r="AC103" s="8" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="AD103" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AE103" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF103" s="8" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="AG103" s="8" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="AH103" s="8" t="inlineStr">
+        <is>
+          <t>57.4%</t>
+        </is>
+      </c>
+      <c r="AI103" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ103" s="8" t="inlineStr">
+        <is>
+          <t>Maybe</t>
+        </is>
+      </c>
+      <c r="AK103" s="8" t="inlineStr">
+        <is>
+          <t>• Ahmedabad-based with 8+ years recruiting experience
+• Full-cycle recruitment background with proactive sourcing
+• Engineering degree suggests technical awareness</t>
+        </is>
+      </c>
+      <c r="AL103" s="8" t="inlineStr">
+        <is>
+          <t>No Sales recruiting; limited pure SaaS exposure; no high-volume call metrics; no ATS/Greenhouse experience; consulting vs. product company background</t>
+        </is>
+      </c>
+      <c r="AM103" s="8" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="8" t="inlineStr">
+        <is>
+          <t>Anamika Pandit</t>
+        </is>
+      </c>
+      <c r="B104" s="8" t="inlineStr"/>
+      <c r="C104" s="8" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/anamika-pandit-157883157</t>
+        </is>
+      </c>
+      <c r="D104" s="8" t="inlineStr">
+        <is>
+          <t>Senior Talent Acquisition Specialist</t>
+        </is>
+      </c>
+      <c r="E104" s="8" t="inlineStr">
+        <is>
+          <t>SUDERO ADVISORS AND CONSULTING</t>
+        </is>
+      </c>
+      <c r="F104" s="8" t="inlineStr">
+        <is>
+          <t>Bangalore, Maharashtra, India</t>
+        </is>
+      </c>
+      <c r="G104" s="8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H104" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I104" s="8" t="inlineStr">
+        <is>
+          <t>BFSI/Banking industry majority (non-tech); No Gujarat/Gujarati connection; Zero SaaS/venture-backed tech exposure</t>
+        </is>
+      </c>
+      <c r="J104" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" s="8" t="inlineStr"/>
+      <c r="L104" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="8" t="inlineStr"/>
+      <c r="N104" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" s="8" t="inlineStr"/>
+      <c r="P104" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" s="8" t="inlineStr"/>
+      <c r="R104" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" s="8" t="inlineStr"/>
+      <c r="T104" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" s="8" t="inlineStr"/>
+      <c r="V104" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W104" s="8" t="inlineStr"/>
+      <c r="X104" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y104" s="8" t="inlineStr"/>
+      <c r="Z104" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA104" s="8" t="inlineStr"/>
+      <c r="AB104" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC104" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD104" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE104" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF104" s="8" t="inlineStr">
+        <is>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="AG104" s="8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AH104" s="8" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AI104" s="8" t="inlineStr">
+        <is>
+          <t>Hard No</t>
+        </is>
+      </c>
+      <c r="AJ104" s="8" t="inlineStr"/>
+      <c r="AK104" s="8" t="inlineStr"/>
+      <c r="AL104" s="8" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t>Iramben Saumil Virani</t>
+        </is>
+      </c>
+      <c r="B105" s="8" t="inlineStr"/>
+      <c r="C105" s="8" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/iramben-saumil-virani-23110a21b</t>
+        </is>
+      </c>
+      <c r="D105" s="8" t="inlineStr">
+        <is>
+          <t>Recruiter / US Recruiter</t>
+        </is>
+      </c>
+      <c r="E105" s="8" t="inlineStr">
+        <is>
+          <t>HGS / IMS People Possible</t>
+        </is>
+      </c>
+      <c r="F105" s="8" t="inlineStr">
+        <is>
+          <t>Ahmedabad, Gujarat, India</t>
+        </is>
+      </c>
+      <c r="G105" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H105" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I105" s="8" t="inlineStr">
+        <is>
+          <t>Zero SaaS or Software Product exposure or worked at a venture backed technology company</t>
+        </is>
+      </c>
+      <c r="J105" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" s="8" t="inlineStr">
+        <is>
+          <t>Recruiter title, not Recruiting Coordinator; full-cycle but not coordination-focused</t>
+        </is>
+      </c>
+      <c r="L105" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="8" t="inlineStr">
+        <is>
+          <t>Quantified: 5-10 hires/quarter; high-volume projects (warehouse, logistics, healthcare, manufacturing); Fortune 100/500 clients</t>
+        </is>
+      </c>
+      <c r="N105" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" s="8" t="inlineStr">
+        <is>
+          <t>No evidence of Sales recruiting (SDRs, AEs, AMs, BDRs); recruited for IT, healthcare, warehouse, logistics</t>
+        </is>
+      </c>
+      <c r="P105" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" s="8" t="inlineStr">
+        <is>
+          <t>Zero SaaS exposure; career in staffing agency (IMS People Possible), BPO (HGS), and healthcare (Advantmed)</t>
+        </is>
+      </c>
+      <c r="R105" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" s="8" t="inlineStr">
+        <is>
+          <t>Master's degree in Food Science &amp; Nutrition from Gujarat University; not traditional HR education; no HR certifications mentioned</t>
+        </is>
+      </c>
+      <c r="T105" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U105" s="8" t="inlineStr">
+        <is>
+          <t>ATS experience: Bullhorn, Job Diva, E-recruit; coordination duties: onboarding, scheduling, candidate communication</t>
+        </is>
+      </c>
+      <c r="V105" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W105" s="8" t="inlineStr">
+        <is>
+          <t>HGS 6mo, IMS People Possible 11mo, Advantmed 11mo; pattern of short tenures and job-hopping</t>
+        </is>
+      </c>
+      <c r="X105" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y105" s="8" t="inlineStr">
+        <is>
+          <t>IMS People Possible: India company but US Recruiter role, worked with US-based Fortune 100/500 clients</t>
+        </is>
+      </c>
+      <c r="Z105" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA105" s="8" t="inlineStr">
+        <is>
+          <t>No VC-backed or startup experience; all companies established (BPO, staffing agency, healthcare)</t>
+        </is>
+      </c>
+      <c r="AB105" s="8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC105" s="8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AD105" s="8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AE105" s="8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AF105" s="8" t="inlineStr">
+        <is>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="AG105" s="8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AH105" s="8" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AI105" s="8" t="inlineStr">
+        <is>
+          <t>Hard No</t>
+        </is>
+      </c>
+      <c r="AJ105" s="8" t="inlineStr"/>
+      <c r="AK105" s="8" t="inlineStr">
+        <is>
+          <t>No SaaS/tech background - auto-disqualified per JD requirements</t>
+        </is>
+      </c>
+      <c r="AL105" s="8" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="8" t="inlineStr">
+        <is>
+          <t>Yash Raj</t>
+        </is>
+      </c>
+      <c r="B106" s="8" t="inlineStr"/>
+      <c r="C106" s="8" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/yashrajsolanki</t>
+        </is>
+      </c>
+      <c r="D106" s="8" t="inlineStr">
+        <is>
+          <t>MSP Delivery Manager (North America)</t>
+        </is>
+      </c>
+      <c r="E106" s="8" t="inlineStr">
+        <is>
+          <t>Hirextra</t>
+        </is>
+      </c>
+      <c r="F106" s="8" t="inlineStr">
+        <is>
+          <t>Vadodara, Gujarat, India</t>
+        </is>
+      </c>
+      <c r="G106" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H106" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I106" s="8" t="inlineStr">
+        <is>
+          <t>Zero SaaS/Software/Venture-backed tech exposure — entire career in staffing agencies and MSP recruiting</t>
+        </is>
+      </c>
+      <c r="J106" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" s="8" t="inlineStr"/>
+      <c r="L106" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="8" t="inlineStr"/>
+      <c r="N106" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" s="8" t="inlineStr"/>
+      <c r="P106" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" s="8" t="inlineStr"/>
+      <c r="R106" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" s="8" t="inlineStr"/>
+      <c r="T106" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" s="8" t="inlineStr"/>
+      <c r="V106" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W106" s="8" t="inlineStr"/>
+      <c r="X106" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y106" s="8" t="inlineStr"/>
+      <c r="Z106" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA106" s="8" t="inlineStr"/>
+      <c r="AB106" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC106" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD106" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE106" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF106" s="8" t="inlineStr">
+        <is>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="AG106" s="8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AH106" s="8" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AI106" s="8" t="inlineStr">
+        <is>
+          <t>Hard No</t>
+        </is>
+      </c>
+      <c r="AJ106" s="8" t="inlineStr"/>
+      <c r="AK106" s="8" t="inlineStr">
+        <is>
+          <t>No tech/SaaS exposure</t>
+        </is>
+      </c>
+      <c r="AL106" s="8" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="8" t="inlineStr">
+        <is>
+          <t>UNABLE_TO_EVALUATE</t>
+        </is>
+      </c>
+      <c r="B107" s="8" t="inlineStr"/>
+      <c r="C107" s="8" t="inlineStr"/>
+      <c r="D107" s="8" t="inlineStr"/>
+      <c r="E107" s="8" t="inlineStr"/>
+      <c r="F107" s="8" t="inlineStr"/>
+      <c r="G107" s="8" t="inlineStr"/>
+      <c r="H107" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I107" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn Recruiter access denied - profile ID AEMAAC56J-wBJLXiiRndjJJwPZq4Ekc0CwoPY4MM not accessible</t>
+        </is>
+      </c>
+      <c r="J107" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" s="8" t="inlineStr"/>
+      <c r="L107" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="8" t="inlineStr"/>
+      <c r="N107" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" s="8" t="inlineStr"/>
+      <c r="P107" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" s="8" t="inlineStr"/>
+      <c r="R107" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" s="8" t="inlineStr"/>
+      <c r="T107" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" s="8" t="inlineStr"/>
+      <c r="V107" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W107" s="8" t="inlineStr"/>
+      <c r="X107" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y107" s="8" t="inlineStr"/>
+      <c r="Z107" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA107" s="8" t="inlineStr"/>
+      <c r="AB107" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC107" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD107" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE107" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF107" s="8" t="inlineStr">
+        <is>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="AG107" s="8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AH107" s="8" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AI107" s="8" t="inlineStr">
+        <is>
+          <t>Unable to Evaluate</t>
+        </is>
+      </c>
+      <c r="AJ107" s="8" t="inlineStr"/>
+      <c r="AK107" s="8" t="inlineStr"/>
+      <c r="AL107" s="8" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="8" t="inlineStr">
+        <is>
+          <t>Dhwani Saija</t>
+        </is>
+      </c>
+      <c r="B108" s="8" t="inlineStr"/>
+      <c r="C108" s="8" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dhwani-saija-349466188</t>
+        </is>
+      </c>
+      <c r="D108" s="8" t="inlineStr">
+        <is>
+          <t>Sr Talent Acquisition &amp; Partner</t>
+        </is>
+      </c>
+      <c r="E108" s="8" t="inlineStr">
+        <is>
+          <t>E2M Solutions</t>
+        </is>
+      </c>
+      <c r="F108" s="8" t="inlineStr">
+        <is>
+          <t>Ahmedabad, Gujarat, India</t>
+        </is>
+      </c>
+      <c r="G108" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H108" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I108" s="8" t="inlineStr">
+        <is>
+          <t>Zero SaaS/Software Product exposure — E2M Solutions is HR Services/recruiting firm, not tech SaaS company</t>
+        </is>
+      </c>
+      <c r="J108" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" s="8" t="inlineStr"/>
+      <c r="L108" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="8" t="inlineStr"/>
+      <c r="N108" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" s="8" t="inlineStr"/>
+      <c r="P108" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" s="8" t="inlineStr"/>
+      <c r="R108" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" s="8" t="inlineStr"/>
+      <c r="T108" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U108" s="8" t="inlineStr"/>
+      <c r="V108" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W108" s="8" t="inlineStr"/>
+      <c r="X108" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y108" s="8" t="inlineStr"/>
+      <c r="Z108" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA108" s="8" t="inlineStr"/>
+      <c r="AB108" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC108" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD108" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE108" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF108" s="8" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="AG108" s="8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AH108" s="8" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AI108" s="8" t="inlineStr">
+        <is>
+          <t>Hard No</t>
+        </is>
+      </c>
+      <c r="AJ108" s="8" t="inlineStr"/>
+      <c r="AK108" s="8" t="inlineStr">
+        <is>
+          <t>E2M Solutions is HR Services/recruiting, not tech SaaS</t>
+        </is>
+      </c>
+      <c r="AL108" s="8" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>Roger Sequeira</t>
+        </is>
+      </c>
+      <c r="B109" s="8" t="inlineStr"/>
+      <c r="C109" s="8" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/roger-sequeira-01583424</t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="inlineStr">
+        <is>
+          <t>Sr. Talent Acquisition</t>
+        </is>
+      </c>
+      <c r="E109" s="8" t="inlineStr">
+        <is>
+          <t>Microlink Solutions Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="F109" s="8" t="inlineStr">
+        <is>
+          <t>Ahmedabad, Gujarat, India</t>
+        </is>
+      </c>
+      <c r="G109" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H109" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I109" s="8" t="inlineStr">
+        <is>
+          <t>Zero SaaS or Software Product exposure - all roles at IT Services companies</t>
+        </is>
+      </c>
+      <c r="J109" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" s="8" t="inlineStr">
+        <is>
+          <t>Sr. TA at IT services - not recruiting coordinator role</t>
+        </is>
+      </c>
+      <c r="L109" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="8" t="inlineStr"/>
+      <c r="N109" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" s="8" t="inlineStr"/>
+      <c r="P109" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" s="8" t="inlineStr"/>
+      <c r="R109" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" s="8" t="inlineStr"/>
+      <c r="T109" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U109" s="8" t="inlineStr"/>
+      <c r="V109" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W109" s="8" t="inlineStr"/>
+      <c r="X109" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y109" s="8" t="inlineStr"/>
+      <c r="Z109" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA109" s="8" t="inlineStr"/>
+      <c r="AB109" s="8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC109" s="8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AD109" s="8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AE109" s="8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AF109" s="8" t="inlineStr">
+        <is>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="AG109" s="8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AH109" s="8" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AI109" s="8" t="inlineStr">
+        <is>
+          <t>Hard No</t>
+        </is>
+      </c>
+      <c r="AJ109" s="8" t="inlineStr"/>
+      <c r="AK109" s="8" t="inlineStr">
+        <is>
+          <t>Auto-disqualified: zero SaaS exposure</t>
+        </is>
+      </c>
+      <c r="AL109" s="8" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:AN1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/_OUTPUT--Recruiting_Coord.xlsx
+++ b/_OUTPUT--Recruiting_Coord.xlsx
@@ -74,7 +74,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -103,6 +103,19 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -468,29 +481,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN112"/>
+  <dimension ref="A1:AN122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20.29" customWidth="1" min="1" max="1"/>
-    <col width="13.71" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="11.57" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="37.43" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="12.71" customWidth="1" min="8" max="8"/>
-    <col width="21.86" customWidth="1" min="9" max="9"/>
-    <col width="11.14" customWidth="1" min="28" max="28"/>
-    <col width="25" customWidth="1" min="29" max="29"/>
-    <col width="24" customWidth="1" min="30" max="30"/>
-    <col width="25.71" customWidth="1" min="31" max="31"/>
-    <col width="10.29" customWidth="1" min="32" max="32"/>
-    <col width="10.43" customWidth="1" min="33" max="33"/>
-    <col width="4.29" customWidth="1" min="34" max="34"/>
-    <col width="8.859999999999999" customWidth="1" min="35" max="35"/>
-    <col width="60" customWidth="1" min="36" max="36"/>
-    <col width="59.43" customWidth="1" min="37" max="37"/>
-    <col width="37.43" customWidth="1" min="38" max="38"/>
+    <col width="20.29" customWidth="1" style="14" min="1" max="1"/>
+    <col width="13.71" customWidth="1" style="14" min="2" max="2"/>
+    <col width="13.71" customWidth="1" style="14" min="3" max="3"/>
+    <col width="13.71" customWidth="1" style="14" min="4" max="4"/>
+    <col width="22" customWidth="1" style="14" min="5" max="5"/>
+    <col width="37.43" customWidth="1" style="14" min="6" max="6"/>
+    <col width="15" customWidth="1" style="14" min="7" max="7"/>
+    <col width="12.71" customWidth="1" style="14" min="8" max="8"/>
+    <col width="21.86" customWidth="1" style="14" min="9" max="9"/>
+    <col width="11.14" customWidth="1" style="14" min="28" max="28"/>
+    <col width="25" customWidth="1" style="14" min="29" max="29"/>
+    <col width="24" customWidth="1" style="14" min="30" max="30"/>
+    <col width="25.71" customWidth="1" style="14" min="31" max="31"/>
+    <col width="10.29" customWidth="1" style="14" min="32" max="32"/>
+    <col width="10.43" customWidth="1" style="14" min="33" max="33"/>
+    <col width="4.29" customWidth="1" style="14" min="34" max="34"/>
+    <col width="8.859999999999999" customWidth="1" style="14" min="35" max="35"/>
+    <col width="60" customWidth="1" style="14" min="36" max="36"/>
+    <col width="59.43" customWidth="1" style="14" min="37" max="37"/>
+    <col width="37.43" customWidth="1" style="14" min="38" max="38"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -504,12 +517,12 @@
           <t>Greenhouse URL</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>Public LI URL</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>LIR URL</t>
         </is>
@@ -701,13 +714,13 @@
           <t>Sayali Paunikar</t>
         </is>
       </c>
-      <c r="B2" s="5" t="n"/>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="B2" s="13" t="n"/>
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/sayali-paunikar</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n"/>
+      <c r="D2" s="12" t="n"/>
       <c r="E2" s="4" t="n"/>
       <c r="F2" s="4" t="inlineStr">
         <is>
@@ -871,13 +884,13 @@
           <t>Deepali Tanna</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="B3" s="13" t="n"/>
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/deepali-tanna-shrm-cp</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n"/>
+      <c r="D3" s="12" t="n"/>
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="inlineStr">
         <is>
@@ -1043,9 +1056,9 @@
           <t>Binod Kumar Samal</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="3" t="n"/>
+      <c r="B4" s="13" t="n"/>
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="12" t="n"/>
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="inlineStr">
         <is>
@@ -1211,13 +1224,13 @@
           <t>Shruti Rajput</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="B5" s="13" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/shruti-rajput-baa6a9253</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n"/>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="4" t="inlineStr">
         <is>
@@ -1382,13 +1395,13 @@
           <t>Cairns Dabhi</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/cairns-dabhi-549554251</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n"/>
+      <c r="D6" s="12" t="n"/>
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="inlineStr">
         <is>
@@ -1552,13 +1565,13 @@
           <t>Namita Gupta</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="B7" s="13" t="n"/>
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/namita-gupta</t>
         </is>
       </c>
-      <c r="D7" s="3" t="n"/>
+      <c r="D7" s="12" t="n"/>
       <c r="E7" s="4" t="n"/>
       <c r="F7" s="4" t="inlineStr">
         <is>
@@ -1723,13 +1736,13 @@
           <t>Naman Tiwari</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="B8" s="13" t="n"/>
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/naman-tiwari</t>
         </is>
       </c>
-      <c r="D8" s="3" t="n"/>
+      <c r="D8" s="12" t="n"/>
       <c r="E8" s="4" t="n"/>
       <c r="F8" s="4" t="inlineStr">
         <is>
@@ -1893,13 +1906,13 @@
           <t>Prince Kandachalil</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="B9" s="13" t="n"/>
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/prince-kandachalil</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n"/>
+      <c r="D9" s="12" t="n"/>
       <c r="E9" s="4" t="n"/>
       <c r="F9" s="4" t="inlineStr">
         <is>
@@ -2065,13 +2078,13 @@
           <t>Faizan Shaikh</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="B10" s="13" t="n"/>
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/faizan-shaikh</t>
         </is>
       </c>
-      <c r="D10" s="3" t="n"/>
+      <c r="D10" s="12" t="n"/>
       <c r="E10" s="4" t="n"/>
       <c r="F10" s="4" t="inlineStr">
         <is>
@@ -2241,13 +2254,13 @@
           <t>Dharmik Bharakhda</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/dharmik-bharakhda</t>
         </is>
       </c>
-      <c r="D11" s="3" t="n"/>
+      <c r="D11" s="12" t="n"/>
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="inlineStr">
         <is>
@@ -2411,13 +2424,13 @@
           <t>Jal Kuntar</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/jal-kuntar</t>
         </is>
       </c>
-      <c r="D12" s="3" t="n"/>
+      <c r="D12" s="12" t="n"/>
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="4" t="inlineStr">
         <is>
@@ -2581,13 +2594,13 @@
           <t>Disha N.</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="B13" s="13" t="n"/>
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/disha-nagpal</t>
         </is>
       </c>
-      <c r="D13" s="3" t="n"/>
+      <c r="D13" s="12" t="n"/>
       <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="inlineStr">
         <is>
@@ -2753,13 +2766,13 @@
           <t>Tamanna Chouhan</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/tamanna-chouhan-798891202</t>
         </is>
       </c>
-      <c r="D14" s="3" t="n"/>
+      <c r="D14" s="12" t="n"/>
       <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="inlineStr">
         <is>
@@ -2925,13 +2938,13 @@
           <t>Jay Patel</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="B15" s="13" t="n"/>
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/jay-patel-a4444b330</t>
         </is>
       </c>
-      <c r="D15" s="3" t="n"/>
+      <c r="D15" s="12" t="n"/>
       <c r="E15" s="4" t="n"/>
       <c r="F15" s="4" t="inlineStr">
         <is>
@@ -3095,13 +3108,13 @@
           <t>Nandini Parmar</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/nandini-parmar</t>
         </is>
       </c>
-      <c r="D16" s="3" t="n"/>
+      <c r="D16" s="12" t="n"/>
       <c r="E16" s="4" t="n"/>
       <c r="F16" s="4" t="inlineStr">
         <is>
@@ -3255,13 +3268,13 @@
           <t>Chanchal Soni</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="B17" s="13" t="n"/>
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/chanchal-soni-b90909313</t>
         </is>
       </c>
-      <c r="D17" s="3" t="n"/>
+      <c r="D17" s="12" t="n"/>
       <c r="E17" s="4" t="n"/>
       <c r="F17" s="4" t="inlineStr">
         <is>
@@ -3425,13 +3438,13 @@
           <t>Shilpa Paul</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/shilpa-paul-recruiting</t>
         </is>
       </c>
-      <c r="D18" s="3" t="n"/>
+      <c r="D18" s="12" t="n"/>
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="inlineStr">
         <is>
@@ -3595,13 +3608,13 @@
           <t>Khushi Kanabar</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="B19" s="13" t="n"/>
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/khushi-kanabar</t>
         </is>
       </c>
-      <c r="D19" s="3" t="n"/>
+      <c r="D19" s="12" t="n"/>
       <c r="E19" s="4" t="n"/>
       <c r="F19" s="4" t="inlineStr">
         <is>
@@ -3765,13 +3778,13 @@
           <t>Abhilas Das</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="B20" s="13" t="n"/>
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/abhilasrecruiter</t>
         </is>
       </c>
-      <c r="D20" s="3" t="n"/>
+      <c r="D20" s="12" t="n"/>
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="inlineStr">
         <is>
@@ -3935,13 +3948,13 @@
           <t>Siddhanth Singh</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="B21" s="13" t="n"/>
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/siddhanth-singh</t>
         </is>
       </c>
-      <c r="D21" s="3" t="n"/>
+      <c r="D21" s="12" t="n"/>
       <c r="E21" s="4" t="n"/>
       <c r="F21" s="4" t="inlineStr">
         <is>
@@ -4105,13 +4118,13 @@
           <t>Adesh Srivastava</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/adesh-srivastava-recruiting</t>
         </is>
       </c>
-      <c r="D22" s="3" t="n"/>
+      <c r="D22" s="12" t="n"/>
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="inlineStr">
         <is>
@@ -4275,13 +4288,13 @@
           <t>Ishita Kamani</t>
         </is>
       </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/ishitakamani</t>
         </is>
       </c>
-      <c r="D23" s="3" t="n"/>
+      <c r="D23" s="12" t="n"/>
       <c r="E23" s="4" t="n"/>
       <c r="F23" s="4" t="inlineStr">
         <is>
@@ -4449,13 +4462,13 @@
           <t>Mamta Uttamchandani</t>
         </is>
       </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="B24" s="13" t="n"/>
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/mamta-uttamchandani-77014b214</t>
         </is>
       </c>
-      <c r="D24" s="3" t="n"/>
+      <c r="D24" s="12" t="n"/>
       <c r="E24" s="4" t="n"/>
       <c r="F24" s="4" t="inlineStr">
         <is>
@@ -4619,13 +4632,13 @@
           <t>Divyanshi Chittora</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="B25" s="13" t="n"/>
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/divyanshi-chittora</t>
         </is>
       </c>
-      <c r="D25" s="3" t="n"/>
+      <c r="D25" s="12" t="n"/>
       <c r="E25" s="4" t="n"/>
       <c r="F25" s="4" t="inlineStr">
         <is>
@@ -4789,13 +4802,13 @@
           <t>Runali Joshi</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/runali-joshi-539266217</t>
         </is>
       </c>
-      <c r="D26" s="3" t="n"/>
+      <c r="D26" s="12" t="n"/>
       <c r="E26" s="4" t="n"/>
       <c r="F26" s="4" t="inlineStr">
         <is>
@@ -4949,13 +4962,13 @@
           <t>Shikha Singh</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="B27" s="13" t="n"/>
+      <c r="C27" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/shikha-singh</t>
         </is>
       </c>
-      <c r="D27" s="3" t="n"/>
+      <c r="D27" s="12" t="n"/>
       <c r="E27" s="4" t="n"/>
       <c r="F27" s="4" t="inlineStr">
         <is>
@@ -5119,13 +5132,13 @@
           <t>Urvashi Ghodke</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="B28" s="13" t="n"/>
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/urvashi-ghodke-8b9aa1189</t>
         </is>
       </c>
-      <c r="D28" s="3" t="n"/>
+      <c r="D28" s="12" t="n"/>
       <c r="E28" s="4" t="n"/>
       <c r="F28" s="4" t="inlineStr">
         <is>
@@ -5279,13 +5292,13 @@
           <t>Palak Shah</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="B29" s="13" t="n"/>
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/palak-shah</t>
         </is>
       </c>
-      <c r="D29" s="3" t="n"/>
+      <c r="D29" s="12" t="n"/>
       <c r="E29" s="4" t="n"/>
       <c r="F29" s="4" t="inlineStr">
         <is>
@@ -5449,13 +5462,13 @@
           <t>Dattul Patel</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="B30" s="13" t="n"/>
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/dattul-patel-89a7851a9</t>
         </is>
       </c>
-      <c r="D30" s="3" t="n"/>
+      <c r="D30" s="12" t="n"/>
       <c r="E30" s="4" t="n"/>
       <c r="F30" s="4" t="inlineStr">
         <is>
@@ -5619,13 +5632,13 @@
           <t>Nishi Acharya</t>
         </is>
       </c>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="B31" s="13" t="n"/>
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/nishi-acharya-a0536231a</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/talent/profile/AEMAAFDavSUBtSaqubyCfA_tmkCDmbzZeykrUfY</t>
         </is>
@@ -5793,13 +5806,13 @@
           <t>Yash Basrani</t>
         </is>
       </c>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="B32" s="13" t="n"/>
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/yash-basrani</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D32" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/talent/profile/AEMAACgF49EB8XLqrUdQ59SDFUXu5H9ijLU2Q10</t>
         </is>
@@ -5967,13 +5980,13 @@
           <t>Shubham Patel</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="B33" s="13" t="n"/>
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/shubham-patel-sap356427</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D33" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/talent/profile/AEMAADV7-rMBq5lTm7XaNLk68qrDTxeA7PVficc</t>
         </is>
@@ -6141,13 +6154,13 @@
           <t>Anupama B.</t>
         </is>
       </c>
-      <c r="B34" s="5" t="n"/>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="B34" s="13" t="n"/>
+      <c r="C34" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/anupamabartare</t>
         </is>
       </c>
-      <c r="D34" s="3" t="n"/>
+      <c r="D34" s="12" t="n"/>
       <c r="E34" s="4" t="n"/>
       <c r="F34" s="4" t="inlineStr">
         <is>
@@ -6311,13 +6324,13 @@
           <t>Yashodhara Parmar</t>
         </is>
       </c>
-      <c r="B35" s="5" t="n"/>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="B35" s="13" t="n"/>
+      <c r="C35" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/yashodharaparmar</t>
         </is>
       </c>
-      <c r="D35" s="3" t="n"/>
+      <c r="D35" s="12" t="n"/>
       <c r="E35" s="4" t="n"/>
       <c r="F35" s="4" t="inlineStr">
         <is>
@@ -6481,13 +6494,13 @@
           <t>Alnaz Pathan</t>
         </is>
       </c>
-      <c r="B36" s="5" t="n"/>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="B36" s="13" t="n"/>
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/alnaz-pathan-948423164</t>
         </is>
       </c>
-      <c r="D36" s="3" t="n"/>
+      <c r="D36" s="12" t="n"/>
       <c r="E36" s="4" t="n"/>
       <c r="F36" s="4" t="inlineStr">
         <is>
@@ -6653,13 +6666,13 @@
           <t>Apoorva Pandey</t>
         </is>
       </c>
-      <c r="B37" s="5" t="n"/>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="B37" s="13" t="n"/>
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/apoorva-pandey-5b168b19a</t>
         </is>
       </c>
-      <c r="D37" s="3" t="n"/>
+      <c r="D37" s="12" t="n"/>
       <c r="E37" s="4" t="n"/>
       <c r="F37" s="4" t="inlineStr">
         <is>
@@ -6823,13 +6836,13 @@
           <t>Ridham Jain</t>
         </is>
       </c>
-      <c r="B38" s="5" t="n"/>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="B38" s="13" t="n"/>
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/ridham-jain-227126300</t>
         </is>
       </c>
-      <c r="D38" s="3" t="n"/>
+      <c r="D38" s="12" t="n"/>
       <c r="E38" s="4" t="n"/>
       <c r="F38" s="4" t="inlineStr">
         <is>
@@ -6993,13 +7006,13 @@
           <t>Piyush Malviya</t>
         </is>
       </c>
-      <c r="B39" s="5" t="n"/>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="B39" s="13" t="n"/>
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/piyush-malviya-7a6382375</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D39" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/talent/profile/AEMAAFzIDe4BPucGq8TqheaFYhgboGOh8AJNlUw</t>
         </is>
@@ -7167,13 +7180,13 @@
           <t>Simran Kumari</t>
         </is>
       </c>
-      <c r="B40" s="5" t="n"/>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="B40" s="13" t="n"/>
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/simran-kumari-a29075200</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D40" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/talent/profile/AEMAADNEXoEBP8EfpTStSd8WZo0-a0Nc9XGC8wk</t>
         </is>
@@ -7341,13 +7354,13 @@
           <t>Biplov Sarkar</t>
         </is>
       </c>
-      <c r="B41" s="5" t="n"/>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="B41" s="13" t="n"/>
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/biplov-sarkar-693a9a157</t>
         </is>
       </c>
-      <c r="D41" s="3" t="n"/>
+      <c r="D41" s="12" t="n"/>
       <c r="E41" s="4" t="n"/>
       <c r="F41" s="4" t="inlineStr">
         <is>
@@ -7513,13 +7526,13 @@
           <t>Ambasi Bhavik</t>
         </is>
       </c>
-      <c r="B42" s="5" t="n"/>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="B42" s="13" t="n"/>
+      <c r="C42" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/ambasi-bhavik-943887214</t>
         </is>
       </c>
-      <c r="D42" s="3" t="n"/>
+      <c r="D42" s="12" t="n"/>
       <c r="E42" s="4" t="n"/>
       <c r="F42" s="4" t="inlineStr">
         <is>
@@ -7683,13 +7696,13 @@
           <t>Hetvi Shah</t>
         </is>
       </c>
-      <c r="B43" s="5" t="n"/>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="B43" s="13" t="n"/>
+      <c r="C43" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/hetvi-shah-4b2465276</t>
         </is>
       </c>
-      <c r="D43" s="3" t="n"/>
+      <c r="D43" s="12" t="n"/>
       <c r="E43" s="4" t="n"/>
       <c r="F43" s="4" t="inlineStr">
         <is>
@@ -7813,13 +7826,13 @@
           <t>Ayushi Thakor</t>
         </is>
       </c>
-      <c r="B44" s="5" t="n"/>
-      <c r="C44" s="6" t="inlineStr">
+      <c r="B44" s="13" t="n"/>
+      <c r="C44" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/ayushi-thakor-229857261/</t>
         </is>
       </c>
-      <c r="D44" s="3" t="n"/>
+      <c r="D44" s="12" t="n"/>
       <c r="E44" s="4" t="n"/>
       <c r="F44" s="4" t="inlineStr">
         <is>
@@ -7979,13 +7992,13 @@
           <t>Palak Joshi</t>
         </is>
       </c>
-      <c r="B45" s="5" t="n"/>
-      <c r="C45" s="6" t="inlineStr">
+      <c r="B45" s="13" t="n"/>
+      <c r="C45" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/palak-joshi-065b7a18b</t>
         </is>
       </c>
-      <c r="D45" s="3" t="n"/>
+      <c r="D45" s="12" t="n"/>
       <c r="E45" s="4" t="n"/>
       <c r="F45" s="4" t="inlineStr">
         <is>
@@ -8149,13 +8162,13 @@
           <t>Chirag Goyal</t>
         </is>
       </c>
-      <c r="B46" s="5" t="n"/>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="B46" s="13" t="n"/>
+      <c r="C46" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/chirag-goyal-891b7918b</t>
         </is>
       </c>
-      <c r="D46" s="3" t="n"/>
+      <c r="D46" s="12" t="n"/>
       <c r="E46" s="4" t="n"/>
       <c r="F46" s="4" t="inlineStr">
         <is>
@@ -8315,13 +8328,13 @@
           <t>Akil Kumbhar</t>
         </is>
       </c>
-      <c r="B47" s="5" t="n"/>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="B47" s="13" t="n"/>
+      <c r="C47" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/akil-kumbhar-2046b9252</t>
         </is>
       </c>
-      <c r="D47" s="3" t="n"/>
+      <c r="D47" s="12" t="n"/>
       <c r="E47" s="4" t="n"/>
       <c r="F47" s="4" t="inlineStr">
         <is>
@@ -8485,13 +8498,13 @@
           <t>Anushree Banerjee</t>
         </is>
       </c>
-      <c r="B48" s="5" t="n"/>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="B48" s="13" t="n"/>
+      <c r="C48" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/anushree-banerjee-445595195</t>
         </is>
       </c>
-      <c r="D48" s="3" t="n"/>
+      <c r="D48" s="12" t="n"/>
       <c r="E48" s="4" t="n"/>
       <c r="F48" s="4" t="inlineStr">
         <is>
@@ -8655,13 +8668,13 @@
           <t>Princy Gosaliya</t>
         </is>
       </c>
-      <c r="B49" s="5" t="n"/>
-      <c r="C49" s="6" t="inlineStr">
+      <c r="B49" s="13" t="n"/>
+      <c r="C49" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/princy-gosaliya-1a1b91181</t>
         </is>
       </c>
-      <c r="D49" s="3" t="n"/>
+      <c r="D49" s="12" t="n"/>
       <c r="E49" s="4" t="n"/>
       <c r="F49" s="4" t="inlineStr">
         <is>
@@ -8825,13 +8838,13 @@
           <t>Swati Kothari</t>
         </is>
       </c>
-      <c r="B50" s="5" t="n"/>
-      <c r="C50" s="6" t="inlineStr">
+      <c r="B50" s="13" t="n"/>
+      <c r="C50" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/swati-kothari-908791183</t>
         </is>
       </c>
-      <c r="D50" s="3" t="n"/>
+      <c r="D50" s="12" t="n"/>
       <c r="E50" s="4" t="n"/>
       <c r="F50" s="4" t="inlineStr">
         <is>
@@ -8955,13 +8968,13 @@
           <t>Aastha Bhadani</t>
         </is>
       </c>
-      <c r="B51" s="5" t="n"/>
-      <c r="C51" s="6" t="inlineStr">
+      <c r="B51" s="13" t="n"/>
+      <c r="C51" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/aastha-bhadani-57a536161</t>
         </is>
       </c>
-      <c r="D51" s="3" t="n"/>
+      <c r="D51" s="12" t="n"/>
       <c r="E51" s="4" t="n"/>
       <c r="F51" s="4" t="inlineStr">
         <is>
@@ -9129,13 +9142,13 @@
           <t>Himanshi Kothari</t>
         </is>
       </c>
-      <c r="B52" s="5" t="n"/>
-      <c r="C52" s="6" t="inlineStr">
+      <c r="B52" s="13" t="n"/>
+      <c r="C52" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/himanshi-kothari</t>
         </is>
       </c>
-      <c r="D52" s="3" t="n"/>
+      <c r="D52" s="12" t="n"/>
       <c r="E52" s="4" t="n"/>
       <c r="F52" s="4" t="inlineStr">
         <is>
@@ -9263,13 +9276,13 @@
           <t>HARDIK MATHUR</t>
         </is>
       </c>
-      <c r="B53" s="5" t="n"/>
-      <c r="C53" s="6" t="inlineStr">
+      <c r="B53" s="13" t="n"/>
+      <c r="C53" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/hardik-mathur-660169185</t>
         </is>
       </c>
-      <c r="D53" s="3" t="n"/>
+      <c r="D53" s="12" t="n"/>
       <c r="E53" s="4" t="n"/>
       <c r="F53" s="4" t="inlineStr">
         <is>
@@ -9393,13 +9406,13 @@
           <t>Vidhi Shah</t>
         </is>
       </c>
-      <c r="B54" s="5" t="n"/>
-      <c r="C54" s="6" t="inlineStr">
+      <c r="B54" s="13" t="n"/>
+      <c r="C54" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/vidhi-shah-9909b9215</t>
         </is>
       </c>
-      <c r="D54" s="3" t="n"/>
+      <c r="D54" s="12" t="n"/>
       <c r="E54" s="4" t="n"/>
       <c r="F54" s="4" t="inlineStr">
         <is>
@@ -9559,13 +9572,13 @@
           <t>Kavin Patel</t>
         </is>
       </c>
-      <c r="B55" s="5" t="n"/>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="B55" s="13" t="n"/>
+      <c r="C55" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/kavinpatel0411</t>
         </is>
       </c>
-      <c r="D55" s="3" t="n"/>
+      <c r="D55" s="12" t="n"/>
       <c r="E55" s="4" t="n"/>
       <c r="F55" s="4" t="inlineStr">
         <is>
@@ -9729,13 +9742,13 @@
           <t>Jaipal singh Tanwar</t>
         </is>
       </c>
-      <c r="B56" s="5" t="n"/>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="B56" s="13" t="n"/>
+      <c r="C56" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/jaipal-singh-tanwar-1813261b1</t>
         </is>
       </c>
-      <c r="D56" s="3" t="n"/>
+      <c r="D56" s="12" t="n"/>
       <c r="E56" s="4" t="n"/>
       <c r="F56" s="4" t="inlineStr">
         <is>
@@ -9895,13 +9908,13 @@
           <t>Jaimin Panchal</t>
         </is>
       </c>
-      <c r="B57" s="5" t="n"/>
-      <c r="C57" s="6" t="inlineStr">
+      <c r="B57" s="13" t="n"/>
+      <c r="C57" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/jaimin-panchal</t>
         </is>
       </c>
-      <c r="D57" s="3" t="n"/>
+      <c r="D57" s="12" t="n"/>
       <c r="E57" s="4" t="n"/>
       <c r="F57" s="4" t="inlineStr">
         <is>
@@ -10065,13 +10078,13 @@
           <t>Mukul Mahor</t>
         </is>
       </c>
-      <c r="B58" s="5" t="n"/>
-      <c r="C58" s="6" t="inlineStr">
+      <c r="B58" s="13" t="n"/>
+      <c r="C58" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/mukul-mahor-258b2726b</t>
         </is>
       </c>
-      <c r="D58" s="3" t="n"/>
+      <c r="D58" s="12" t="n"/>
       <c r="E58" s="4" t="n"/>
       <c r="F58" s="4" t="inlineStr">
         <is>
@@ -10235,13 +10248,13 @@
           <t>Rupali Kumari</t>
         </is>
       </c>
-      <c r="B59" s="5" t="n"/>
-      <c r="C59" s="6" t="inlineStr">
+      <c r="B59" s="13" t="n"/>
+      <c r="C59" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/rupali-kumari-075b8b32b</t>
         </is>
       </c>
-      <c r="D59" s="3" t="n"/>
+      <c r="D59" s="12" t="n"/>
       <c r="E59" s="4" t="n"/>
       <c r="F59" s="4" t="inlineStr">
         <is>
@@ -10401,13 +10414,13 @@
           <t>Ronak Laddha</t>
         </is>
       </c>
-      <c r="B60" s="5" t="n"/>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="B60" s="13" t="n"/>
+      <c r="C60" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/ronak-laddha-153339a8</t>
         </is>
       </c>
-      <c r="D60" s="3" t="n"/>
+      <c r="D60" s="12" t="n"/>
       <c r="E60" s="4" t="n"/>
       <c r="F60" s="4" t="inlineStr">
         <is>
@@ -10574,13 +10587,13 @@
           <t>Rashmi Makhija</t>
         </is>
       </c>
-      <c r="B61" s="5" t="n"/>
-      <c r="C61" s="6" t="inlineStr">
+      <c r="B61" s="13" t="n"/>
+      <c r="C61" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/rashmi-makhija-53a33b2a2</t>
         </is>
       </c>
-      <c r="D61" s="3" t="n"/>
+      <c r="D61" s="12" t="n"/>
       <c r="E61" s="4" t="n"/>
       <c r="F61" s="4" t="inlineStr">
         <is>
@@ -10744,13 +10757,13 @@
           <t>Krupa Patel</t>
         </is>
       </c>
-      <c r="B62" s="5" t="n"/>
-      <c r="C62" s="6" t="inlineStr">
+      <c r="B62" s="13" t="n"/>
+      <c r="C62" s="11" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/krupa-patel</t>
         </is>
       </c>
-      <c r="D62" s="3" t="n"/>
+      <c r="D62" s="12" t="n"/>
       <c r="E62" s="4" t="n"/>
       <c r="F62" s="4" t="inlineStr">
         <is>
@@ -10874,13 +10887,13 @@
           <t>Axn Sadokpam</t>
         </is>
       </c>
-      <c r="B63" s="5" t="n"/>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="B63" s="13" t="n"/>
+      <c r="C63" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/theaxnsadokpam</t>
         </is>
       </c>
-      <c r="D63" s="3" t="n"/>
+      <c r="D63" s="12" t="n"/>
       <c r="E63" s="7" t="n"/>
       <c r="F63" s="7" t="inlineStr">
         <is>
@@ -11056,13 +11069,13 @@
           <t>Anisa Shaikh</t>
         </is>
       </c>
-      <c r="B64" s="5" t="n"/>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="B64" s="13" t="n"/>
+      <c r="C64" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/anisa-shaikh-25383123b</t>
         </is>
       </c>
-      <c r="D64" s="3" t="n"/>
+      <c r="D64" s="12" t="n"/>
       <c r="E64" s="7" t="n"/>
       <c r="F64" s="7" t="inlineStr">
         <is>
@@ -11242,13 +11255,13 @@
           <t>Sejoti Banik</t>
         </is>
       </c>
-      <c r="B65" s="5" t="n"/>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="B65" s="13" t="n"/>
+      <c r="C65" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/sejoti-banik-0694b1142</t>
         </is>
       </c>
-      <c r="D65" s="3" t="n"/>
+      <c r="D65" s="12" t="n"/>
       <c r="E65" s="7" t="n"/>
       <c r="F65" s="7" t="inlineStr">
         <is>
@@ -11407,13 +11420,13 @@
           <t>Meera Thanki</t>
         </is>
       </c>
-      <c r="B66" s="5" t="n"/>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="B66" s="13" t="n"/>
+      <c r="C66" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/meera-thanki-7a6b5c2d</t>
         </is>
       </c>
-      <c r="D66" s="3" t="n"/>
+      <c r="D66" s="12" t="n"/>
       <c r="E66" s="7" t="n"/>
       <c r="F66" s="7" t="inlineStr">
         <is>
@@ -11597,13 +11610,13 @@
           <t>Bhatt N.</t>
         </is>
       </c>
-      <c r="B67" s="5" t="n"/>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="B67" s="13" t="n"/>
+      <c r="C67" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/bhatt-n-388814119</t>
         </is>
       </c>
-      <c r="D67" s="5" t="inlineStr">
+      <c r="D67" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/talent/profile/AEMAAB18nhgBQ9hq0-a0IP11JhtlykeCfdTdcMY?project=1894950466&amp;searchHistoryId=20810676818</t>
         </is>
@@ -11765,13 +11778,13 @@
           <t>Manoo P.</t>
         </is>
       </c>
-      <c r="B68" s="5" t="n"/>
-      <c r="C68" s="7" t="inlineStr">
+      <c r="B68" s="13" t="n"/>
+      <c r="C68" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/manoo-p-317639252</t>
         </is>
       </c>
-      <c r="D68" s="7" t="inlineStr">
+      <c r="D68" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/talent/profile/AEMAAD5i2YMBv9NGff_NLe2pY9gy4X-6oBrzsrI?project=1894950466&amp;searchHistoryId=20810676818</t>
         </is>
@@ -11959,13 +11972,13 @@
           <t>Stanley Buwa</t>
         </is>
       </c>
-      <c r="B69" s="5" t="n"/>
-      <c r="C69" s="7" t="inlineStr">
+      <c r="B69" s="13" t="n"/>
+      <c r="C69" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/saurabh-buwa</t>
         </is>
       </c>
-      <c r="D69" s="7" t="inlineStr">
+      <c r="D69" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/talent/profile/AEMAADPFWXUBpKM1dvBUBpOPygmKElV3e_4scIA?project=1894950466</t>
         </is>
@@ -12113,9 +12126,9 @@
           <t>Dhara Bharadiya</t>
         </is>
       </c>
-      <c r="B70" s="5" t="n"/>
-      <c r="C70" s="7" t="n"/>
-      <c r="D70" s="7" t="inlineStr">
+      <c r="B70" s="13" t="n"/>
+      <c r="C70" s="13" t="n"/>
+      <c r="D70" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/dharabharadiya/</t>
         </is>
@@ -12275,9 +12288,9 @@
           <t>Lincy T Abey</t>
         </is>
       </c>
-      <c r="B71" s="5" t="n"/>
-      <c r="C71" s="7" t="n"/>
-      <c r="D71" s="7" t="n"/>
+      <c r="B71" s="13" t="n"/>
+      <c r="C71" s="13" t="n"/>
+      <c r="D71" s="13" t="n"/>
       <c r="E71" s="7" t="n"/>
       <c r="F71" s="7" t="inlineStr">
         <is>
@@ -12417,9 +12430,9 @@
           <t>Kalpit Patel</t>
         </is>
       </c>
-      <c r="B72" s="5" t="n"/>
-      <c r="C72" s="7" t="n"/>
-      <c r="D72" s="7" t="inlineStr">
+      <c r="B72" s="13" t="n"/>
+      <c r="C72" s="13" t="n"/>
+      <c r="D72" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/patelkalpit</t>
         </is>
@@ -12608,13 +12621,13 @@
           <t>Priyanka Songara</t>
         </is>
       </c>
-      <c r="B73" s="5" t="n"/>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="B73" s="13" t="n"/>
+      <c r="C73" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/priyanka-songara-67b0401b9</t>
         </is>
       </c>
-      <c r="D73" s="3" t="n"/>
+      <c r="D73" s="12" t="n"/>
       <c r="E73" s="7" t="n"/>
       <c r="F73" s="7" t="inlineStr">
         <is>
@@ -12794,13 +12807,13 @@
           <t>Rajat Gupta</t>
         </is>
       </c>
-      <c r="B74" s="5" t="n"/>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="B74" s="13" t="n"/>
+      <c r="C74" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/rajatgupta0508</t>
         </is>
       </c>
-      <c r="D74" s="3" t="n"/>
+      <c r="D74" s="12" t="n"/>
       <c r="E74" s="7" t="n"/>
       <c r="F74" s="7" t="inlineStr">
         <is>
@@ -12940,9 +12953,9 @@
           <t>Dhruvi Shah</t>
         </is>
       </c>
-      <c r="B75" s="5" t="n"/>
-      <c r="C75" s="5" t="n"/>
-      <c r="D75" s="3" t="n"/>
+      <c r="B75" s="13" t="n"/>
+      <c r="C75" s="13" t="n"/>
+      <c r="D75" s="12" t="n"/>
       <c r="E75" s="7" t="n"/>
       <c r="F75" s="7" t="inlineStr">
         <is>
@@ -13126,13 +13139,13 @@
           <t>Jay Milak</t>
         </is>
       </c>
-      <c r="B76" s="5" t="n"/>
-      <c r="C76" s="5" t="inlineStr">
+      <c r="B76" s="13" t="n"/>
+      <c r="C76" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/connectwithjaymilak</t>
         </is>
       </c>
-      <c r="D76" s="3" t="n"/>
+      <c r="D76" s="12" t="n"/>
       <c r="E76" s="7" t="n"/>
       <c r="F76" s="7" t="inlineStr">
         <is>
@@ -13272,13 +13285,13 @@
           <t>Yasham M.</t>
         </is>
       </c>
-      <c r="B77" s="5" t="n"/>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="B77" s="13" t="n"/>
+      <c r="C77" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/yashamm</t>
         </is>
       </c>
-      <c r="D77" s="3" t="n"/>
+      <c r="D77" s="12" t="n"/>
       <c r="E77" s="7" t="n"/>
       <c r="F77" s="7" t="inlineStr">
         <is>
@@ -13462,13 +13475,13 @@
           <t>Devanshi Thakkar</t>
         </is>
       </c>
-      <c r="B78" s="5" t="n"/>
-      <c r="C78" s="5" t="inlineStr">
+      <c r="B78" s="13" t="n"/>
+      <c r="C78" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/devanshi-thakkar-296661291</t>
         </is>
       </c>
-      <c r="D78" s="3" t="n"/>
+      <c r="D78" s="12" t="n"/>
       <c r="E78" s="7" t="n"/>
       <c r="F78" s="7" t="inlineStr">
         <is>
@@ -13652,13 +13665,13 @@
           <t>Bharti Meena</t>
         </is>
       </c>
-      <c r="B79" s="5" t="n"/>
-      <c r="C79" s="5" t="inlineStr">
+      <c r="B79" s="13" t="n"/>
+      <c r="C79" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/bharti-meena-2507381b4</t>
         </is>
       </c>
-      <c r="D79" s="3" t="n"/>
+      <c r="D79" s="12" t="n"/>
       <c r="E79" s="7" t="n"/>
       <c r="F79" s="7" t="inlineStr">
         <is>
@@ -13823,13 +13836,13 @@
           <t>Siddhant Gaikwad</t>
         </is>
       </c>
-      <c r="B80" s="5" t="n"/>
-      <c r="C80" s="5" t="inlineStr">
+      <c r="B80" s="13" t="n"/>
+      <c r="C80" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/siddhant-gaikwad-828b23186</t>
         </is>
       </c>
-      <c r="D80" s="3" t="n"/>
+      <c r="D80" s="12" t="n"/>
       <c r="E80" s="7" t="n"/>
       <c r="F80" s="7" t="inlineStr">
         <is>
@@ -14009,13 +14022,13 @@
           <t>Kapil Solanki</t>
         </is>
       </c>
-      <c r="B81" s="5" t="n"/>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="B81" s="13" t="n"/>
+      <c r="C81" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/kapil-solanki-91259817b</t>
         </is>
       </c>
-      <c r="D81" s="3" t="n"/>
+      <c r="D81" s="12" t="n"/>
       <c r="E81" s="7" t="n"/>
       <c r="F81" s="7" t="inlineStr">
         <is>
@@ -14159,13 +14172,13 @@
           <t>Sarthak (Sam) Choudhury</t>
         </is>
       </c>
-      <c r="B82" s="5" t="n"/>
-      <c r="C82" s="5" t="inlineStr">
+      <c r="B82" s="13" t="n"/>
+      <c r="C82" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/sarthak-sam-choudhury-80918a23b</t>
         </is>
       </c>
-      <c r="D82" s="3" t="n"/>
+      <c r="D82" s="12" t="n"/>
       <c r="E82" s="7" t="n"/>
       <c r="F82" s="7" t="inlineStr">
         <is>
@@ -14309,13 +14322,13 @@
           <t>Keya Thakkar</t>
         </is>
       </c>
-      <c r="B83" s="5" t="n"/>
-      <c r="C83" s="5" t="inlineStr">
+      <c r="B83" s="13" t="n"/>
+      <c r="C83" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/keya-thakkar-33794b179</t>
         </is>
       </c>
-      <c r="D83" s="3" t="n"/>
+      <c r="D83" s="12" t="n"/>
       <c r="E83" s="7" t="n"/>
       <c r="F83" s="7" t="inlineStr">
         <is>
@@ -14455,13 +14468,13 @@
           <t>Reena Khatri</t>
         </is>
       </c>
-      <c r="B84" s="5" t="n"/>
-      <c r="C84" s="5" t="inlineStr">
+      <c r="B84" s="13" t="n"/>
+      <c r="C84" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/reena-khatri-75986a19b</t>
         </is>
       </c>
-      <c r="D84" s="3" t="n"/>
+      <c r="D84" s="12" t="n"/>
       <c r="E84" s="7" t="n"/>
       <c r="F84" s="7" t="inlineStr">
         <is>
@@ -14601,13 +14614,13 @@
           <t>Vrunda P</t>
         </is>
       </c>
-      <c r="B85" s="5" t="n"/>
-      <c r="C85" s="5" t="inlineStr">
+      <c r="B85" s="13" t="n"/>
+      <c r="C85" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/vrundaparikh</t>
         </is>
       </c>
-      <c r="D85" s="3" t="n"/>
+      <c r="D85" s="12" t="n"/>
       <c r="E85" s="7" t="n"/>
       <c r="F85" s="7" t="inlineStr">
         <is>
@@ -14789,13 +14802,13 @@
           <t>Vidit Mishra</t>
         </is>
       </c>
-      <c r="B86" s="5" t="n"/>
-      <c r="C86" s="5" t="inlineStr">
+      <c r="B86" s="13" t="n"/>
+      <c r="C86" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/vidit-mishra</t>
         </is>
       </c>
-      <c r="D86" s="3" t="n"/>
+      <c r="D86" s="12" t="n"/>
       <c r="E86" s="7" t="n"/>
       <c r="F86" s="7" t="inlineStr">
         <is>
@@ -14943,13 +14956,13 @@
           <t>Bhargav Purabiya</t>
         </is>
       </c>
-      <c r="B87" s="5" t="n"/>
-      <c r="C87" s="5" t="inlineStr">
+      <c r="B87" s="13" t="n"/>
+      <c r="C87" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/bhargav-purabiya-548ab2243</t>
         </is>
       </c>
-      <c r="D87" s="3" t="n"/>
+      <c r="D87" s="12" t="n"/>
       <c r="E87" s="7" t="n"/>
       <c r="F87" s="7" t="inlineStr">
         <is>
@@ -15101,13 +15114,13 @@
           <t>Maharshi Panchal</t>
         </is>
       </c>
-      <c r="B88" s="5" t="n"/>
-      <c r="C88" s="5" t="inlineStr">
+      <c r="B88" s="13" t="n"/>
+      <c r="C88" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/maharshi-panchal-30759a27a</t>
         </is>
       </c>
-      <c r="D88" s="3" t="n"/>
+      <c r="D88" s="12" t="n"/>
       <c r="E88" s="7" t="n"/>
       <c r="F88" s="7" t="inlineStr">
         <is>
@@ -15283,13 +15296,13 @@
           <t>Himanshu Bhadoriya</t>
         </is>
       </c>
-      <c r="B89" s="5" t="n"/>
-      <c r="C89" s="5" t="inlineStr">
+      <c r="B89" s="13" t="n"/>
+      <c r="C89" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/himanshubhadoriya</t>
         </is>
       </c>
-      <c r="D89" s="3" t="n"/>
+      <c r="D89" s="12" t="n"/>
       <c r="E89" s="7" t="n"/>
       <c r="F89" s="7" t="inlineStr">
         <is>
@@ -15473,13 +15486,13 @@
           <t>Riya Gaur</t>
         </is>
       </c>
-      <c r="B90" s="5" t="n"/>
-      <c r="C90" s="5" t="inlineStr">
+      <c r="B90" s="13" t="n"/>
+      <c r="C90" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/riya-gaur-b50546217</t>
         </is>
       </c>
-      <c r="D90" s="3" t="n"/>
+      <c r="D90" s="12" t="n"/>
       <c r="E90" s="7" t="n"/>
       <c r="F90" s="7" t="inlineStr">
         <is>
@@ -15664,13 +15677,13 @@
           <t>Rahul Sharma</t>
         </is>
       </c>
-      <c r="B91" s="5" t="n"/>
-      <c r="C91" s="5" t="inlineStr">
+      <c r="B91" s="13" t="n"/>
+      <c r="C91" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/rahul-sharma-b50546217</t>
         </is>
       </c>
-      <c r="D91" s="3" t="n"/>
+      <c r="D91" s="12" t="n"/>
       <c r="E91" s="7" t="n"/>
       <c r="F91" s="7" t="inlineStr">
         <is>
@@ -15838,7 +15851,7 @@
           <t>All recruiting roles at staffing/recruiting agencies (Surekha Technologies, Tridhya Tech, HireWay Consulting). No in-house recruiting coordinator experience at product company.</t>
         </is>
       </c>
-      <c r="AN91" s="3" t="inlineStr">
+      <c r="AN91" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -15850,13 +15863,13 @@
           <t>Aarti Ranglani</t>
         </is>
       </c>
-      <c r="B92" s="5" t="n"/>
-      <c r="C92" s="7" t="inlineStr">
+      <c r="B92" s="13" t="n"/>
+      <c r="C92" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/aarti-ranglani-10447b251</t>
         </is>
       </c>
-      <c r="D92" s="7" t="n"/>
+      <c r="D92" s="13" t="n"/>
       <c r="E92" s="7" t="n"/>
       <c r="F92" s="7" t="inlineStr">
         <is>
@@ -15982,13 +15995,13 @@
           <t>Helly Shah</t>
         </is>
       </c>
-      <c r="B93" s="5" t="n"/>
-      <c r="C93" s="7" t="inlineStr">
+      <c r="B93" s="13" t="n"/>
+      <c r="C93" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/helly-shah-7a55b2222</t>
         </is>
       </c>
-      <c r="D93" s="7" t="inlineStr">
+      <c r="D93" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/talent/profile/AEMAADf5KO0Bkyy5PJX_mx2zQllj-Ls7KyxTfdA?project=1894950466</t>
         </is>
@@ -16135,7 +16148,7 @@
           <t>Associate TA title (not coordinator); no high-volume metrics; zero Sales hiring experience; recent Adani role (traditional conglomerate) concerning; no ATS/Greenhouse experience; no US exposure</t>
         </is>
       </c>
-      <c r="AN93" s="3" t="inlineStr">
+      <c r="AN93" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -16147,13 +16160,13 @@
           <t>Jayesh Sunilkumar</t>
         </is>
       </c>
-      <c r="B94" s="5" t="n"/>
-      <c r="C94" s="7" t="inlineStr">
+      <c r="B94" s="13" t="n"/>
+      <c r="C94" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/jayeshsunilkumar</t>
         </is>
       </c>
-      <c r="D94" s="7" t="n"/>
+      <c r="D94" s="13" t="n"/>
       <c r="E94" s="7" t="n"/>
       <c r="F94" s="7" t="inlineStr">
         <is>
@@ -16234,8 +16247,8 @@
         </is>
       </c>
       <c r="AL94" s="7" t="n"/>
-      <c r="AM94" s="3" t="n"/>
-      <c r="AN94" s="3" t="inlineStr">
+      <c r="AM94" s="12" t="n"/>
+      <c r="AN94" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -16247,9 +16260,9 @@
           <t>Nitin M.</t>
         </is>
       </c>
-      <c r="B95" s="5" t="n"/>
-      <c r="C95" s="7" t="n"/>
-      <c r="D95" s="7" t="n"/>
+      <c r="B95" s="13" t="n"/>
+      <c r="C95" s="13" t="n"/>
+      <c r="D95" s="13" t="n"/>
       <c r="E95" s="7" t="n"/>
       <c r="F95" s="7" t="inlineStr">
         <is>
@@ -16381,7 +16394,7 @@
           <t>No clear SaaS company background; all roles at staffing/recruitment agencies or unknown companies</t>
         </is>
       </c>
-      <c r="AN95" s="3" t="inlineStr">
+      <c r="AN95" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -16393,13 +16406,13 @@
           <t>Shephali Srivastava</t>
         </is>
       </c>
-      <c r="B96" s="5" t="n"/>
-      <c r="C96" s="7" t="inlineStr">
+      <c r="B96" s="13" t="n"/>
+      <c r="C96" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/shephali-srivastava-9b98b9180</t>
         </is>
       </c>
-      <c r="D96" s="7" t="inlineStr">
+      <c r="D96" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/talent/profile/AEMAACrZHV0B3SjwDhURtJ0enDVmz6JwhmdTAco?project=1894950466&amp;searchHistoryId=20810676818</t>
         </is>
@@ -16588,13 +16601,13 @@
           <t>Suman Kumari</t>
         </is>
       </c>
-      <c r="B97" s="5" t="n"/>
-      <c r="C97" s="7" t="inlineStr">
+      <c r="B97" s="13" t="n"/>
+      <c r="C97" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/suman-kumari-682450220</t>
         </is>
       </c>
-      <c r="D97" s="7" t="n"/>
+      <c r="D97" s="13" t="n"/>
       <c r="E97" s="7" t="n"/>
       <c r="F97" s="7" t="inlineStr">
         <is>
@@ -16777,13 +16790,13 @@
           <t>Harsh Bhatt</t>
         </is>
       </c>
-      <c r="B98" s="5" t="n"/>
-      <c r="C98" s="7" t="inlineStr">
+      <c r="B98" s="13" t="n"/>
+      <c r="C98" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/harsh-bhatt-3515a51b3</t>
         </is>
       </c>
-      <c r="D98" s="7" t="n"/>
+      <c r="D98" s="13" t="n"/>
       <c r="E98" s="7" t="n"/>
       <c r="F98" s="7" t="inlineStr">
         <is>
@@ -16951,7 +16964,7 @@
           <t>Entire career at staffing agencies (IMS People Possible, Shivansh Outsourcing). Pharma/life science recruiting is non-SaaS. No in-house recruiting coordination experience.</t>
         </is>
       </c>
-      <c r="AN98" s="3" t="inlineStr">
+      <c r="AN98" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -16963,13 +16976,13 @@
           <t>Shivani Shah</t>
         </is>
       </c>
-      <c r="B99" s="5" t="n"/>
-      <c r="C99" s="7" t="inlineStr">
+      <c r="B99" s="13" t="n"/>
+      <c r="C99" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/shivani-shah-95b683158</t>
         </is>
       </c>
-      <c r="D99" s="7" t="n"/>
+      <c r="D99" s="13" t="n"/>
       <c r="E99" s="7" t="n"/>
       <c r="F99" s="7" t="inlineStr">
         <is>
@@ -17137,7 +17150,7 @@
           <t>Career limited to staffing/recruiting agencies and in-house HR ops. No SaaS product company experience.</t>
         </is>
       </c>
-      <c r="AN99" s="3" t="inlineStr">
+      <c r="AN99" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -17149,13 +17162,13 @@
           <t>Kamakshi Mishra</t>
         </is>
       </c>
-      <c r="B100" s="5" t="n"/>
-      <c r="C100" s="7" t="inlineStr">
+      <c r="B100" s="13" t="n"/>
+      <c r="C100" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/kamakshi-mishra-60873420b</t>
         </is>
       </c>
-      <c r="D100" s="7" t="n"/>
+      <c r="D100" s="13" t="n"/>
       <c r="E100" s="7" t="n"/>
       <c r="F100" s="7" t="inlineStr">
         <is>
@@ -17283,7 +17296,7 @@
       </c>
       <c r="AL100" s="7" t="n"/>
       <c r="AM100" s="7" t="n"/>
-      <c r="AN100" s="3" t="inlineStr">
+      <c r="AN100" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -17295,13 +17308,13 @@
           <t>Zeel Bhavsar</t>
         </is>
       </c>
-      <c r="B101" s="5" t="n"/>
-      <c r="C101" s="7" t="inlineStr">
+      <c r="B101" s="13" t="n"/>
+      <c r="C101" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/zeel-bhavsar-519b9422b</t>
         </is>
       </c>
-      <c r="D101" s="7" t="n"/>
+      <c r="D101" s="13" t="n"/>
       <c r="E101" s="7" t="n"/>
       <c r="F101" s="7" t="inlineStr">
         <is>
@@ -17429,7 +17442,7 @@
       </c>
       <c r="AL101" s="7" t="n"/>
       <c r="AM101" s="7" t="n"/>
-      <c r="AN101" s="3" t="inlineStr">
+      <c r="AN101" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -17441,9 +17454,9 @@
           <t>Dimple Tiwari</t>
         </is>
       </c>
-      <c r="B102" s="5" t="n"/>
-      <c r="C102" s="7" t="n"/>
-      <c r="D102" s="7" t="inlineStr">
+      <c r="B102" s="13" t="n"/>
+      <c r="C102" s="13" t="n"/>
+      <c r="D102" s="13" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/dimple-tiwari-29034618a</t>
         </is>
@@ -17631,12 +17644,12 @@
         </is>
       </c>
       <c r="B103" s="8" t="inlineStr"/>
-      <c r="C103" s="8" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/parashah</t>
         </is>
       </c>
-      <c r="D103" s="8" t="inlineStr">
+      <c r="D103" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/talent/profile/AEMAAB_w53kBJjUA4mGrVR4OZYVK_EGxxZehRIA</t>
         </is>
@@ -17791,12 +17804,12 @@
         </is>
       </c>
       <c r="B104" s="8" t="inlineStr"/>
-      <c r="C104" s="8" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/anamika-pandit-157883157</t>
         </is>
       </c>
-      <c r="D104" s="8" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>Senior Talent Acquisition Specialist</t>
         </is>
@@ -17906,12 +17919,12 @@
         </is>
       </c>
       <c r="B105" s="8" t="inlineStr"/>
-      <c r="C105" s="8" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/iramben-saumil-virani-23110a21b</t>
         </is>
       </c>
-      <c r="D105" s="8" t="inlineStr">
+      <c r="D105" t="inlineStr">
         <is>
           <t>Recruiter / US Recruiter</t>
         </is>
@@ -18069,12 +18082,12 @@
         </is>
       </c>
       <c r="B106" s="8" t="inlineStr"/>
-      <c r="C106" s="8" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/yashrajsolanki</t>
         </is>
       </c>
-      <c r="D106" s="8" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>MSP Delivery Manager (North America)</t>
         </is>
@@ -18188,8 +18201,6 @@
         </is>
       </c>
       <c r="B107" s="8" t="inlineStr"/>
-      <c r="C107" s="8" t="inlineStr"/>
-      <c r="D107" s="8" t="inlineStr"/>
       <c r="E107" s="8" t="n"/>
       <c r="F107" s="8" t="n"/>
       <c r="G107" s="8" t="n"/>
@@ -18291,12 +18302,12 @@
         </is>
       </c>
       <c r="B108" s="8" t="inlineStr"/>
-      <c r="C108" s="8" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/dhwani-saija-349466188</t>
         </is>
       </c>
-      <c r="D108" s="8" t="inlineStr">
+      <c r="D108" t="inlineStr">
         <is>
           <t>Sr Talent Acquisition &amp; Partner</t>
         </is>
@@ -18408,12 +18419,12 @@
         </is>
       </c>
       <c r="B109" s="8" t="inlineStr"/>
-      <c r="C109" s="8" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/roger-sequeira-01583424</t>
         </is>
       </c>
-      <c r="D109" s="8" t="inlineStr">
+      <c r="D109" t="inlineStr">
         <is>
           <t>Sr. Talent Acquisition</t>
         </is>
@@ -18539,12 +18550,12 @@
         </is>
       </c>
       <c r="B110" s="8" t="inlineStr"/>
-      <c r="C110" s="8" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/manasha-ranjan-5a7ba2193</t>
         </is>
       </c>
-      <c r="D110" s="8" t="inlineStr">
+      <c r="D110" t="inlineStr">
         <is>
           <t>HR Business Partner</t>
         </is>
@@ -18705,12 +18716,12 @@
         </is>
       </c>
       <c r="B111" s="8" t="inlineStr"/>
-      <c r="C111" s="8" t="inlineStr">
+      <c r="C111" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/prachi-parmar</t>
         </is>
       </c>
-      <c r="D111" s="8" t="inlineStr">
+      <c r="D111" t="inlineStr">
         <is>
           <t>HR Manager</t>
         </is>
@@ -18865,12 +18876,12 @@
         </is>
       </c>
       <c r="B112" s="8" t="inlineStr"/>
-      <c r="C112" s="8" t="inlineStr">
+      <c r="C112" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/bhagyashreejoglekar-18772b238/</t>
         </is>
       </c>
-      <c r="D112" s="8" t="inlineStr">
+      <c r="D112" t="inlineStr">
         <is>
           <t>Human Resources Executive</t>
         </is>
@@ -19014,6 +19025,1721 @@
         </is>
       </c>
       <c r="AM112" s="8" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="8" t="inlineStr">
+        <is>
+          <t>Shefali Patel</t>
+        </is>
+      </c>
+      <c r="B113" s="8" t="inlineStr"/>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shefali-patel-935ba940</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/talent/profile/AEMAAAi4L_kB6cxL2O-oTDhqSCjwEJESFTD5ZMw</t>
+        </is>
+      </c>
+      <c r="E113" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-25 19:03:04</t>
+        </is>
+      </c>
+      <c r="F113" s="8" t="inlineStr">
+        <is>
+          <t>Talent Acquisition Manager</t>
+        </is>
+      </c>
+      <c r="G113" s="8" t="inlineStr">
+        <is>
+          <t>Matrix Comsec</t>
+        </is>
+      </c>
+      <c r="H113" s="8" t="inlineStr">
+        <is>
+          <t>Vadodara, Gujarat, India</t>
+        </is>
+      </c>
+      <c r="I113" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J113" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K113" s="8" t="inlineStr"/>
+      <c r="L113" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M113" s="8" t="inlineStr">
+        <is>
+          <t>Talent Acquisition Manager, not Recruiting Coordinator—higher-level role with coordination duties</t>
+        </is>
+      </c>
+      <c r="N113" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O113" s="8" t="inlineStr">
+        <is>
+          <t>Team leadership and high-volume hiring context; no quantified metrics</t>
+        </is>
+      </c>
+      <c r="P113" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" s="8" t="inlineStr">
+        <is>
+          <t>No evidence of Sales role recruiting (SDRs, AEs, AMs, BDRs)</t>
+        </is>
+      </c>
+      <c r="R113" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="S113" s="8" t="inlineStr">
+        <is>
+          <t>Automation Anywhere (US HQ SaaS, Tier 1) 3.75 yrs; Zycus (validated SaaS)</t>
+        </is>
+      </c>
+      <c r="T113" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U113" s="8" t="inlineStr">
+        <is>
+          <t>Certified Human Resource Business Partner (Aug 2020-Present)</t>
+        </is>
+      </c>
+      <c r="V113" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W113" s="8" t="inlineStr">
+        <is>
+          <t>Recruiting operations and team coordination implied; no explicit ATS tool mention</t>
+        </is>
+      </c>
+      <c r="X113" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y113" s="8" t="inlineStr">
+        <is>
+          <t>Multiple 3+ year tenures: Automation Anywhere 3.75 yrs, Matrix Comsec 4.83 yrs, Helios 5.33 yrs</t>
+        </is>
+      </c>
+      <c r="Z113" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA113" s="8" t="inlineStr">
+        <is>
+          <t>Zycus office in Princeton, NJ, United States (2 mos)</t>
+        </is>
+      </c>
+      <c r="AB113" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC113" s="8" t="inlineStr">
+        <is>
+          <t>Automation Anywhere is VC-backed Series-funded startup (Oct 2016-Jun 2020); current role not startup</t>
+        </is>
+      </c>
+      <c r="AD113" s="8" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="AE113" s="8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF113" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG113" s="8" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="AH113" s="8" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="AI113" s="8" t="inlineStr">
+        <is>
+          <t>72.35%</t>
+        </is>
+      </c>
+      <c r="AJ113" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AK113" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AL113" s="8" t="inlineStr">
+        <is>
+          <t>• 15+ years TA/recruiting experience
+• Strong tenure at Automation Anywhere (US HQ SaaS, Tier 1)
+• HR Business Partner certification
+• Located in Vadodara, Gujarat with extensive local recruiting</t>
+        </is>
+      </c>
+      <c r="AM113" s="8" t="inlineStr">
+        <is>
+          <t>Title mismatch (TA Manager vs. Recruiting Coordinator); No Sales hiring experience; No explicit ATS tool knowledge</t>
+        </is>
+      </c>
+      <c r="AN113" s="8" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="8" t="inlineStr">
+        <is>
+          <t>Aman Jobanputra</t>
+        </is>
+      </c>
+      <c r="B114" s="8" t="inlineStr"/>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/amanjobanputra</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/talent/profile/AEMAABZZ-IwB77-uZjVPZBHsfzVCHSRnfft-l94</t>
+        </is>
+      </c>
+      <c r="E114" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-25 19:04:53</t>
+        </is>
+      </c>
+      <c r="F114" s="8" t="inlineStr">
+        <is>
+          <t>Deputy Manager Talent Acquisition</t>
+        </is>
+      </c>
+      <c r="G114" s="8" t="inlineStr">
+        <is>
+          <t>Adani Group</t>
+        </is>
+      </c>
+      <c r="H114" s="8" t="inlineStr">
+        <is>
+          <t>Ahmedabad, Gujarat, India</t>
+        </is>
+      </c>
+      <c r="I114" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J114" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K114" s="8" t="inlineStr"/>
+      <c r="L114" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M114" s="8" t="inlineStr">
+        <is>
+          <t>Team Lead/Manager TA role at major companies; recruiting background but title elevated beyond coordinator level</t>
+        </is>
+      </c>
+      <c r="N114" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O114" s="8" t="inlineStr">
+        <is>
+          <t>Managed teams of 11-15 corporate recruiters; implies high-volume but no explicit metrics (calls/day, screens/week)</t>
+        </is>
+      </c>
+      <c r="P114" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q114" s="8" t="inlineStr">
+        <is>
+          <t>No evidence of hiring for Sales roles; IT/Corporate recruitment focus only</t>
+        </is>
+      </c>
+      <c r="R114" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="S114" s="8" t="inlineStr">
+        <is>
+          <t>6.2+ yrs at US HQ SaaS: eClinicalWorks (corporate recruiter 4.8yrs + team lead 1.7yrs); also at PetPooja (validated non-US SaaS)</t>
+        </is>
+      </c>
+      <c r="T114" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U114" s="8" t="inlineStr">
+        <is>
+          <t>Post Graduate Diploma in HR &amp; Marketing; B.E. Mechanical Engineering — no SHRM/PHR or MBA</t>
+        </is>
+      </c>
+      <c r="V114" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W114" s="8" t="inlineStr">
+        <is>
+          <t>HRIS and problem-solving listed; no explicit Greenhouse or ATS system mentioned; coordination implied but not explicit</t>
+        </is>
+      </c>
+      <c r="X114" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y114" s="8" t="inlineStr">
+        <is>
+          <t>4 yrs 8 mos at eClinicalWorks (single long tenure); 2+ yrs at PetPooja; recent 3 mos at Adani</t>
+        </is>
+      </c>
+      <c r="Z114" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA114" s="8" t="inlineStr">
+        <is>
+          <t>eClinicalWorks — US HQ SaaS company; likely US-facing recruiting roles</t>
+        </is>
+      </c>
+      <c r="AB114" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC114" s="8" t="inlineStr">
+        <is>
+          <t>No explicit VC-backed or startup experience; all roles at established enterprises</t>
+        </is>
+      </c>
+      <c r="AD114" s="8" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="AE114" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF114" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG114" s="8" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="AH114" s="8" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="AI114" s="8" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="AJ114" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AK114" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AL114" s="8" t="inlineStr">
+        <is>
+          <t>• 6+ yrs SaaS recruiting (eClinicalWorks tier-1 US HQ, PetPooja validated)
+• Team Lead TA with 11-15 recruiter span — high-volume environment
+• Ahmedabad-based, Gujarati location confirmed
+• Strong tenure: 4.8yrs at eClinicalWorks</t>
+        </is>
+      </c>
+      <c r="AM114" s="8" t="inlineStr">
+        <is>
+          <t>No Sales hiring experience; no explicit Greenhouse/ATS; no startup/early-stage background</t>
+        </is>
+      </c>
+      <c r="AN114" s="8" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="8" t="inlineStr">
+        <is>
+          <t>Shlesh Patel</t>
+        </is>
+      </c>
+      <c r="B115" s="8" t="inlineStr"/>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shlesh-patel-6830a945</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/talent/profile/AEMAAAlyOoMBzgc4owWEvF0jo7QpXYZQncBx72Q</t>
+        </is>
+      </c>
+      <c r="E115" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-25 19:06:45</t>
+        </is>
+      </c>
+      <c r="F115" s="8" t="inlineStr">
+        <is>
+          <t>HR (Talent Acquisition)</t>
+        </is>
+      </c>
+      <c r="G115" s="8" t="inlineStr">
+        <is>
+          <t>eClinicalWorks</t>
+        </is>
+      </c>
+      <c r="H115" s="8" t="inlineStr">
+        <is>
+          <t>Ahmedabad, Gujarat, India</t>
+        </is>
+      </c>
+      <c r="I115" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J115" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K115" s="8" t="inlineStr"/>
+      <c r="L115" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M115" s="8" t="inlineStr">
+        <is>
+          <t>HR TA at SaaS, but not specific coordinator title</t>
+        </is>
+      </c>
+      <c r="N115" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O115" s="8" t="inlineStr">
+        <is>
+          <t>10+ years in recruiting, but no quantified metrics</t>
+        </is>
+      </c>
+      <c r="P115" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" s="8" t="inlineStr">
+        <is>
+          <t>No explicit Sales hiring experience mentioned</t>
+        </is>
+      </c>
+      <c r="R115" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="S115" s="8" t="inlineStr">
+        <is>
+          <t>eClinicalWorks - US HQ SaaS (healthcare IT)</t>
+        </is>
+      </c>
+      <c r="T115" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U115" s="8" t="inlineStr">
+        <is>
+          <t>Bachelor of Commerce + Bachelor of Laws</t>
+        </is>
+      </c>
+      <c r="V115" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="W115" s="8" t="inlineStr">
+        <is>
+          <t>ATS mentioned, but no Greenhouse or specific tools</t>
+        </is>
+      </c>
+      <c r="X115" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y115" s="8" t="inlineStr">
+        <is>
+          <t>6+ years at eClinicalWorks demonstrates stability</t>
+        </is>
+      </c>
+      <c r="Z115" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA115" s="8" t="inlineStr">
+        <is>
+          <t>eClinicalWorks is US HQ, direct US coordination</t>
+        </is>
+      </c>
+      <c r="AB115" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC115" s="8" t="inlineStr">
+        <is>
+          <t>Primarily large enterprise, minor startup exposure</t>
+        </is>
+      </c>
+      <c r="AD115" s="8" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="AE115" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF115" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG115" s="8" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="AH115" s="8" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="AI115" s="8" t="inlineStr">
+        <is>
+          <t>70.5%</t>
+        </is>
+      </c>
+      <c r="AJ115" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AK115" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AL115" s="8" t="inlineStr">
+        <is>
+          <t>• 6+ years in talent acquisition at eClinicalWorks (US HQ SaaS)
+• Ahmedabad-based with Gujarat connections
+• Strong full-cycle recruiting background
+• ATS experience (though not Greenhouse)</t>
+        </is>
+      </c>
+      <c r="AM115" s="8" t="inlineStr">
+        <is>
+          <t>Title not specifically "Recruiting Coordinator"; No Sales hiring experience; Earlier career in manufacturing/staffing</t>
+        </is>
+      </c>
+      <c r="AN115" s="8" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="8" t="inlineStr">
+        <is>
+          <t>Tilak B.</t>
+        </is>
+      </c>
+      <c r="B116" s="8" t="inlineStr"/>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tilak-brahmbhatt</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/talent/profile/AEMAABm1REABq_0Qyx5-u9-g4y-rs7kmmB7uSL4</t>
+        </is>
+      </c>
+      <c r="E116" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-25 19:08:48</t>
+        </is>
+      </c>
+      <c r="F116" s="8" t="inlineStr">
+        <is>
+          <t>Senior Talent Acquisition</t>
+        </is>
+      </c>
+      <c r="G116" s="8" t="inlineStr">
+        <is>
+          <t>VC ERP Consulting</t>
+        </is>
+      </c>
+      <c r="H116" s="8" t="inlineStr">
+        <is>
+          <t>Ahmedabad, Gujarat, India</t>
+        </is>
+      </c>
+      <c r="I116" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J116" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K116" s="8" t="inlineStr"/>
+      <c r="L116" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M116" s="8" t="inlineStr">
+        <is>
+          <t>Senior TA role with TA/Acquisition titles</t>
+        </is>
+      </c>
+      <c r="N116" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O116" s="8" t="inlineStr">
+        <is>
+          <t>Sources applicants but no quantified metrics</t>
+        </is>
+      </c>
+      <c r="P116" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" s="8" t="inlineStr">
+        <is>
+          <t>No Sales hiring experience, IT recruitment focus</t>
+        </is>
+      </c>
+      <c r="R116" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="S116" s="8" t="inlineStr">
+        <is>
+          <t>eClinicalWorks (US SaaS, 9 mos)</t>
+        </is>
+      </c>
+      <c r="T116" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U116" s="8" t="inlineStr">
+        <is>
+          <t>BBA in Human Resources Management</t>
+        </is>
+      </c>
+      <c r="V116" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W116" s="8" t="inlineStr">
+        <is>
+          <t>No ATS mentioned; some coordination duties</t>
+        </is>
+      </c>
+      <c r="X116" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y116" s="8" t="inlineStr">
+        <is>
+          <t>6 roles in ~4 years, frequent moves</t>
+        </is>
+      </c>
+      <c r="Z116" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA116" s="8" t="inlineStr">
+        <is>
+          <t>eClinicalWorks is US HQ company</t>
+        </is>
+      </c>
+      <c r="AB116" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC116" s="8" t="inlineStr">
+        <is>
+          <t>VC ERP Consulting background unclear</t>
+        </is>
+      </c>
+      <c r="AD116" s="8" t="inlineStr">
+        <is>
+          <t>29.6</t>
+        </is>
+      </c>
+      <c r="AE116" s="8" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="AF116" s="8" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AG116" s="8" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
+      </c>
+      <c r="AH116" s="8" t="inlineStr">
+        <is>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="AI116" s="8" t="inlineStr">
+        <is>
+          <t>64.4%</t>
+        </is>
+      </c>
+      <c r="AJ116" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AK116" s="8" t="inlineStr">
+        <is>
+          <t>Maybe</t>
+        </is>
+      </c>
+      <c r="AL116" s="8" t="inlineStr">
+        <is>
+          <t>• Senior TA/Acquisition background at 6+ companies
+• Gujarat-based, Ahmedabad explicit
+• eClinicalWorks (US SaaS) experience
+• BBA in HR background</t>
+        </is>
+      </c>
+      <c r="AM116" s="8" t="inlineStr">
+        <is>
+          <t>No quantified high-volume sourcing metrics; no Sales hiring experience; no ATS tools mentioned; frequent job changes (1-1.5yr avg tenure)</t>
+        </is>
+      </c>
+      <c r="AN116" s="8" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="8" t="inlineStr">
+        <is>
+          <t>Jennifer M.</t>
+        </is>
+      </c>
+      <c r="B117" s="8" t="inlineStr"/>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jennifer-m-3389ab39</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/talent/profile/AEMAAAgn8hwBDSYyBXz6fjM4PrQrVTo46VaL3R4</t>
+        </is>
+      </c>
+      <c r="E117" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-25 19:11:45</t>
+        </is>
+      </c>
+      <c r="F117" s="8" t="inlineStr">
+        <is>
+          <t>Manager - Human Resource</t>
+        </is>
+      </c>
+      <c r="G117" s="8" t="inlineStr">
+        <is>
+          <t>Si2 Technologies Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="H117" s="8" t="inlineStr">
+        <is>
+          <t>Vadodara, Gujarat, India</t>
+        </is>
+      </c>
+      <c r="I117" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J117" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K117" s="8" t="inlineStr"/>
+      <c r="L117" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M117" s="8" t="inlineStr">
+        <is>
+          <t>HR Manager role, not Recruiting Coordinator title</t>
+        </is>
+      </c>
+      <c r="N117" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O117" s="8" t="inlineStr">
+        <is>
+          <t>No quantified volume metrics (calls/day, screens/week)</t>
+        </is>
+      </c>
+      <c r="P117" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q117" s="8" t="inlineStr">
+        <is>
+          <t>No Sales hiring experience mentioned</t>
+        </is>
+      </c>
+      <c r="R117" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S117" s="8" t="inlineStr">
+        <is>
+          <t>Automation Anywhere (US HQ tier 1), Si2 Technologies (SaaS)</t>
+        </is>
+      </c>
+      <c r="T117" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U117" s="8" t="inlineStr">
+        <is>
+          <t>PGD Business Mgmt + BA HR Management, no HR certification</t>
+        </is>
+      </c>
+      <c r="V117" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W117" s="8" t="inlineStr">
+        <is>
+          <t>No ATS mentioned; some coordination implied</t>
+        </is>
+      </c>
+      <c r="X117" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y117" s="8" t="inlineStr">
+        <is>
+          <t>8.2 years at Odysseus Solutions (2016-2024)</t>
+        </is>
+      </c>
+      <c r="Z117" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA117" s="8" t="inlineStr">
+        <is>
+          <t>Automation Anywhere (US HQ) 2.75 years</t>
+        </is>
+      </c>
+      <c r="AB117" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC117" s="8" t="inlineStr">
+        <is>
+          <t>No VC-backed or startup experience</t>
+        </is>
+      </c>
+      <c r="AD117" s="8" t="inlineStr">
+        <is>
+          <t>23.9</t>
+        </is>
+      </c>
+      <c r="AE117" s="8" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="AF117" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG117" s="8" t="inlineStr">
+        <is>
+          <t>26.3</t>
+        </is>
+      </c>
+      <c r="AH117" s="8" t="inlineStr">
+        <is>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="AI117" s="8" t="inlineStr">
+        <is>
+          <t>49.8%</t>
+        </is>
+      </c>
+      <c r="AJ117" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AK117" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL117" s="8" t="inlineStr">
+        <is>
+          <t>• SaaS experience at Automation Anywhere (US HQ)
+• Strong tenure stability (8+ years at previous role)
+• Located in Gujarat</t>
+        </is>
+      </c>
+      <c r="AM117" s="8" t="inlineStr">
+        <is>
+          <t>No recruiting coordinator title; no quantified high-volume metrics; no Sales hiring experience; no ATS proficiency mentioned</t>
+        </is>
+      </c>
+      <c r="AN117" s="8" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="8" t="inlineStr">
+        <is>
+          <t>Shefali M.</t>
+        </is>
+      </c>
+      <c r="B118" s="8" t="inlineStr"/>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shefali-m-888784b6</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/talent/profile/AEMAABis2-gBZXm6jJIFTiumg5WcQlWChJLnIAM</t>
+        </is>
+      </c>
+      <c r="E118" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-25 19:17:24</t>
+        </is>
+      </c>
+      <c r="F118" s="8" t="inlineStr">
+        <is>
+          <t>Human Resources Executive</t>
+        </is>
+      </c>
+      <c r="G118" s="8" t="inlineStr">
+        <is>
+          <t>Infocusp Innovations</t>
+        </is>
+      </c>
+      <c r="H118" s="8" t="inlineStr">
+        <is>
+          <t>Ahmedabad, Gujarat, India</t>
+        </is>
+      </c>
+      <c r="I118" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J118" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K118" s="8" t="inlineStr"/>
+      <c r="L118" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M118" s="8" t="inlineStr">
+        <is>
+          <t>HR Executive with recruiting responsibilities, not dedicated Recruiting Coordinator title</t>
+        </is>
+      </c>
+      <c r="N118" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O118" s="8" t="inlineStr">
+        <is>
+          <t>Mentions full-cycle recruitment and end-to-end strategy, but lacks quantified sourcing metrics (calls/screens/day)</t>
+        </is>
+      </c>
+      <c r="P118" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q118" s="8" t="inlineStr">
+        <is>
+          <t>No evidence of recruiting for Sales roles (SDRs, AEs, BDRs). Appears to be general HR/IT recruitment</t>
+        </is>
+      </c>
+      <c r="R118" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S118" s="8" t="inlineStr">
+        <is>
+          <t>Infocusp Innovations (3y3m, VC-backed SaaS) + eClinicalWorks (2y, US HQ SaaS tier 1). Strong SaaS exposure.</t>
+        </is>
+      </c>
+      <c r="T118" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U118" s="8" t="inlineStr">
+        <is>
+          <t>Bachelor's (B.Com) + Master's (Computer Management) - relevant to HR field</t>
+        </is>
+      </c>
+      <c r="V118" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W118" s="8" t="inlineStr">
+        <is>
+          <t>Managed ATS and HRMS systems, implemented interview frameworks. No specific tools mentioned (Greenhouse, Lever).</t>
+        </is>
+      </c>
+      <c r="X118" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y118" s="8" t="inlineStr">
+        <is>
+          <t>3y3m at Infocusp, 2y at eClinicalWorks. Shows stability with multi-year tenures at SaaS companies.</t>
+        </is>
+      </c>
+      <c r="Z118" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA118" s="8" t="inlineStr">
+        <is>
+          <t>2 years at eClinicalWorks (US HQ), managed US healthcare accounts. Direct US company experience.</t>
+        </is>
+      </c>
+      <c r="AB118" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC118" s="8" t="inlineStr">
+        <is>
+          <t>3+ years at VC-backed SaaS startup Infocusp Innovations. Clear startup environment experience.</t>
+        </is>
+      </c>
+      <c r="AD118" s="8" t="inlineStr">
+        <is>
+          <t>28.5</t>
+        </is>
+      </c>
+      <c r="AE118" s="8" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="AF118" s="8" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="AG118" s="8" t="inlineStr">
+        <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="AH118" s="8" t="inlineStr">
+        <is>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="AI118" s="8" t="inlineStr">
+        <is>
+          <t>73.68%</t>
+        </is>
+      </c>
+      <c r="AJ118" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AK118" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AL118" s="8" t="inlineStr">
+        <is>
+          <t>• SaaS recruiting experience: 5+ years across Infocusp (VC-backed) and eClinicalWorks (US HQ)
+• Ahmedabad-based, Gujarat location confirmed
+• HR Executive managing end-to-end recruitment and ATS systems
+• US company experience with healthcare account management
+• Strong startup environment exposure (VC-backed SaaS)
+• Comprehensive HR skills including interview frameworks and workforce planning</t>
+        </is>
+      </c>
+      <c r="AM118" s="8" t="inlineStr">
+        <is>
+          <t>No quantified high-volume sourcing metrics (calls/day, screens/week). No explicit Sales hiring experience. Title is HR Executive, not Recruiting Coordinator.</t>
+        </is>
+      </c>
+      <c r="AN118" s="8" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="8" t="inlineStr">
+        <is>
+          <t>Krupal Panchal</t>
+        </is>
+      </c>
+      <c r="B119" s="8" t="inlineStr"/>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/krupal-panchal-915765137</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/talent/profile/AEMAABdzqmUB-ipuJGxKMTeJBfKnQ_ulywWxzdk</t>
+        </is>
+      </c>
+      <c r="E119" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-25 19:19:13</t>
+        </is>
+      </c>
+      <c r="F119" s="8" t="inlineStr">
+        <is>
+          <t>Employee Relations - HRBP</t>
+        </is>
+      </c>
+      <c r="G119" s="8" t="inlineStr">
+        <is>
+          <t>eClinicalWorks</t>
+        </is>
+      </c>
+      <c r="H119" s="8" t="inlineStr">
+        <is>
+          <t>Ahmedabad, Gujarat, India</t>
+        </is>
+      </c>
+      <c r="I119" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J119" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K119" s="8" t="inlineStr"/>
+      <c r="L119" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M119" s="8" t="inlineStr">
+        <is>
+          <t>Currently Employee Relations HRBP, not recruiting coordinator title. Previously Corporate Recruiter but no coordination-specific duties mentioned</t>
+        </is>
+      </c>
+      <c r="N119" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O119" s="8" t="inlineStr">
+        <is>
+          <t>Mentions sourcing and screening but no quantified high-volume metrics (calls/day, screens/week, pipeline size)</t>
+        </is>
+      </c>
+      <c r="P119" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" s="8" t="inlineStr">
+        <is>
+          <t>No evidence of Sales hiring experience (SDRs, AEs, Account Managers, BDRs)</t>
+        </is>
+      </c>
+      <c r="R119" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="S119" s="8" t="inlineStr">
+        <is>
+          <t>eClinicalWorks — US HQ SaaS (Tier 1 validated), 7 yrs 3 months current role</t>
+        </is>
+      </c>
+      <c r="T119" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U119" s="8" t="inlineStr">
+        <is>
+          <t>PGDHRM from Jaipur National University + B.Com from Gujarat University</t>
+        </is>
+      </c>
+      <c r="V119" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W119" s="8" t="inlineStr">
+        <is>
+          <t>No ATS, Greenhouse, or recruiting operations experience mentioned</t>
+        </is>
+      </c>
+      <c r="X119" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y119" s="8" t="inlineStr">
+        <is>
+          <t>7 yrs 3 months at eClinicalWorks; 5+ years recruiting roles</t>
+        </is>
+      </c>
+      <c r="Z119" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA119" s="8" t="inlineStr">
+        <is>
+          <t>eClinicalWorks is US HQ SaaS company, currently employed there</t>
+        </is>
+      </c>
+      <c r="AB119" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC119" s="8" t="inlineStr">
+        <is>
+          <t>eClinicalWorks is established company, not early-stage startup</t>
+        </is>
+      </c>
+      <c r="AD119" s="8" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="AE119" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF119" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG119" s="8" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AH119" s="8" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="AI119" s="8" t="inlineStr">
+        <is>
+          <t>48.7%</t>
+        </is>
+      </c>
+      <c r="AJ119" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AK119" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL119" s="8" t="inlineStr">
+        <is>
+          <t>• SaaS experience at eClinicalWorks (Tier 1 US HQ company)
+• Strong tenure (7+ years at current company)
+• Located in Ahmedabad, Gujarat</t>
+        </is>
+      </c>
+      <c r="AM119" s="8" t="inlineStr">
+        <is>
+          <t>Not recruiting coordinator title. No quantified high-volume sourcing metrics. No Sales hiring background. No ATS/Greenhouse experience. Limited coordination-specific responsibilities.</t>
+        </is>
+      </c>
+      <c r="AN119" s="8" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="8" t="inlineStr">
+        <is>
+          <t>Ekta Amar Mehta</t>
+        </is>
+      </c>
+      <c r="B120" s="8" t="inlineStr"/>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ekta-amar-mehta-4a9b2a19a/</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/talent/profile/AEMAAC7MDEEB6z7FsJPz9S_HxSgMpAabKa9D81c</t>
+        </is>
+      </c>
+      <c r="E120" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-25 19:21:47</t>
+        </is>
+      </c>
+      <c r="F120" s="8" t="inlineStr">
+        <is>
+          <t>Head of Human Resources</t>
+        </is>
+      </c>
+      <c r="G120" s="8" t="inlineStr">
+        <is>
+          <t>Confidential</t>
+        </is>
+      </c>
+      <c r="H120" s="8" t="inlineStr">
+        <is>
+          <t>Ahmedabad, Gujarat, India</t>
+        </is>
+      </c>
+      <c r="I120" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J120" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K120" s="8" t="inlineStr"/>
+      <c r="L120" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="8" t="inlineStr">
+        <is>
+          <t>Head of HR, not recruiting coordinator — too senior, manages full HR operations</t>
+        </is>
+      </c>
+      <c r="N120" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="O120" s="8" t="inlineStr">
+        <is>
+          <t>Closed 250+ positions, conducted bulk hiring drives, managed high-volume campaigns</t>
+        </is>
+      </c>
+      <c r="P120" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q120" s="8" t="inlineStr">
+        <is>
+          <t>Recruited for Sales &amp; Marketing Dept at Kalpataru (250 positions closed)</t>
+        </is>
+      </c>
+      <c r="R120" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="S120" s="8" t="inlineStr">
+        <is>
+          <t>eClinicalWorks (US HQ SaaS validated), Azilen Technologies, current tech company</t>
+        </is>
+      </c>
+      <c r="T120" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U120" s="8" t="inlineStr">
+        <is>
+          <t>MBA (HR focus) + Post-MBA in Advanced HR from recognized institutions</t>
+        </is>
+      </c>
+      <c r="V120" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="W120" s="8" t="inlineStr">
+        <is>
+          <t>Oracle TALEO, Zoho ATS &amp; HRMS, Oracle, Adrenalin HR — extensive ATS experience</t>
+        </is>
+      </c>
+      <c r="X120" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y120" s="8" t="inlineStr">
+        <is>
+          <t>4.7 yrs current role, 3.75 yrs at Azilen — stable tenure across multiple roles</t>
+        </is>
+      </c>
+      <c r="Z120" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA120" s="8" t="inlineStr">
+        <is>
+          <t>GCM Grosvenor (US HQ), eClinicalWorks US exposure, direct US coordination</t>
+        </is>
+      </c>
+      <c r="AB120" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC120" s="8" t="inlineStr">
+        <is>
+          <t>No VC-backed or startup experience identified</t>
+        </is>
+      </c>
+      <c r="AD120" s="8" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="AE120" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF120" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG120" s="8" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="AH120" s="8" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="AI120" s="8" t="inlineStr">
+        <is>
+          <t>70.5%</t>
+        </is>
+      </c>
+      <c r="AJ120" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AK120" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AL120" s="8" t="inlineStr">
+        <is>
+          <t>• Extensive recruiting experience: 250+ positions closed, bulk hiring drives
+• eClinicalWorks (US HQ SaaS) + Azilen Technologies (SaaS) + current tech company
+• Oracle TALEO &amp; Zoho ATS experience — strong ops background
+• MBA + Advanced HR certification
+• US exposure: GCM Grosvenor, direct US hiring coordination
+• Ahmedabad-based, Gujarat connection explicit</t>
+        </is>
+      </c>
+      <c r="AM120" s="8" t="inlineStr">
+        <is>
+          <t>Current role is Head of HR (too senior for coordinator level) — may have outgrown recruiting coordination focus; experience is broad HR generalist rather than specialized recruiting coordinator</t>
+        </is>
+      </c>
+      <c r="AN120" s="8" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="8" t="inlineStr">
+        <is>
+          <t>Shubhangini V</t>
+        </is>
+      </c>
+      <c r="B121" s="8" t="inlineStr"/>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shubhangini-v-a7aa2419</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/talent/profile/AEMAAAPjiv4B93BCzyoLOcp54Oz21mpvdW5chqk</t>
+        </is>
+      </c>
+      <c r="E121" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-25 19:25:03</t>
+        </is>
+      </c>
+      <c r="F121" s="8" t="inlineStr">
+        <is>
+          <t>Specialist - Talent Acquisition</t>
+        </is>
+      </c>
+      <c r="G121" s="8" t="inlineStr">
+        <is>
+          <t>L&amp;T Technology Services</t>
+        </is>
+      </c>
+      <c r="H121" s="8" t="inlineStr">
+        <is>
+          <t>Vadodara, Gujarat, India</t>
+        </is>
+      </c>
+      <c r="I121" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J121" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K121" s="8" t="inlineStr"/>
+      <c r="L121" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M121" s="8" t="inlineStr">
+        <is>
+          <t>Specialist/Associate TA titles at SaaS, but not pure coordinator role</t>
+        </is>
+      </c>
+      <c r="N121" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O121" s="8" t="inlineStr">
+        <is>
+          <t>No quantified metrics for volume, calls, or cold outreach mentioned</t>
+        </is>
+      </c>
+      <c r="P121" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" s="8" t="inlineStr">
+        <is>
+          <t>No evidence of recruiting for Sales roles (SDRs, AEs, AMs, BDRs)</t>
+        </is>
+      </c>
+      <c r="R121" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="S121" s="8" t="inlineStr">
+        <is>
+          <t>Automation Anywhere - US HQ SaaS tier-1 company, 1.5 yr tenure</t>
+        </is>
+      </c>
+      <c r="T121" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U121" s="8" t="inlineStr">
+        <is>
+          <t>PG Diploma (Applied Economics), BCom, Postgraduate Diploma in HR Management (2023)</t>
+        </is>
+      </c>
+      <c r="V121" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W121" s="8" t="inlineStr">
+        <is>
+          <t>Workday ATS experience mentioned, but no evidence of Greenhouse or process ownership</t>
+        </is>
+      </c>
+      <c r="X121" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y121" s="8" t="inlineStr">
+        <is>
+          <t>Multiple 1-2 year stints (Air Products 1.7yr, Automation Anywhere 1.5yr, Matrix ComsecATL 2.7yr)</t>
+        </is>
+      </c>
+      <c r="Z121" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA121" s="8" t="inlineStr">
+        <is>
+          <t>India-based, no US company experience</t>
+        </is>
+      </c>
+      <c r="AB121" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC121" s="8" t="inlineStr">
+        <is>
+          <t>No startup/VC-backed experience evident</t>
+        </is>
+      </c>
+      <c r="AD121" s="8" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="AE121" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF121" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG121" s="8" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="AH121" s="8" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="AI121" s="8" t="inlineStr">
+        <is>
+          <t>48.5%</t>
+        </is>
+      </c>
+      <c r="AJ121" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AK121" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL121" s="8" t="inlineStr">
+        <is>
+          <t>• Specialist TA experience at Automation Anywhere (SaaS tier-1)
+• Full end-to-end recruitment process ownership
+• Vadodara-based, Gujarati location
+• Postgraduate HR diploma (2023)</t>
+        </is>
+      </c>
+      <c r="AM121" s="8" t="inlineStr">
+        <is>
+          <t>Critical gaps: Zero Sales hiring experience (critical for SwiftSku), no quantified high-volume hiring metrics, no Greenhouse experience, junior-level tenure history with frequent job changes, no US company exposure or startup experience</t>
+        </is>
+      </c>
+      <c r="AN121" s="8" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="8" t="inlineStr">
+        <is>
+          <t>Alisha Mittal</t>
+        </is>
+      </c>
+      <c r="B122" s="8" t="inlineStr"/>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alishaamittal</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/talent/profile/AEMAABuA-LcBpBol4DH5SHFsQtSp8uPicBfq6jA</t>
+        </is>
+      </c>
+      <c r="E122" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-25 19:26:45</t>
+        </is>
+      </c>
+      <c r="F122" s="8" t="inlineStr">
+        <is>
+          <t>Manager HRBP</t>
+        </is>
+      </c>
+      <c r="G122" s="8" t="inlineStr">
+        <is>
+          <t>MSBC Group</t>
+        </is>
+      </c>
+      <c r="H122" s="8" t="inlineStr">
+        <is>
+          <t>Ahmedabad, Gujarat, India</t>
+        </is>
+      </c>
+      <c r="I122" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J122" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K122" s="8" t="inlineStr"/>
+      <c r="L122" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M122" s="8" t="inlineStr">
+        <is>
+          <t>Recruiting Coordinator at IMS People Possible (2016-2017); recent 4+ years in HRBP/Operations with no recruiting coordination</t>
+        </is>
+      </c>
+      <c r="N122" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" s="8" t="inlineStr">
+        <is>
+          <t>No high-volume sourcing, cold calling, or candidate pipeline metrics; focus on HR policy, employee relations, HRIS</t>
+        </is>
+      </c>
+      <c r="P122" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" s="8" t="inlineStr">
+        <is>
+          <t>No Sales hiring experience mentioned; profile does not reference SDRs, AEs, BDRs, or Sales teams</t>
+        </is>
+      </c>
+      <c r="R122" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="S122" s="8" t="inlineStr">
+        <is>
+          <t>eClinicalWorks (US HQ SaaS, 5+ yrs) + AvistaTech (SaaS, 3+ yrs); solid SaaS background</t>
+        </is>
+      </c>
+      <c r="T122" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U122" s="8" t="inlineStr">
+        <is>
+          <t>MBA in HR (Pune Institute, 2014-2016); Bachelor's in Business/Commerce; no SHRM/PHR certifications</t>
+        </is>
+      </c>
+      <c r="V122" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W122" s="8" t="inlineStr">
+        <is>
+          <t>HRIS implementation at AvistaTech; no ATS mentioned (Greenhouse, Lever, etc.); not recruiting-specific operations</t>
+        </is>
+      </c>
+      <c r="X122" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y122" s="8" t="inlineStr">
+        <is>
+          <t>5+ years at eClinicalWorks (meets 3+ year benchmark); stable tenure history</t>
+        </is>
+      </c>
+      <c r="Z122" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA122" s="8" t="inlineStr">
+        <is>
+          <t>eClinicalWorks — US HQ SaaS company; likely US-facing coordination</t>
+        </is>
+      </c>
+      <c r="AB122" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC122" s="8" t="inlineStr">
+        <is>
+          <t>No VC-backed or early-stage startup experience visible</t>
+        </is>
+      </c>
+      <c r="AD122" s="8" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="AE122" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF122" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG122" s="8" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="AH122" s="8" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="AI122" s="8" t="inlineStr">
+        <is>
+          <t>36.5%</t>
+        </is>
+      </c>
+      <c r="AJ122" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AK122" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL122" s="8" t="inlineStr">
+        <is>
+          <t>No recruiting coordination experience in recent roles (4+ years in HRBP/Ops); zero high-volume sourcing or Sales hiring background; no recruiting ATS proficiency</t>
+        </is>
+      </c>
+      <c r="AM122" s="8" t="inlineStr">
+        <is>
+          <t>No recruiting coordination experience in recent roles (4+ years in HRBP/Ops); zero high-volume sourcing or Sales hiring background</t>
+        </is>
+      </c>
+      <c r="AN122" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AN1"/>

--- a/_OUTPUT--Recruiting_Coord.xlsx
+++ b/_OUTPUT--Recruiting_Coord.xlsx
@@ -1035,7 +1035,7 @@
         <v>4</v>
       </c>
       <c r="AG3" s="8" t="n">
-        <v>43.40000000000001</v>
+        <v>43.4</v>
       </c>
       <c r="AH3" s="8" t="n">
         <v>53.4</v>
@@ -2039,7 +2039,7 @@
         <v>6</v>
       </c>
       <c r="AG9" s="5" t="n">
-        <v>39.09999999999999</v>
+        <v>39.1</v>
       </c>
       <c r="AH9" s="5" t="n">
         <v>53.4</v>
@@ -8659,7 +8659,7 @@
         </is>
       </c>
       <c r="AD51" s="8" t="n">
-        <v>0</v>
+        <v>39.8</v>
       </c>
       <c r="AE51" s="8" t="n">
         <v>2.4</v>
@@ -8668,24 +8668,24 @@
         <v>0</v>
       </c>
       <c r="AG51" s="8" t="n">
-        <v>2.4</v>
+        <v>42.2</v>
       </c>
       <c r="AH51" s="8" t="n">
-        <v>52.8</v>
+        <v>53.4</v>
       </c>
       <c r="AI51" s="8" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>79.0%</t>
         </is>
       </c>
       <c r="AJ51" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AK51" s="8" t="inlineStr">
         <is>
-          <t>Hard No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AL51" s="8" t="inlineStr">
@@ -10055,7 +10055,7 @@
         </is>
       </c>
       <c r="AD60" s="8" t="n">
-        <v>0</v>
+        <v>36.9</v>
       </c>
       <c r="AE60" s="8" t="n">
         <v>2.4</v>
@@ -10064,24 +10064,24 @@
         <v>2</v>
       </c>
       <c r="AG60" s="8" t="n">
-        <v>4.4</v>
+        <v>41.3</v>
       </c>
       <c r="AH60" s="8" t="n">
-        <v>52.8</v>
+        <v>53.4</v>
       </c>
       <c r="AI60" s="8" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>77.3%</t>
         </is>
       </c>
       <c r="AJ60" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AK60" s="8" t="inlineStr">
         <is>
-          <t>Hard No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AL60" s="8" t="inlineStr">
@@ -11181,7 +11181,7 @@
         </is>
       </c>
       <c r="AD67" s="10" t="n">
-        <v>0</v>
+        <v>37.2</v>
       </c>
       <c r="AE67" s="10" t="n">
         <v>2.4</v>
@@ -11190,24 +11190,24 @@
         <v>0</v>
       </c>
       <c r="AG67" s="10" t="n">
-        <v>2.4</v>
+        <v>39.6</v>
       </c>
       <c r="AH67" s="10" t="n">
-        <v>52.8</v>
+        <v>53.4</v>
       </c>
       <c r="AI67" s="10" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>74.2%</t>
         </is>
       </c>
       <c r="AJ67" s="10" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AK67" s="10" t="inlineStr">
         <is>
-          <t>Hard No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AL67" s="10" t="inlineStr">
@@ -17118,42 +17118,36 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AD107" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE107" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF107" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG107" s="10" t="inlineStr">
-        <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="AH107" s="10" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
+      <c r="AD107" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE107" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF107" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG107" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH107" s="10" t="n">
+        <v>53.4</v>
       </c>
       <c r="AI107" s="10" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AJ107" s="10" t="inlineStr">
+        <is>
           <t>F</t>
         </is>
       </c>
-      <c r="AJ107" s="10" t="inlineStr">
-        <is>
-          <t>Unable to Evaluate</t>
-        </is>
-      </c>
-      <c r="AK107" s="10" t="n"/>
+      <c r="AK107" s="10" t="inlineStr">
+        <is>
+          <t>Hard No</t>
+        </is>
+      </c>
       <c r="AL107" s="10" t="n"/>
       <c r="AM107" s="10" t="n"/>
       <c r="AN107" s="10" t="inlineStr">
@@ -18251,7 +18245,7 @@
         </is>
       </c>
       <c r="AD114" s="8" t="n">
-        <v>0</v>
+        <v>26.2</v>
       </c>
       <c r="AE114" s="8" t="n">
         <v>0</v>
@@ -18260,24 +18254,24 @@
         <v>2</v>
       </c>
       <c r="AG114" s="8" t="n">
-        <v>2</v>
+        <v>28.2</v>
       </c>
       <c r="AH114" s="8" t="n">
-        <v>52.8</v>
+        <v>53.4</v>
       </c>
       <c r="AI114" s="8" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="AJ114" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AK114" s="8" t="inlineStr">
         <is>
-          <t>Hard No</t>
+          <t>Maybe</t>
         </is>
       </c>
       <c r="AL114" s="8" t="inlineStr">
@@ -18797,7 +18791,7 @@
         </is>
       </c>
       <c r="AD117" s="10" t="n">
-        <v>0</v>
+        <v>23.9</v>
       </c>
       <c r="AE117" s="10" t="n">
         <v>2.4</v>
@@ -18806,24 +18800,24 @@
         <v>0</v>
       </c>
       <c r="AG117" s="10" t="n">
-        <v>2.4</v>
+        <v>26.3</v>
       </c>
       <c r="AH117" s="10" t="n">
-        <v>52.8</v>
+        <v>53.4</v>
       </c>
       <c r="AI117" s="10" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="AJ117" s="10" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="AK117" s="10" t="inlineStr">
         <is>
-          <t>Hard No</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AL117" s="10" t="inlineStr">
@@ -19129,7 +19123,7 @@
         </is>
       </c>
       <c r="AD119" s="10" t="n">
-        <v>0</v>
+        <v>23.3</v>
       </c>
       <c r="AE119" s="10" t="n">
         <v>2.4</v>
@@ -19138,24 +19132,24 @@
         <v>0</v>
       </c>
       <c r="AG119" s="10" t="n">
-        <v>2.4</v>
+        <v>25.7</v>
       </c>
       <c r="AH119" s="10" t="n">
-        <v>52.8</v>
+        <v>53.4</v>
       </c>
       <c r="AI119" s="10" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="AJ119" s="10" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="AK119" s="10" t="inlineStr">
         <is>
-          <t>Hard No</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AL119" s="10" t="inlineStr">
@@ -20796,7 +20790,7 @@
         </is>
       </c>
       <c r="AD129" s="10" t="n">
-        <v>37.90000000000001</v>
+        <v>37.9</v>
       </c>
       <c r="AE129" s="10" t="n">
         <v>0.8</v>
@@ -33179,34 +33173,24 @@
           <t>Angel and Genie/datavuul appear startup-adjacent</t>
         </is>
       </c>
-      <c r="AD204" s="15" t="inlineStr">
-        <is>
-          <t>17.2</t>
-        </is>
-      </c>
-      <c r="AE204" s="15" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="AF204" s="15" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AG204" s="15" t="inlineStr">
-        <is>
-          <t>22.0</t>
-        </is>
-      </c>
-      <c r="AH204" s="15" t="inlineStr">
-        <is>
-          <t>53.4</t>
-        </is>
+      <c r="AD204" s="15" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="AE204" s="15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AF204" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG204" s="15" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="AH204" s="15" t="n">
+        <v>53.4</v>
       </c>
       <c r="AI204" s="15" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="AJ204" s="15" t="inlineStr">
@@ -34027,34 +34011,24 @@
           <t>Primarily large platforms/agencies; minimal clear startup/VC exposure</t>
         </is>
       </c>
-      <c r="AD209" s="15" t="inlineStr">
-        <is>
-          <t>23.3</t>
-        </is>
-      </c>
-      <c r="AE209" s="15" t="inlineStr">
-        <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="AF209" s="15" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AG209" s="15" t="inlineStr">
-        <is>
-          <t>27.7</t>
-        </is>
-      </c>
-      <c r="AH209" s="15" t="inlineStr">
-        <is>
-          <t>53.4</t>
-        </is>
+      <c r="AD209" s="15" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="AE209" s="15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF209" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG209" s="15" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="AH209" s="15" t="n">
+        <v>53.4</v>
       </c>
       <c r="AI209" s="15" t="inlineStr">
         <is>
-          <t>51.88%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="AJ209" s="15" t="inlineStr">
@@ -35624,7 +35598,7 @@
       </c>
       <c r="AN219" s="15" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>DUPLICATE</t>
         </is>
       </c>
     </row>
@@ -38747,7 +38721,7 @@
       </c>
       <c r="AI239" s="15" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="AJ239" s="15" t="inlineStr">
@@ -41218,7 +41192,7 @@
       </c>
       <c r="AI255" s="15" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AJ255" s="15" t="inlineStr">
@@ -43056,7 +43030,7 @@
       </c>
       <c r="AI268" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AJ268" s="15" t="inlineStr">
@@ -43066,7 +43040,7 @@
       </c>
       <c r="AK268" s="15" t="inlineStr">
         <is>
-          <t>Hard No — Auto-DQ</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AL268" s="15" t="inlineStr"/>
@@ -43182,7 +43156,7 @@
       </c>
       <c r="AI269" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AJ269" s="15" t="inlineStr">
@@ -43192,7 +43166,7 @@
       </c>
       <c r="AK269" s="15" t="inlineStr">
         <is>
-          <t>Hard No — Auto-DQ</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AL269" s="15" t="inlineStr"/>
@@ -43308,7 +43282,7 @@
       </c>
       <c r="AI270" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AJ270" s="15" t="inlineStr">
@@ -43318,7 +43292,7 @@
       </c>
       <c r="AK270" s="15" t="inlineStr">
         <is>
-          <t>Hard No — Auto-DQ</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AL270" s="15" t="inlineStr"/>
@@ -43434,7 +43408,7 @@
       </c>
       <c r="AI271" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AJ271" s="15" t="inlineStr">
@@ -43444,7 +43418,7 @@
       </c>
       <c r="AK271" s="15" t="inlineStr">
         <is>
-          <t>Hard No — Auto-DQ</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AL271" s="15" t="inlineStr"/>
@@ -43592,17 +43566,17 @@
       </c>
       <c r="AI272" s="15" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AJ272" s="15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="AK272" s="15" t="inlineStr">
         <is>
-          <t>Maybe</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AL272" s="15" t="inlineStr">
@@ -43726,7 +43700,7 @@
       </c>
       <c r="AI273" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AJ273" s="15" t="inlineStr">
@@ -43736,7 +43710,7 @@
       </c>
       <c r="AK273" s="15" t="inlineStr">
         <is>
-          <t>Hard No — Auto-DQ</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AL273" s="15" t="inlineStr"/>
@@ -43852,7 +43826,7 @@
       </c>
       <c r="AI274" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AJ274" s="15" t="inlineStr">
@@ -43862,7 +43836,7 @@
       </c>
       <c r="AK274" s="15" t="inlineStr">
         <is>
-          <t>Hard No — non-tech traditional industry recruiting (pharma mfg, coal &amp; mining, finance)</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AL274" s="15" t="inlineStr"/>
@@ -44020,7 +43994,7 @@
       </c>
       <c r="AK275" s="15" t="inlineStr">
         <is>
-          <t>Strong Yes — exact RC title at Lendingkart fintech (2yr), 3500-candidate high-volume hiring, Darwinbox + Greenhouse ATS, sales hiring experience</t>
+          <t>Strong Yes</t>
         </is>
       </c>
       <c r="AL275" s="15" t="inlineStr">
@@ -44144,7 +44118,7 @@
       </c>
       <c r="AI276" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AJ276" s="15" t="inlineStr">
@@ -44154,7 +44128,7 @@
       </c>
       <c r="AK276" s="15" t="inlineStr">
         <is>
-          <t>Hard No — pure agency staffing (REQ Solutions) with healthcare sourcing, no in-house experience</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AL276" s="15" t="inlineStr"/>
@@ -44270,7 +44244,7 @@
       </c>
       <c r="AI277" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AJ277" s="15" t="inlineStr">
@@ -44280,7 +44254,7 @@
       </c>
       <c r="AK277" s="15" t="inlineStr">
         <is>
-          <t>Hard No — pure agency staffing chain (Veterans Sourcing Group + IMS People Possible)</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AL277" s="15" t="inlineStr"/>
@@ -44396,7 +44370,7 @@
       </c>
       <c r="AI278" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AJ278" s="15" t="inlineStr">
@@ -44406,7 +44380,7 @@
       </c>
       <c r="AK278" s="15" t="inlineStr">
         <is>
-          <t>Hard No — pure agency staffing (Placon HR Services), no in-house experience, still pursuing MBA</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AL278" s="15" t="inlineStr"/>
@@ -44522,7 +44496,7 @@
       </c>
       <c r="AI279" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AJ279" s="15" t="inlineStr">
@@ -44532,7 +44506,7 @@
       </c>
       <c r="AK279" s="15" t="inlineStr">
         <is>
-          <t>Hard No — pure RPO agency (Horizon Talent Alliance), serving US staffing firms offshore</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AL279" s="15" t="inlineStr"/>
@@ -44648,7 +44622,7 @@
       </c>
       <c r="AI280" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AJ280" s="15" t="inlineStr">
@@ -44658,7 +44632,7 @@
       </c>
       <c r="AK280" s="15" t="inlineStr">
         <is>
-          <t>Hard No — pure agency (iConsultera), healthcare staffing, accounting industry</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AL280" s="15" t="inlineStr"/>
@@ -44774,7 +44748,7 @@
       </c>
       <c r="AI281" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AJ281" s="15" t="inlineStr">
@@ -44784,7 +44758,7 @@
       </c>
       <c r="AK281" s="15" t="inlineStr">
         <is>
-          <t>Hard No — pure agency chain (Confidential + LanceSoft), UK/Europe focus, contract/interim staffing</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AL281" s="15" t="inlineStr"/>
@@ -44942,7 +44916,7 @@
       </c>
       <c r="AK282" s="15" t="inlineStr">
         <is>
-          <t>Hard No — very junior TA at legal services company, no high-volume/SaaS/sales hiring experience</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AL282" s="15" t="inlineStr">
@@ -45066,7 +45040,7 @@
       </c>
       <c r="AI283" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AJ283" s="15" t="inlineStr">
@@ -45076,7 +45050,7 @@
       </c>
       <c r="AK283" s="15" t="inlineStr">
         <is>
-          <t>Hard No — pure agency chain (TalentCore + IMS Group), US IT staffing/bench sales</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AL283" s="15" t="inlineStr"/>
@@ -45192,7 +45166,7 @@
       </c>
       <c r="AI284" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AJ284" s="15" t="inlineStr">
@@ -45202,7 +45176,7 @@
       </c>
       <c r="AK284" s="15" t="inlineStr">
         <is>
-          <t>Hard No — BPO background (Medusind AR Caller) + IMS People Possible agency chain</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AL284" s="15" t="inlineStr"/>
@@ -45318,7 +45292,7 @@
       </c>
       <c r="AI285" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AJ285" s="15" t="inlineStr">
@@ -45328,7 +45302,7 @@
       </c>
       <c r="AK285" s="15" t="inlineStr">
         <is>
-          <t>Hard No — pure agency (Kyara Consulting), single role, no in-house experience</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AL285" s="15" t="inlineStr"/>
@@ -45444,7 +45418,7 @@
       </c>
       <c r="AI286" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AJ286" s="15" t="inlineStr">
@@ -45454,7 +45428,7 @@
       </c>
       <c r="AK286" s="15" t="inlineStr">
         <is>
-          <t>Hard No — pure IMS People Possible agency (4yr+), UK staffing, no in-house experience</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AL286" s="15" t="inlineStr"/>
@@ -45570,7 +45544,7 @@
       </c>
       <c r="AI287" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AJ287" s="15" t="inlineStr">
@@ -45580,7 +45554,7 @@
       </c>
       <c r="AK287" s="15" t="inlineStr">
         <is>
-          <t>Hard No — pure IMS Group agency (2yr 5mo), UK staffing operations</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AL287" s="15" t="inlineStr"/>
@@ -45727,24 +45701,22 @@
       <c r="AG288" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AH288" s="15" t="inlineStr">
-        <is>
-          <t>53.4</t>
-        </is>
+      <c r="AH288" s="15" t="n">
+        <v>53.4</v>
       </c>
       <c r="AI288" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AJ288" s="15" t="inlineStr">
         <is>
-          <t>DQ/F</t>
+          <t>F</t>
         </is>
       </c>
       <c r="AK288" s="15" t="inlineStr">
         <is>
-          <t>Hard No — primarily a teacher (6yr+), brief agency recruiter stint, education industry</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AL288" s="15" t="inlineStr"/>
@@ -45891,24 +45863,22 @@
       <c r="AG289" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AH289" s="15" t="inlineStr">
-        <is>
-          <t>53.4</t>
-        </is>
+      <c r="AH289" s="15" t="n">
+        <v>53.4</v>
       </c>
       <c r="AI289" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AJ289" s="15" t="inlineStr">
         <is>
-          <t>DQ/F</t>
+          <t>F</t>
         </is>
       </c>
       <c r="AK289" s="15" t="inlineStr">
         <is>
-          <t>Hard No — pure agency chain (IMS People Possible + Unity Systems), UK healthcare staffing</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AL289" s="15" t="inlineStr"/>
@@ -46055,24 +46025,22 @@
       <c r="AG290" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AH290" s="15" t="inlineStr">
-        <is>
-          <t>53.4</t>
-        </is>
+      <c r="AH290" s="15" t="n">
+        <v>53.4</v>
       </c>
       <c r="AI290" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AJ290" s="15" t="inlineStr">
         <is>
-          <t>DQ/F</t>
+          <t>F</t>
         </is>
       </c>
       <c r="AK290" s="15" t="inlineStr">
         <is>
-          <t>Hard No — pure IMS Group agency (4yr 6mo), pharma domain staffing</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AL290" s="15" t="inlineStr"/>
@@ -46219,24 +46187,22 @@
       <c r="AG291" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AH291" s="15" t="inlineStr">
-        <is>
-          <t>53.4</t>
-        </is>
+      <c r="AH291" s="15" t="n">
+        <v>53.4</v>
       </c>
       <c r="AI291" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AJ291" s="15" t="inlineStr">
         <is>
-          <t>DQ/F</t>
+          <t>F</t>
         </is>
       </c>
       <c r="AK291" s="15" t="inlineStr">
         <is>
-          <t>Hard No — pure IMS People Possible (2yr 9mo), healthcare/manufacturing/automotive staffing</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AL291" s="15" t="inlineStr"/>
@@ -46394,7 +46360,7 @@
       </c>
       <c r="AK292" s="15" t="inlineStr">
         <is>
-          <t>No — exact TA Coordinator title but only 4mo tenure, 17yr career gap, no relevant modern experience</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AL292" s="15" t="inlineStr">
@@ -46549,24 +46515,22 @@
       <c r="AG293" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AH293" s="15" t="inlineStr">
-        <is>
-          <t>53.4</t>
-        </is>
+      <c r="AH293" s="15" t="n">
+        <v>53.4</v>
       </c>
       <c r="AI293" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AJ293" s="15" t="inlineStr">
         <is>
-          <t>DQ/F</t>
+          <t>F</t>
         </is>
       </c>
       <c r="AK293" s="15" t="inlineStr">
         <is>
-          <t>Hard No — pure agency (Dangi Recruitment) + auto dealership sales background, very junior</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AL293" s="15" t="inlineStr"/>
@@ -46879,24 +46843,22 @@
       <c r="AG295" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AH295" s="15" t="inlineStr">
-        <is>
-          <t>53.4</t>
-        </is>
+      <c r="AH295" s="15" t="n">
+        <v>53.4</v>
       </c>
       <c r="AI295" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AJ295" s="15" t="inlineStr">
         <is>
-          <t>DQ/F</t>
+          <t>F</t>
         </is>
       </c>
       <c r="AK295" s="15" t="inlineStr">
         <is>
-          <t>Hard No — pure agency bench sales (Radiance Technologies), no recruiting background</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AL295" s="15" t="inlineStr"/>
@@ -47048,17 +47010,17 @@
       </c>
       <c r="AI296" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AJ296" s="15" t="inlineStr">
         <is>
-          <t>DQ/F</t>
+          <t>F</t>
         </is>
       </c>
       <c r="AK296" s="15" t="inlineStr">
         <is>
-          <t>Hard No — Auto-DQ</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AL296" s="15" t="n"/>
@@ -47210,17 +47172,17 @@
       </c>
       <c r="AI297" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AJ297" s="15" t="inlineStr">
         <is>
-          <t>DQ/F</t>
+          <t>F</t>
         </is>
       </c>
       <c r="AK297" s="15" t="inlineStr">
         <is>
-          <t>Hard No — Auto-DQ</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AL297" s="15" t="n"/>
@@ -47372,17 +47334,17 @@
       </c>
       <c r="AI298" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AJ298" s="15" t="inlineStr">
         <is>
-          <t>DQ/F</t>
+          <t>F</t>
         </is>
       </c>
       <c r="AK298" s="15" t="inlineStr">
         <is>
-          <t>Hard No — Auto-DQ</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AL298" s="15" t="n"/>
@@ -47534,17 +47496,17 @@
       </c>
       <c r="AI299" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AJ299" s="15" t="inlineStr">
         <is>
-          <t>DQ/F</t>
+          <t>F</t>
         </is>
       </c>
       <c r="AK299" s="15" t="inlineStr">
         <is>
-          <t>Hard No — Auto-DQ</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AL299" s="15" t="n"/>
@@ -47865,44 +47827,34 @@
           <t>Auto-DQ</t>
         </is>
       </c>
-      <c r="AD301" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE301" t="inlineStr">
-        <is>
-          <t>Auto-DQ</t>
-        </is>
-      </c>
-      <c r="AF301" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG301" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH301" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AD301" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE301" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF301" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG301" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH301" t="n">
+        <v>53.4</v>
       </c>
       <c r="AI301" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>F</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AL301" t="inlineStr">
@@ -47991,12 +47943,26 @@
       <c r="AA302" s="15" t="inlineStr"/>
       <c r="AB302" s="15" t="inlineStr"/>
       <c r="AC302" s="15" t="inlineStr"/>
-      <c r="AD302" s="15" t="inlineStr"/>
-      <c r="AE302" s="15" t="inlineStr"/>
-      <c r="AF302" s="15" t="inlineStr"/>
-      <c r="AG302" s="15" t="inlineStr"/>
-      <c r="AH302" s="15" t="inlineStr"/>
-      <c r="AI302" s="15" t="inlineStr"/>
+      <c r="AD302" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE302" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF302" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG302" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH302" s="15" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="AI302" s="15" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="AJ302" s="15" t="inlineStr">
         <is>
           <t>F</t>
@@ -48009,7 +47975,11 @@
       </c>
       <c r="AL302" s="15" t="inlineStr"/>
       <c r="AM302" s="15" t="inlineStr"/>
-      <c r="AN302" s="15" t="inlineStr"/>
+      <c r="AN302" s="15" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="15" t="inlineStr">
@@ -48159,7 +48129,11 @@
       </c>
       <c r="AL303" s="15" t="inlineStr"/>
       <c r="AM303" s="15" t="inlineStr"/>
-      <c r="AN303" s="15" t="inlineStr"/>
+      <c r="AN303" s="15" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="15" t="inlineStr">
@@ -48281,24 +48255,36 @@
           <t>ZURU appears growth-stage tech but no explicit VC/YC mention; Ascension is large enterprise; minimal startup experience</t>
         </is>
       </c>
-      <c r="AD304" s="15" t="inlineStr">
+      <c r="AD304" s="15" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="AE304" s="15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF304" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG304" s="15" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="AH304" s="15" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="AI304" s="15" t="inlineStr">
+        <is>
+          <t>56.9%</t>
+        </is>
+      </c>
+      <c r="AJ304" s="15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="AE304" s="15" t="inlineStr">
+      <c r="AK304" s="15" t="inlineStr">
         <is>
           <t>Maybe</t>
         </is>
       </c>
-      <c r="AF304" s="15" t="n">
-        <v>56.93</v>
-      </c>
-      <c r="AG304" s="15" t="inlineStr"/>
-      <c r="AH304" s="15" t="inlineStr"/>
-      <c r="AI304" s="15" t="inlineStr"/>
-      <c r="AJ304" s="15" t="inlineStr"/>
-      <c r="AK304" s="15" t="inlineStr"/>
       <c r="AL304" s="15" t="inlineStr"/>
       <c r="AM304" s="15" t="inlineStr"/>
       <c r="AN304" s="15" t="inlineStr"/>
@@ -48437,30 +48423,20 @@
           <t>Large enterprise/IT services background; no startup exposure evident</t>
         </is>
       </c>
-      <c r="AD305" s="15" t="inlineStr">
-        <is>
-          <t>23.6</t>
-        </is>
-      </c>
-      <c r="AE305" s="15" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="AF305" s="15" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AG305" s="15" t="inlineStr">
-        <is>
-          <t>26.4</t>
-        </is>
-      </c>
-      <c r="AH305" s="15" t="inlineStr">
-        <is>
-          <t>53.4</t>
-        </is>
+      <c r="AD305" s="15" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="AE305" s="15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AF305" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG305" s="15" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="AH305" s="15" t="n">
+        <v>53.4</v>
       </c>
       <c r="AI305" s="15" t="inlineStr">
         <is>
@@ -48613,30 +48589,20 @@
           <t>No clear startup/VC-backed company experience; self-employed consulting is not VC-backed</t>
         </is>
       </c>
-      <c r="AD306" s="15" t="inlineStr">
-        <is>
-          <t>21.6</t>
-        </is>
-      </c>
-      <c r="AE306" s="15" t="inlineStr">
-        <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="AF306" s="15" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AG306" s="15" t="inlineStr">
-        <is>
-          <t>26.0</t>
-        </is>
-      </c>
-      <c r="AH306" s="15" t="inlineStr">
-        <is>
-          <t>53.4</t>
-        </is>
+      <c r="AD306" s="15" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="AE306" s="15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF306" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG306" s="15" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH306" s="15" t="n">
+        <v>53.4</v>
       </c>
       <c r="AI306" s="15" t="inlineStr">
         <is>
@@ -48807,34 +48773,24 @@
           <t>No VC-backed or startup experience evident</t>
         </is>
       </c>
-      <c r="AD307" s="15" t="inlineStr">
-        <is>
-          <t>19.2</t>
-        </is>
-      </c>
-      <c r="AE307" s="15" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="AF307" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG307" s="15" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="AH307" s="15" t="inlineStr">
-        <is>
-          <t>53.4</t>
-        </is>
+      <c r="AD307" s="15" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="AE307" s="15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AF307" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG307" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH307" s="15" t="n">
+        <v>53.4</v>
       </c>
       <c r="AI307" s="15" t="inlineStr">
         <is>
-          <t>37.45%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="AJ307" s="15" t="inlineStr">
@@ -49106,34 +49062,24 @@
           <t>Profile not accessible</t>
         </is>
       </c>
-      <c r="AD309" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE309" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF309" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG309" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH309" s="15" t="inlineStr">
-        <is>
-          <t>53.4</t>
-        </is>
+      <c r="AD309" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE309" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF309" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG309" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH309" s="15" t="n">
+        <v>53.4</v>
       </c>
       <c r="AI309" s="15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AJ309" s="15" t="inlineStr">
@@ -49143,7 +49089,7 @@
       </c>
       <c r="AK309" s="15" t="inlineStr">
         <is>
-          <t>Unable to Evaluate</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AL309" s="15" t="inlineStr"/>
@@ -49340,6 +49286,11 @@
           <t>Career entirely in staffing agencies and IT services/non-product companies. No in-house recruiting coordinator experience at a product company. Adecco Group is a major staffing agency.</t>
         </is>
       </c>
+      <c r="AN310" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -49482,34 +49433,24 @@
           <t>Large enterprise (Vodafone subsidiary), no startup</t>
         </is>
       </c>
-      <c r="AD311" t="inlineStr">
-        <is>
-          <t>11.2</t>
-        </is>
-      </c>
-      <c r="AE311" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF311" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG311" t="inlineStr">
-        <is>
-          <t>11.2</t>
-        </is>
-      </c>
-      <c r="AH311" t="inlineStr">
-        <is>
-          <t>53.4</t>
-        </is>
+      <c r="AD311" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="AE311" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF311" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG311" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="AH311" t="n">
+        <v>53.4</v>
       </c>
       <c r="AI311" t="inlineStr">
         <is>
-          <t>20.97%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="AJ311" t="inlineStr">
@@ -49684,30 +49625,20 @@
           <t>Adani is large enterprise; CAVITAK unclear but appears staffing firm</t>
         </is>
       </c>
-      <c r="AD312" s="15" t="inlineStr">
-        <is>
-          <t>19.9</t>
-        </is>
-      </c>
-      <c r="AE312" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF312" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG312" s="15" t="inlineStr">
-        <is>
-          <t>19.9</t>
-        </is>
-      </c>
-      <c r="AH312" s="15" t="inlineStr">
-        <is>
-          <t>53.4</t>
-        </is>
+      <c r="AD312" s="15" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="AE312" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF312" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG312" s="15" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="AH312" s="15" t="n">
+        <v>53.4</v>
       </c>
       <c r="AI312" s="15" t="inlineStr">
         <is>
@@ -49740,7 +49671,11 @@
           <t>0% SaaS fit; non-tech traditional industry background (Adani); no Sales hiring exposure</t>
         </is>
       </c>
-      <c r="AN312" s="15" t="inlineStr"/>
+      <c r="AN312" s="15" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/_OUTPUT--Recruiting_Coord.xlsx
+++ b/_OUTPUT--Recruiting_Coord.xlsx
@@ -1035,7 +1035,7 @@
         <v>4</v>
       </c>
       <c r="AG3" s="8" t="n">
-        <v>43.4</v>
+        <v>43.40000000000001</v>
       </c>
       <c r="AH3" s="8" t="n">
         <v>53.4</v>
@@ -2039,7 +2039,7 @@
         <v>6</v>
       </c>
       <c r="AG9" s="5" t="n">
-        <v>39.1</v>
+        <v>39.09999999999999</v>
       </c>
       <c r="AH9" s="5" t="n">
         <v>53.4</v>
@@ -8659,7 +8659,7 @@
         </is>
       </c>
       <c r="AD51" s="8" t="n">
-        <v>39.8</v>
+        <v>0</v>
       </c>
       <c r="AE51" s="8" t="n">
         <v>2.4</v>
@@ -8668,24 +8668,24 @@
         <v>0</v>
       </c>
       <c r="AG51" s="8" t="n">
-        <v>42.2</v>
+        <v>2.4</v>
       </c>
       <c r="AH51" s="8" t="n">
-        <v>53.4</v>
+        <v>52.8</v>
       </c>
       <c r="AI51" s="8" t="inlineStr">
         <is>
-          <t>79.0%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="AJ51" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="AK51" s="8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AL51" s="8" t="inlineStr">
@@ -10055,7 +10055,7 @@
         </is>
       </c>
       <c r="AD60" s="8" t="n">
-        <v>36.9</v>
+        <v>0</v>
       </c>
       <c r="AE60" s="8" t="n">
         <v>2.4</v>
@@ -10064,24 +10064,24 @@
         <v>2</v>
       </c>
       <c r="AG60" s="8" t="n">
-        <v>41.3</v>
+        <v>4.4</v>
       </c>
       <c r="AH60" s="8" t="n">
-        <v>53.4</v>
+        <v>52.8</v>
       </c>
       <c r="AI60" s="8" t="inlineStr">
         <is>
-          <t>77.3%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="AJ60" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="AK60" s="8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AL60" s="8" t="inlineStr">
@@ -11181,7 +11181,7 @@
         </is>
       </c>
       <c r="AD67" s="10" t="n">
-        <v>37.2</v>
+        <v>0</v>
       </c>
       <c r="AE67" s="10" t="n">
         <v>2.4</v>
@@ -11190,24 +11190,24 @@
         <v>0</v>
       </c>
       <c r="AG67" s="10" t="n">
-        <v>39.6</v>
+        <v>2.4</v>
       </c>
       <c r="AH67" s="10" t="n">
-        <v>53.4</v>
+        <v>52.8</v>
       </c>
       <c r="AI67" s="10" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="AJ67" s="10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="AK67" s="10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AL67" s="10" t="inlineStr">
@@ -17118,36 +17118,42 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AD107" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE107" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF107" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG107" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH107" s="10" t="n">
-        <v>53.4</v>
+      <c r="AD107" s="10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE107" s="10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF107" s="10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG107" s="10" t="inlineStr">
+        <is>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="AH107" s="10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
       </c>
       <c r="AI107" s="10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>F</t>
         </is>
       </c>
       <c r="AJ107" s="10" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AK107" s="10" t="inlineStr">
-        <is>
-          <t>Hard No</t>
-        </is>
-      </c>
+          <t>Unable to Evaluate</t>
+        </is>
+      </c>
+      <c r="AK107" s="10" t="n"/>
       <c r="AL107" s="10" t="n"/>
       <c r="AM107" s="10" t="n"/>
       <c r="AN107" s="10" t="inlineStr">
@@ -18245,7 +18251,7 @@
         </is>
       </c>
       <c r="AD114" s="8" t="n">
-        <v>26.2</v>
+        <v>0</v>
       </c>
       <c r="AE114" s="8" t="n">
         <v>0</v>
@@ -18254,24 +18260,24 @@
         <v>2</v>
       </c>
       <c r="AG114" s="8" t="n">
-        <v>28.2</v>
+        <v>2</v>
       </c>
       <c r="AH114" s="8" t="n">
-        <v>53.4</v>
+        <v>52.8</v>
       </c>
       <c r="AI114" s="8" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="AJ114" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="AK114" s="8" t="inlineStr">
         <is>
-          <t>Maybe</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AL114" s="8" t="inlineStr">
@@ -18791,7 +18797,7 @@
         </is>
       </c>
       <c r="AD117" s="10" t="n">
-        <v>23.9</v>
+        <v>0</v>
       </c>
       <c r="AE117" s="10" t="n">
         <v>2.4</v>
@@ -18800,24 +18806,24 @@
         <v>0</v>
       </c>
       <c r="AG117" s="10" t="n">
-        <v>26.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH117" s="10" t="n">
-        <v>53.4</v>
+        <v>52.8</v>
       </c>
       <c r="AI117" s="10" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="AJ117" s="10" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="AK117" s="10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AL117" s="10" t="inlineStr">
@@ -19123,7 +19129,7 @@
         </is>
       </c>
       <c r="AD119" s="10" t="n">
-        <v>23.3</v>
+        <v>0</v>
       </c>
       <c r="AE119" s="10" t="n">
         <v>2.4</v>
@@ -19132,24 +19138,24 @@
         <v>0</v>
       </c>
       <c r="AG119" s="10" t="n">
-        <v>25.7</v>
+        <v>2.4</v>
       </c>
       <c r="AH119" s="10" t="n">
-        <v>53.4</v>
+        <v>52.8</v>
       </c>
       <c r="AI119" s="10" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="AJ119" s="10" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="AK119" s="10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Hard No</t>
         </is>
       </c>
       <c r="AL119" s="10" t="inlineStr">
@@ -20790,7 +20796,7 @@
         </is>
       </c>
       <c r="AD129" s="10" t="n">
-        <v>37.9</v>
+        <v>37.90000000000001</v>
       </c>
       <c r="AE129" s="10" t="n">
         <v>0.8</v>
@@ -33173,24 +33179,34 @@
           <t>Angel and Genie/datavuul appear startup-adjacent</t>
         </is>
       </c>
-      <c r="AD204" s="15" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="AE204" s="15" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AF204" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG204" s="15" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="AH204" s="15" t="n">
-        <v>53.4</v>
+      <c r="AD204" s="15" t="inlineStr">
+        <is>
+          <t>17.2</t>
+        </is>
+      </c>
+      <c r="AE204" s="15" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="AF204" s="15" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AG204" s="15" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="AH204" s="15" t="inlineStr">
+        <is>
+          <t>53.4</t>
+        </is>
       </c>
       <c r="AI204" s="15" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="AJ204" s="15" t="inlineStr">
@@ -34011,24 +34027,34 @@
           <t>Primarily large platforms/agencies; minimal clear startup/VC exposure</t>
         </is>
       </c>
-      <c r="AD209" s="15" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="AE209" s="15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AF209" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG209" s="15" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="AH209" s="15" t="n">
-        <v>53.4</v>
+      <c r="AD209" s="15" t="inlineStr">
+        <is>
+          <t>23.3</t>
+        </is>
+      </c>
+      <c r="AE209" s="15" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="AF209" s="15" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AG209" s="15" t="inlineStr">
+        <is>
+          <t>27.7</t>
+        </is>
+      </c>
+      <c r="AH209" s="15" t="inlineStr">
+        <is>
+          <t>53.4</t>
+        </is>
       </c>
       <c r="AI209" s="15" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>51.88%</t>
         </is>
       </c>
       <c r="AJ209" s="15" t="inlineStr">
@@ -35598,7 +35624,7 @@
       </c>
       <c r="AN219" s="15" t="inlineStr">
         <is>
-          <t>DUPLICATE</t>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
@@ -38721,7 +38747,7 @@
       </c>
       <c r="AI239" s="15" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="AJ239" s="15" t="inlineStr">
@@ -41192,7 +41218,7 @@
       </c>
       <c r="AI255" s="15" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="AJ255" s="15" t="inlineStr">
@@ -43030,7 +43056,7 @@
       </c>
       <c r="AI268" s="15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AJ268" s="15" t="inlineStr">
@@ -43040,7 +43066,7 @@
       </c>
       <c r="AK268" s="15" t="inlineStr">
         <is>
-          <t>Hard No</t>
+          <t>Hard No — Auto-DQ</t>
         </is>
       </c>
       <c r="AL268" s="15" t="inlineStr"/>
@@ -43156,7 +43182,7 @@
       </c>
       <c r="AI269" s="15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AJ269" s="15" t="inlineStr">
@@ -43166,7 +43192,7 @@
       </c>
       <c r="AK269" s="15" t="inlineStr">
         <is>
-          <t>Hard No</t>
+          <t>Hard No — Auto-DQ</t>
         </is>
       </c>
       <c r="AL269" s="15" t="inlineStr"/>
@@ -43282,7 +43308,7 @@
       </c>
       <c r="AI270" s="15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AJ270" s="15" t="inlineStr">
@@ -43292,7 +43318,7 @@
       </c>
       <c r="AK270" s="15" t="inlineStr">
         <is>
-          <t>Hard No</t>
+          <t>Hard No — Auto-DQ</t>
         </is>
       </c>
       <c r="AL270" s="15" t="inlineStr"/>
@@ -43408,7 +43434,7 @@
       </c>
       <c r="AI271" s="15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AJ271" s="15" t="inlineStr">
@@ -43418,7 +43444,7 @@
       </c>
       <c r="AK271" s="15" t="inlineStr">
         <is>
-          <t>Hard No</t>
+          <t>Hard No — Auto-DQ</t>
         </is>
       </c>
       <c r="AL271" s="15" t="inlineStr"/>
@@ -43566,17 +43592,17 @@
       </c>
       <c r="AI272" s="15" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="AJ272" s="15" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AK272" s="15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Maybe</t>
         </is>
       </c>
       <c r="AL272" s="15" t="inlineStr">
@@ -43700,7 +43726,7 @@
       </c>
       <c r="AI273" s="15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AJ273" s="15" t="inlineStr">
@@ -43710,7 +43736,7 @@
       </c>
       <c r="AK273" s="15" t="inlineStr">
         <is>
-          <t>Hard No</t>
+          <t>Hard No — Auto-DQ</t>
         </is>
       </c>
       <c r="AL273" s="15" t="inlineStr"/>
@@ -43826,7 +43852,7 @@
       </c>
       <c r="AI274" s="15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AJ274" s="15" t="inlineStr">
@@ -43836,7 +43862,7 @@
       </c>
       <c r="AK274" s="15" t="inlineStr">
         <is>
-          <t>Hard No</t>
+          <t>Hard No — non-tech traditional industry recruiting (pharma mfg, coal &amp; mining, finance)</t>
         </is>
       </c>
       <c r="AL274" s="15" t="inlineStr"/>
@@ -43994,7 +44020,7 @@
       </c>
       <c r="AK275" s="15" t="inlineStr">
         <is>
-          <t>Strong Yes</t>
+          <t>Strong Yes — exact RC title at Lendingkart fintech (2yr), 3500-candidate high-volume hiring, Darwinbox + Greenhouse ATS, sales hiring experience</t>
         </is>
       </c>
       <c r="AL275" s="15" t="inlineStr">
@@ -44118,7 +44144,7 @@
       </c>
       <c r="AI276" s="15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AJ276" s="15" t="inlineStr">
@@ -44128,7 +44154,7 @@
       </c>
       <c r="AK276" s="15" t="inlineStr">
         <is>
-          <t>Hard No</t>
+          <t>Hard No — pure agency staffing (REQ Solutions) with healthcare sourcing, no in-house experience</t>
         </is>
       </c>
       <c r="AL276" s="15" t="inlineStr"/>
@@ -44244,7 +44270,7 @@
       </c>
       <c r="AI277" s="15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AJ277" s="15" t="inlineStr">
@@ -44254,7 +44280,7 @@
       </c>
       <c r="AK277" s="15" t="inlineStr">
         <is>
-          <t>Hard No</t>
+          <t>Hard No — pure agency staffing chain (Veterans Sourcing Group + IMS People Possible)</t>
         </is>
       </c>
       <c r="AL277" s="15" t="inlineStr"/>
@@ -44370,7 +44396,7 @@
       </c>
       <c r="AI278" s="15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AJ278" s="15" t="inlineStr">
@@ -44380,7 +44406,7 @@
       </c>
       <c r="AK278" s="15" t="inlineStr">
         <is>
-          <t>Hard No</t>
+          <t>Hard No — pure agency staffing (Placon HR Services), no in-house experience, still pursuing MBA</t>
         </is>
       </c>
       <c r="AL278" s="15" t="inlineStr"/>
@@ -44496,7 +44522,7 @@
       </c>
       <c r="AI279" s="15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AJ279" s="15" t="inlineStr">
@@ -44506,7 +44532,7 @@
       </c>
       <c r="AK279" s="15" t="inlineStr">
         <is>
-          <t>Hard No</t>
+          <t>Hard No — pure RPO agency (Horizon Talent Alliance), serving US staffing firms offshore</t>
         </is>
       </c>
       <c r="AL279" s="15" t="inlineStr"/>
@@ -44622,7 +44648,7 @@
       </c>
       <c r="AI280" s="15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AJ280" s="15" t="inlineStr">
@@ -44632,7 +44658,7 @@
       </c>
       <c r="AK280" s="15" t="inlineStr">
         <is>
-          <t>Hard No</t>
+          <t>Hard No — pure agency (iConsultera), healthcare staffing, accounting industry</t>
         </is>
       </c>
       <c r="AL280" s="15" t="inlineStr"/>
@@ -44748,7 +44774,7 @@
       </c>
       <c r="AI281" s="15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AJ281" s="15" t="inlineStr">
@@ -44758,7 +44784,7 @@
       </c>
       <c r="AK281" s="15" t="inlineStr">
         <is>
-          <t>Hard No</t>
+          <t>Hard No — pure agency chain (Confidential + LanceSoft), UK/Europe focus, contract/interim staffing</t>
         </is>
       </c>
       <c r="AL281" s="15" t="inlineStr"/>
@@ -44916,7 +44942,7 @@
       </c>
       <c r="AK282" s="15" t="inlineStr">
         <is>
-          <t>Hard No</t>
+          <t>Hard No — very junior TA at legal services company, no high-volume/SaaS/sales hiring experience</t>
         </is>
       </c>
       <c r="AL282" s="15" t="inlineStr">
@@ -45040,7 +45066,7 @@
       </c>
       <c r="AI283" s="15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AJ283" s="15" t="inlineStr">
@@ -45050,7 +45076,7 @@
       </c>
       <c r="AK283" s="15" t="inlineStr">
         <is>
-          <t>Hard No</t>
+          <t>Hard No — pure agency chain (TalentCore + IMS Group), US IT staffing/bench sales</t>
         </is>
       </c>
       <c r="AL283" s="15" t="inlineStr"/>
@@ -45166,7 +45192,7 @@
       </c>
       <c r="AI284" s="15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AJ284" s="15" t="inlineStr">
@@ -45176,7 +45202,7 @@
       </c>
       <c r="AK284" s="15" t="inlineStr">
         <is>
-          <t>Hard No</t>
+          <t>Hard No — BPO background (Medusind AR Caller) + IMS People Possible agency chain</t>
         </is>
       </c>
       <c r="AL284" s="15" t="inlineStr"/>
@@ -45292,7 +45318,7 @@
       </c>
       <c r="AI285" s="15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AJ285" s="15" t="inlineStr">
@@ -45302,7 +45328,7 @@
       </c>
       <c r="AK285" s="15" t="inlineStr">
         <is>
-          <t>Hard No</t>
+          <t>Hard No — pure agency (Kyara Consulting), single role, no in-house experience</t>
         </is>
       </c>
       <c r="AL285" s="15" t="inlineStr"/>
@@ -45418,7 +45444,7 @@
       </c>
       <c r="AI286" s="15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AJ286" s="15" t="inlineStr">
@@ -45428,7 +45454,7 @@
       </c>
       <c r="AK286" s="15" t="inlineStr">
         <is>
-          <t>Hard No</t>
+          <t>Hard No — pure IMS People Possible agency (4yr+), UK staffing, no in-house experience</t>
         </is>
       </c>
       <c r="AL286" s="15" t="inlineStr"/>
@@ -45544,7 +45570,7 @@
       </c>
       <c r="AI287" s="15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AJ287" s="15" t="inlineStr">
@@ -45554,7 +45580,7 @@
       </c>
       <c r="AK287" s="15" t="inlineStr">
         <is>
-          <t>Hard No</t>
+          <t>Hard No — pure IMS Group agency (2yr 5mo), UK staffing operations</t>
         </is>
       </c>
       <c r="AL287" s="15" t="inlineStr"/>
@@ -45701,22 +45727,24 @@
       <c r="AG288" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AH288" s="15" t="n">
-        <v>53.4</v>
+      <c r="AH288" s="15" t="inlineStr">
+        <is>
+          <t>53.4</t>
+        </is>
       </c>
       <c r="AI288" s="15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AJ288" s="15" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>DQ/F</t>
         </is>
       </c>
       <c r="AK288" s="15" t="inlineStr">
         <is>
-          <t>Hard No</t>
+          <t>Hard No — primarily a teacher (6yr+), brief agency recruiter stint, education industry</t>
         </is>
       </c>
       <c r="AL288" s="15" t="inlineStr"/>
@@ -45863,22 +45891,24 @@
       <c r="AG289" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AH289" s="15" t="n">
-        <v>53.4</v>
+      <c r="AH289" s="15" t="inlineStr">
+        <is>
+          <t>53.4</t>
+        </is>
       </c>
       <c r="AI289" s="15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AJ289" s="15" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>DQ/F</t>
         </is>
       </c>
       <c r="AK289" s="15" t="inlineStr">
         <is>
-          <t>Hard No</t>
+          <t>Hard No — pure agency chain (IMS People Possible + Unity Systems), UK healthcare staffing</t>
         </is>
       </c>
       <c r="AL289" s="15" t="inlineStr"/>
@@ -46025,22 +46055,24 @@
       <c r="AG290" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AH290" s="15" t="n">
-        <v>53.4</v>
+      <c r="AH290" s="15" t="inlineStr">
+        <is>
+          <t>53.4</t>
+        </is>
       </c>
       <c r="AI290" s="15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AJ290" s="15" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>DQ/F</t>
         </is>
       </c>
       <c r="AK290" s="15" t="inlineStr">
         <is>
-          <t>Hard No</t>
+          <t>Hard No — pure IMS Group agency (4yr 6mo), pharma domain staffing</t>
         </is>
       </c>
       <c r="AL290" s="15" t="inlineStr"/>
@@ -46187,22 +46219,24 @@
       <c r="AG291" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AH291" s="15" t="n">
-        <v>53.4</v>
+      <c r="AH291" s="15" t="inlineStr">
+        <is>
+          <t>53.4</t>
+        </is>
       </c>
       <c r="AI291" s="15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AJ291" s="15" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>DQ/F</t>
         </is>
       </c>
       <c r="AK291" s="15" t="inlineStr">
         <is>
-          <t>Hard No</t>
+          <t>Hard No — pure IMS People Possible (2yr 9mo), healthcare/manufacturing/automotive staffing</t>
         </is>
       </c>
       <c r="AL291" s="15" t="inlineStr"/>
@@ -46360,7 +46394,7 @@
       </c>
       <c r="AK292" s="15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No — exact TA Coordinator title but only 4mo tenure, 17yr career gap, no relevant modern experience</t>
         </is>
       </c>
       <c r="AL292" s="15" t="inlineStr">
@@ -46515,22 +46549,24 @@
       <c r="AG293" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AH293" s="15" t="n">
-        <v>53.4</v>
+      <c r="AH293" s="15" t="inlineStr">
+        <is>
+          <t>53.4</t>
+        </is>
       </c>
       <c r="AI293" s="15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AJ293" s="15" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>DQ/F</t>
         </is>
       </c>
       <c r="AK293" s="15" t="inlineStr">
         <is>
-          <t>Hard No</t>
+          <t>Hard No — pure agency (Dangi Recruitment) + auto dealership sales background, very junior</t>
         </is>
       </c>
       <c r="AL293" s="15" t="inlineStr"/>
@@ -46843,22 +46879,24 @@
       <c r="AG295" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AH295" s="15" t="n">
-        <v>53.4</v>
+      <c r="AH295" s="15" t="inlineStr">
+        <is>
+          <t>53.4</t>
+        </is>
       </c>
       <c r="AI295" s="15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AJ295" s="15" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>DQ/F</t>
         </is>
       </c>
       <c r="AK295" s="15" t="inlineStr">
         <is>
-          <t>Hard No</t>
+          <t>Hard No — pure agency bench sales (Radiance Technologies), no recruiting background</t>
         </is>
       </c>
       <c r="AL295" s="15" t="inlineStr"/>
@@ -47010,17 +47048,17 @@
       </c>
       <c r="AI296" s="15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AJ296" s="15" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>DQ/F</t>
         </is>
       </c>
       <c r="AK296" s="15" t="inlineStr">
         <is>
-          <t>Hard No</t>
+          <t>Hard No — Auto-DQ</t>
         </is>
       </c>
       <c r="AL296" s="15" t="n"/>
@@ -47172,17 +47210,17 @@
       </c>
       <c r="AI297" s="15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AJ297" s="15" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>DQ/F</t>
         </is>
       </c>
       <c r="AK297" s="15" t="inlineStr">
         <is>
-          <t>Hard No</t>
+          <t>Hard No — Auto-DQ</t>
         </is>
       </c>
       <c r="AL297" s="15" t="n"/>
@@ -47334,17 +47372,17 @@
       </c>
       <c r="AI298" s="15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AJ298" s="15" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>DQ/F</t>
         </is>
       </c>
       <c r="AK298" s="15" t="inlineStr">
         <is>
-          <t>Hard No</t>
+          <t>Hard No — Auto-DQ</t>
         </is>
       </c>
       <c r="AL298" s="15" t="n"/>
@@ -47496,17 +47534,17 @@
       </c>
       <c r="AI299" s="15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AJ299" s="15" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>DQ/F</t>
         </is>
       </c>
       <c r="AK299" s="15" t="inlineStr">
         <is>
-          <t>Hard No</t>
+          <t>Hard No — Auto-DQ</t>
         </is>
       </c>
       <c r="AL299" s="15" t="n"/>
@@ -47827,34 +47865,44 @@
           <t>Auto-DQ</t>
         </is>
       </c>
-      <c r="AD301" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE301" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF301" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG301" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH301" t="n">
-        <v>53.4</v>
+      <c r="AD301" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE301" t="inlineStr">
+        <is>
+          <t>Auto-DQ</t>
+        </is>
+      </c>
+      <c r="AF301" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG301" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH301" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="AI301" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
         <is>
-          <t>Hard No</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AL301" t="inlineStr">
@@ -47943,26 +47991,12 @@
       <c r="AA302" s="15" t="inlineStr"/>
       <c r="AB302" s="15" t="inlineStr"/>
       <c r="AC302" s="15" t="inlineStr"/>
-      <c r="AD302" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE302" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF302" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG302" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH302" s="15" t="n">
-        <v>53.4</v>
-      </c>
-      <c r="AI302" s="15" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
+      <c r="AD302" s="15" t="inlineStr"/>
+      <c r="AE302" s="15" t="inlineStr"/>
+      <c r="AF302" s="15" t="inlineStr"/>
+      <c r="AG302" s="15" t="inlineStr"/>
+      <c r="AH302" s="15" t="inlineStr"/>
+      <c r="AI302" s="15" t="inlineStr"/>
       <c r="AJ302" s="15" t="inlineStr">
         <is>
           <t>F</t>
@@ -47975,11 +48009,7 @@
       </c>
       <c r="AL302" s="15" t="inlineStr"/>
       <c r="AM302" s="15" t="inlineStr"/>
-      <c r="AN302" s="15" t="inlineStr">
-        <is>
-          <t>DUPLICATE</t>
-        </is>
-      </c>
+      <c r="AN302" s="15" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" s="15" t="inlineStr">
@@ -48129,11 +48159,7 @@
       </c>
       <c r="AL303" s="15" t="inlineStr"/>
       <c r="AM303" s="15" t="inlineStr"/>
-      <c r="AN303" s="15" t="inlineStr">
-        <is>
-          <t>DUPLICATE</t>
-        </is>
-      </c>
+      <c r="AN303" s="15" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" s="15" t="inlineStr">
@@ -48255,36 +48281,24 @@
           <t>ZURU appears growth-stage tech but no explicit VC/YC mention; Ascension is large enterprise; minimal startup experience</t>
         </is>
       </c>
-      <c r="AD304" s="15" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="AE304" s="15" t="n">
-        <v>1.6</v>
+      <c r="AD304" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AE304" s="15" t="inlineStr">
+        <is>
+          <t>Maybe</t>
+        </is>
       </c>
       <c r="AF304" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG304" s="15" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="AH304" s="15" t="n">
-        <v>53.4</v>
-      </c>
-      <c r="AI304" s="15" t="inlineStr">
-        <is>
-          <t>56.9%</t>
-        </is>
-      </c>
-      <c r="AJ304" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AK304" s="15" t="inlineStr">
-        <is>
-          <t>Maybe</t>
-        </is>
-      </c>
+        <v>56.93</v>
+      </c>
+      <c r="AG304" s="15" t="inlineStr"/>
+      <c r="AH304" s="15" t="inlineStr"/>
+      <c r="AI304" s="15" t="inlineStr"/>
+      <c r="AJ304" s="15" t="inlineStr"/>
+      <c r="AK304" s="15" t="inlineStr"/>
       <c r="AL304" s="15" t="inlineStr"/>
       <c r="AM304" s="15" t="inlineStr"/>
       <c r="AN304" s="15" t="inlineStr"/>
@@ -48423,20 +48437,30 @@
           <t>Large enterprise/IT services background; no startup exposure evident</t>
         </is>
       </c>
-      <c r="AD305" s="15" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="AE305" s="15" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AF305" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG305" s="15" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="AH305" s="15" t="n">
-        <v>53.4</v>
+      <c r="AD305" s="15" t="inlineStr">
+        <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="AE305" s="15" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="AF305" s="15" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AG305" s="15" t="inlineStr">
+        <is>
+          <t>26.4</t>
+        </is>
+      </c>
+      <c r="AH305" s="15" t="inlineStr">
+        <is>
+          <t>53.4</t>
+        </is>
       </c>
       <c r="AI305" s="15" t="inlineStr">
         <is>
@@ -48589,20 +48613,30 @@
           <t>No clear startup/VC-backed company experience; self-employed consulting is not VC-backed</t>
         </is>
       </c>
-      <c r="AD306" s="15" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="AE306" s="15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AF306" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG306" s="15" t="n">
-        <v>26</v>
-      </c>
-      <c r="AH306" s="15" t="n">
-        <v>53.4</v>
+      <c r="AD306" s="15" t="inlineStr">
+        <is>
+          <t>21.6</t>
+        </is>
+      </c>
+      <c r="AE306" s="15" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="AF306" s="15" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AG306" s="15" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
+      <c r="AH306" s="15" t="inlineStr">
+        <is>
+          <t>53.4</t>
+        </is>
       </c>
       <c r="AI306" s="15" t="inlineStr">
         <is>
@@ -48773,24 +48807,34 @@
           <t>No VC-backed or startup experience evident</t>
         </is>
       </c>
-      <c r="AD307" s="15" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="AE307" s="15" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AF307" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG307" s="15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH307" s="15" t="n">
-        <v>53.4</v>
+      <c r="AD307" s="15" t="inlineStr">
+        <is>
+          <t>19.2</t>
+        </is>
+      </c>
+      <c r="AE307" s="15" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="AF307" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG307" s="15" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="AH307" s="15" t="inlineStr">
+        <is>
+          <t>53.4</t>
+        </is>
       </c>
       <c r="AI307" s="15" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>37.45%</t>
         </is>
       </c>
       <c r="AJ307" s="15" t="inlineStr">
@@ -49062,24 +49106,34 @@
           <t>Profile not accessible</t>
         </is>
       </c>
-      <c r="AD309" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE309" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF309" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG309" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH309" s="15" t="n">
-        <v>53.4</v>
+      <c r="AD309" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE309" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF309" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG309" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH309" s="15" t="inlineStr">
+        <is>
+          <t>53.4</t>
+        </is>
       </c>
       <c r="AI309" s="15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AJ309" s="15" t="inlineStr">
@@ -49089,7 +49143,7 @@
       </c>
       <c r="AK309" s="15" t="inlineStr">
         <is>
-          <t>Hard No</t>
+          <t>Unable to Evaluate</t>
         </is>
       </c>
       <c r="AL309" s="15" t="inlineStr"/>
@@ -49286,11 +49340,6 @@
           <t>Career entirely in staffing agencies and IT services/non-product companies. No in-house recruiting coordinator experience at a product company. Adecco Group is a major staffing agency.</t>
         </is>
       </c>
-      <c r="AN310" t="inlineStr">
-        <is>
-          <t>DUPLICATE</t>
-        </is>
-      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -49433,24 +49482,34 @@
           <t>Large enterprise (Vodafone subsidiary), no startup</t>
         </is>
       </c>
-      <c r="AD311" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="AE311" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF311" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG311" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="AH311" t="n">
-        <v>53.4</v>
+      <c r="AD311" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="AE311" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF311" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG311" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="AH311" t="inlineStr">
+        <is>
+          <t>53.4</t>
+        </is>
       </c>
       <c r="AI311" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>20.97%</t>
         </is>
       </c>
       <c r="AJ311" t="inlineStr">
@@ -49625,20 +49684,30 @@
           <t>Adani is large enterprise; CAVITAK unclear but appears staffing firm</t>
         </is>
       </c>
-      <c r="AD312" s="15" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="AE312" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF312" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG312" s="15" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="AH312" s="15" t="n">
-        <v>53.4</v>
+      <c r="AD312" s="15" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="AE312" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF312" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG312" s="15" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="AH312" s="15" t="inlineStr">
+        <is>
+          <t>53.4</t>
+        </is>
       </c>
       <c r="AI312" s="15" t="inlineStr">
         <is>
@@ -49671,11 +49740,7 @@
           <t>0% SaaS fit; non-tech traditional industry background (Adani); no Sales hiring exposure</t>
         </is>
       </c>
-      <c r="AN312" s="15" t="inlineStr">
-        <is>
-          <t>DUPLICATE</t>
-        </is>
-      </c>
+      <c r="AN312" s="15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
